--- a/src/lil/stagiaires.xlsx
+++ b/src/lil/stagiaires.xlsx
@@ -398,12 +398,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BN63"/>
+  <dimension ref="A1:BN54"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
     <col min="5" max="5" width="35.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
@@ -419,17 +419,17 @@
     <col min="17" max="17" width="16.83203125" customWidth="1"/>
     <col min="18" max="18" width="68.83203125" customWidth="1"/>
     <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="23.83203125" customWidth="1"/>
+    <col min="20" max="20" width="30.83203125" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="28.83203125" customWidth="1"/>
-    <col min="23" max="23" width="45.83203125" customWidth="1"/>
+    <col min="23" max="23" width="38.83203125" customWidth="1"/>
     <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="19.83203125" customWidth="1"/>
     <col min="26" max="26" width="5.83203125" customWidth="1"/>
     <col min="27" max="27" width="10.83203125" customWidth="1"/>
     <col min="28" max="28" width="5.83203125" customWidth="1"/>
     <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="26.83203125" customWidth="1"/>
+    <col min="30" max="30" width="19.83203125" customWidth="1"/>
     <col min="31" max="31" width="28.83203125" customWidth="1"/>
     <col min="32" max="32" width="5.83203125" customWidth="1"/>
     <col min="33" max="33" width="6.83203125" customWidth="1"/>
@@ -448,16 +448,16 @@
     <col min="46" max="46" width="16.83203125" customWidth="1"/>
     <col min="47" max="47" width="68.83203125" customWidth="1"/>
     <col min="48" max="48" width="61.83203125" customWidth="1"/>
-    <col min="49" max="49" width="36.83203125" customWidth="1"/>
+    <col min="49" max="49" width="59.83203125" customWidth="1"/>
     <col min="50" max="50" width="68.83203125" customWidth="1"/>
-    <col min="51" max="51" width="40.83203125" customWidth="1"/>
+    <col min="51" max="51" width="38.83203125" customWidth="1"/>
     <col min="52" max="52" width="27.83203125" customWidth="1"/>
     <col min="53" max="53" width="28.83203125" customWidth="1"/>
-    <col min="54" max="54" width="104.83203125" customWidth="1"/>
+    <col min="54" max="54" width="25.83203125" customWidth="1"/>
     <col min="55" max="55" width="28.83203125" customWidth="1"/>
     <col min="56" max="56" width="59.83203125" customWidth="1"/>
     <col min="57" max="57" width="31.83203125" customWidth="1"/>
-    <col min="58" max="58" width="32.83203125" customWidth="1"/>
+    <col min="58" max="58" width="28.83203125" customWidth="1"/>
     <col min="59" max="59" width="24.83203125" customWidth="1"/>
     <col min="60" max="60" width="68.83203125" customWidth="1"/>
     <col min="61" max="61" width="23.83203125" customWidth="1"/>
@@ -670,22 +670,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>136959</v>
+        <v>140632</v>
       </c>
       <c r="B2" t="str">
         <v>Homme</v>
       </c>
       <c r="C2" t="str">
-        <v>ALI</v>
+        <v>SANA</v>
       </c>
       <c r="D2" t="str">
-        <v>Ilyas</v>
+        <v>Estebane</v>
       </c>
       <c r="E2" t="str">
-        <v>i.ali@e2c-grandlille.fr</v>
+        <v>e.sana@e2c-grandlille.fr</v>
       </c>
       <c r="F2" t="str">
-        <v>0744977269</v>
+        <v>0673028120</v>
       </c>
       <c r="G2" t="str">
         <v>Grand Lille</v>
@@ -693,56 +693,50 @@
       <c r="H2" t="str">
         <v>Lille</v>
       </c>
-      <c r="K2" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L2" t="str">
-        <v>référés Anne</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M2" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O2" t="str">
-        <v>CAPEAU Anne</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="R2" s="1">
-        <v>37610</v>
+        <v>39784</v>
       </c>
       <c r="T2" t="str">
-        <v>KOLYOLEY (SOMALIE)</v>
+        <v>MAUBEUGE</v>
       </c>
       <c r="U2" t="str">
-        <v>AUTRE</v>
+        <v>FRANCAISE</v>
       </c>
       <c r="W2" t="str">
-        <v>33 Chemin des Visiteurs</v>
+        <v>59 Rue Gabriel Péri</v>
       </c>
       <c r="X2" t="str">
-        <v>59650</v>
+        <v>59117</v>
       </c>
       <c r="Y2" t="str">
-        <v>Villeneuve-d'Ascq</v>
+        <v>Wervicq-Sud</v>
       </c>
       <c r="Z2" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>QN05965M</v>
+        <v>Non</v>
       </c>
       <c r="AB2" t="str">
         <v>Non</v>
       </c>
       <c r="AC2" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD2" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE2" t="str">
         <v>Non</v>
@@ -763,78 +757,93 @@
         <v>Non</v>
       </c>
       <c r="AK2" t="str">
-        <v>71h</v>
+        <v>19h15m</v>
       </c>
       <c r="AL2" t="str">
         <v>0m</v>
       </c>
       <c r="AM2" t="str">
-        <v>3h15m</v>
+        <v>67h45m</v>
       </c>
       <c r="AN2" s="1">
-        <v>46160.44532407408</v>
+        <v>46202.47935185185</v>
       </c>
       <c r="AP2" s="1">
-        <v>46436.44375</v>
+        <v>46475.64513888889</v>
       </c>
       <c r="AU2" s="1">
-        <v>46133.67013888889</v>
+        <v>46189.46111111111</v>
       </c>
       <c r="AV2" t="str">
-        <v>MISSION LOCALE MÉTROPOLE EST - Antenne de Villeneuve d'Ascq</v>
+        <v>MELT MISSION EMPLOI LYS TOURCOING</v>
       </c>
       <c r="AW2" t="str">
-        <v>Rachel TILIER</v>
+        <v>Nathalie DESMARCHELIER</v>
       </c>
       <c r="AX2" s="1">
-        <v>46111.675</v>
+        <v>46184.46319444444</v>
+      </c>
+      <c r="AY2" t="str">
+        <v>ndesmarchelier@lamelt.fr</v>
+      </c>
+      <c r="AZ2" t="str">
+        <v>0788801854</v>
       </c>
       <c r="BA2" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB2" t="str">
+        <v>HIRAUX</v>
+      </c>
+      <c r="BC2" t="str">
+        <v>Gaëlle</v>
+      </c>
+      <c r="BD2" t="str">
+        <v>59 RUE GABRIEL PERI 59117 WERVICQ SUD</v>
+      </c>
+      <c r="BE2" t="str">
+        <v>0659021513</v>
+      </c>
+      <c r="BF2" t="str">
+        <v>hiraux.gaelle@orange.fr</v>
       </c>
       <c r="BG2" t="str">
-        <v>16881</v>
-      </c>
-      <c r="BH2" s="1">
-        <v>45950.083333333336</v>
-      </c>
-      <c r="BI2" t="str">
-        <v>5954620N</v>
+        <v>19454</v>
       </c>
       <c r="BJ2" t="str">
-        <v>5d2e3311-ed98-4b42-b7a9-5715f1406f2f</v>
+        <v>e0f0829e-0ecb-44ed-be29-500760603aa0</v>
       </c>
       <c r="BK2" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL2" t="str">
         <v/>
       </c>
       <c r="BM2" t="str">
-        <v>ilyasmahamoudo7@outlook.com</v>
+        <v>sanaestebane0208@gmail.com</v>
       </c>
       <c r="BN2" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_sana_e2c-grandlille_fr/IgBS3my-BefOQr-O9cgZYEAgAUdOvzITaDw_7cQLBWwV1O8?e=ODQtdL</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>136918</v>
+        <v>140528</v>
       </c>
       <c r="B3" t="str">
         <v>Homme</v>
       </c>
       <c r="C3" t="str">
-        <v>HAMRIT</v>
+        <v>MERZOUK</v>
       </c>
       <c r="D3" t="str">
-        <v>Imrane</v>
+        <v>Rayane</v>
       </c>
       <c r="E3" t="str">
-        <v>i.hamrit@e2c-grandlille.fr</v>
+        <v>r.merzouk@e2c-grandlille.fr</v>
       </c>
       <c r="F3" t="str">
-        <v>0651833730</v>
+        <v>0668821298</v>
       </c>
       <c r="G3" t="str">
         <v>Grand Lille</v>
@@ -842,53 +851,41 @@
       <c r="H3" t="str">
         <v>Lille</v>
       </c>
-      <c r="I3" t="str">
-        <v>Electricien / Electricienne bâtiment tertiaire, Coiffeur / Coiffeuse</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Contrat à durée indéterminée, Contrat d'apprentissage</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Je sais</v>
-      </c>
       <c r="L3" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M3" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O3" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R3" s="1">
-        <v>39781</v>
+        <v>38083</v>
       </c>
       <c r="T3" t="str">
-        <v>TOURCOING</v>
+        <v>LILLE</v>
       </c>
       <c r="U3" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W3" t="str">
-        <v>7 Rue Jean Vilar</v>
+        <v>40 Rue de Madrid</v>
       </c>
       <c r="X3" t="str">
-        <v>59650</v>
+        <v>59130</v>
       </c>
       <c r="Y3" t="str">
-        <v>Villeneuve-d'Ascq</v>
+        <v>Lambersart</v>
       </c>
       <c r="Z3" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>QN05965M</v>
+        <v>Non</v>
       </c>
       <c r="AB3" t="str">
         <v>Non</v>
@@ -897,7 +894,7 @@
         <v>NON</v>
       </c>
       <c r="AD3" t="str">
-        <v>3 non validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE3" t="str">
         <v>Non</v>
@@ -918,87 +915,78 @@
         <v>Non</v>
       </c>
       <c r="AK3" t="str">
-        <v>54h45m</v>
+        <v>61h</v>
       </c>
       <c r="AL3" t="str">
-        <v>0m</v>
+        <v>15h</v>
       </c>
       <c r="AM3" t="str">
-        <v>19h30m</v>
+        <v>26h</v>
       </c>
       <c r="AN3" s="1">
-        <v>46160.454421296294</v>
+        <v>46202.47869212963</v>
       </c>
       <c r="AP3" s="1">
-        <v>46436.45416666667</v>
+        <v>46475.63333333333</v>
       </c>
       <c r="AU3" s="1">
-        <v>46133.46527777778</v>
+        <v>46182.48472222222</v>
       </c>
       <c r="AV3" t="str">
-        <v>MISSION LOCALE MÉTROPOLE EST - Antenne de Villeneuve d'Ascq</v>
+        <v>POLE EMPLOI - Lomme</v>
       </c>
       <c r="AW3" t="str">
-        <v>Jessica MARSAC</v>
+        <v>Dominique ALLOUCHERY</v>
       </c>
       <c r="AX3" s="1">
-        <v>46111.46666666667</v>
+        <v>46182.48611111111</v>
       </c>
       <c r="BA3" t="str">
         <v>NON</v>
       </c>
-      <c r="BB3" t="str">
-        <v>FETNACI</v>
-      </c>
-      <c r="BC3" t="str">
-        <v>Nadia</v>
-      </c>
-      <c r="BD3" t="str">
-        <v>7/8 Rue Jean Vilar - 59650 VILLENEUVE D'ASCQ</v>
-      </c>
-      <c r="BE3" t="str">
-        <v>0759215607</v>
-      </c>
-      <c r="BF3" t="str">
-        <v>nennou.arfaoui@outlook.fr</v>
-      </c>
       <c r="BG3" t="str">
-        <v>16887</v>
+        <v>19452</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>45811.083333333336</v>
+      </c>
+      <c r="BI3" t="str">
+        <v>5704766H</v>
       </c>
       <c r="BJ3" t="str">
-        <v>bda8c068-0fc1-48cd-8085-1f3e3ef22502</v>
+        <v>24737686-24b1-432a-8d4b-7bc61fc95743</v>
       </c>
       <c r="BK3" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL3" t="str">
         <v/>
       </c>
       <c r="BM3" t="str">
-        <v>imranehamrit5@gmail.com</v>
+        <v>mr.rayanee@icloud.com</v>
       </c>
       <c r="BN3" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_merzouk_e2c-grandlille_fr/IgBCN8aduOgvRbmw68LrrABrAYUOaKhuIm_tgOrR8T7CuiI?e=xDoKmP</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>136511</v>
+        <v>140520</v>
       </c>
       <c r="B4" t="str">
         <v>Femme</v>
       </c>
       <c r="C4" t="str">
-        <v>FERDI</v>
+        <v>SENOUCI</v>
       </c>
       <c r="D4" t="str">
-        <v>Sofia</v>
+        <v>Asma</v>
       </c>
       <c r="E4" t="str">
-        <v>s.ferdi@e2c-grandlille.fr</v>
+        <v>a.senouci@e2c-grandlille.fr</v>
       </c>
       <c r="F4" t="str">
-        <v>0636134787</v>
+        <v>0650128711</v>
       </c>
       <c r="G4" t="str">
         <v>Grand Lille</v>
@@ -1007,43 +995,43 @@
         <v>Lille</v>
       </c>
       <c r="I4" t="str">
-        <v>Moniteur éducateur / Monitrice éducatrice</v>
+        <v>Prothésiste dentaire</v>
       </c>
       <c r="K4" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L4" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés Sura</v>
       </c>
       <c r="M4" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O4" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>JAMIL HUSSAIN Sura</v>
       </c>
       <c r="P4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R4" s="1">
-        <v>39482</v>
+        <v>39224</v>
       </c>
       <c r="T4" t="str">
-        <v>ROUBAIX</v>
+        <v>BORDJ BOU ARRERIDI (ALGERIE)</v>
       </c>
       <c r="U4" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W4" t="str">
-        <v>647 Rue du Bazinghien</v>
+        <v>116 Boulevard de la Liberté</v>
       </c>
       <c r="X4" t="str">
-        <v>59120</v>
+        <v>59800</v>
       </c>
       <c r="Y4" t="str">
-        <v>Loos</v>
+        <v>Lille</v>
       </c>
       <c r="Z4" t="str">
         <v>Non</v>
@@ -1052,10 +1040,10 @@
         <v>Non</v>
       </c>
       <c r="AC4" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD4" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE4" t="str">
         <v>Non</v>
@@ -1070,84 +1058,75 @@
         <v>Non</v>
       </c>
       <c r="AI4" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AJ4" t="str">
         <v>Non</v>
       </c>
       <c r="AK4" t="str">
-        <v>58h15m</v>
+        <v>63h</v>
       </c>
       <c r="AL4" t="str">
-        <v>0m</v>
+        <v>9h</v>
       </c>
       <c r="AM4" t="str">
-        <v>16h</v>
+        <v>21h</v>
       </c>
       <c r="AN4" s="1">
-        <v>46160.454050925924</v>
+        <v>46202.47976851852</v>
       </c>
       <c r="AP4" s="1">
-        <v>46436.45347222222</v>
+        <v>46475.65138888889</v>
       </c>
       <c r="AU4" s="1">
-        <v>46133.635416666664</v>
+        <v>46182.46666666667</v>
       </c>
       <c r="AV4" t="str">
-        <v>LES APPRENTIS D'AUTEUIL - Loos</v>
-      </c>
-      <c r="AW4" t="str">
-        <v>Audrey DAVOINE</v>
+        <v>En direct</v>
       </c>
       <c r="AX4" s="1">
-        <v>46128.63680555556</v>
-      </c>
-      <c r="AY4" t="str">
-        <v>audrey.davoine@apprentis-auteuil.org</v>
-      </c>
-      <c r="AZ4" t="str">
-        <v>0669912158</v>
+        <v>46182.46875</v>
       </c>
       <c r="BA4" t="str">
         <v>NON</v>
       </c>
       <c r="BG4" t="str">
-        <v>16886</v>
+        <v>19455</v>
       </c>
       <c r="BJ4" t="str">
-        <v>3c282c36-3b0d-43e9-8473-ecdc2269a7c6</v>
+        <v>aa6148cf-bec6-41cf-a81b-878e5919f414</v>
       </c>
       <c r="BK4" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL4" t="str">
         <v/>
       </c>
       <c r="BM4" t="str">
-        <v>fbaiou87@gmail.com</v>
+        <v>senouciasma87@gmail.com</v>
       </c>
       <c r="BN4" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_senouci_e2c-grandlille_fr/IgDuMEXZXhRAQJZAv0htAYQzAbz-jqBeMxc6fquL0qQ4uvI?e=wSZgjz</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>135154</v>
+        <v>140029</v>
       </c>
       <c r="B5" t="str">
         <v>Femme</v>
       </c>
       <c r="C5" t="str">
-        <v>DESREUMAUX</v>
+        <v>PHILIPPE</v>
       </c>
       <c r="D5" t="str">
-        <v>Rachel</v>
+        <v>Mélina</v>
       </c>
       <c r="E5" t="str">
-        <v>r.desreumaux@e2c-grandlille.fr</v>
+        <v>m.philippe@e2c-grandlille.fr</v>
       </c>
       <c r="F5" t="str">
-        <v>0749417478</v>
+        <v>0646762588</v>
       </c>
       <c r="G5" t="str">
         <v>Grand Lille</v>
@@ -1155,29 +1134,23 @@
       <c r="H5" t="str">
         <v>Lille</v>
       </c>
-      <c r="I5" t="str">
-        <v>Secrétaire bureautique, Serveur / Serveuse en restauration, Animateur / Animatrice petite enfance</v>
-      </c>
-      <c r="K5" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L5" t="str">
-        <v>référés Camille</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M5" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O5" t="str">
-        <v>PEAU Camille</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R5" s="1">
-        <v>39437</v>
+        <v>40194</v>
       </c>
       <c r="T5" t="str">
         <v>ARMENTIERES</v>
@@ -1185,11 +1158,14 @@
       <c r="U5" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="W5" t="str">
+        <v>23 Allee des Paturelles</v>
+      </c>
       <c r="X5" t="str">
-        <v>59120</v>
+        <v>59890</v>
       </c>
       <c r="Y5" t="str">
-        <v>Loos</v>
+        <v>Quesnoy-sur-Deûle</v>
       </c>
       <c r="Z5" t="str">
         <v>Non</v>
@@ -1198,7 +1174,7 @@
         <v>Non</v>
       </c>
       <c r="AC5" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD5" t="str">
         <v>Infra 3</v>
@@ -1222,75 +1198,84 @@
         <v>Non</v>
       </c>
       <c r="AK5" t="str">
-        <v>64h30m</v>
+        <v>61h15m</v>
       </c>
       <c r="AL5" t="str">
-        <v>0m</v>
+        <v>42h</v>
       </c>
       <c r="AM5" t="str">
-        <v>9h45m</v>
+        <v>22h45m</v>
       </c>
       <c r="AN5" s="1">
-        <v>46160.45359953704</v>
+        <v>46202.479050925926</v>
       </c>
       <c r="AP5" s="1">
-        <v>46436.45277777778</v>
+        <v>46475.63958333333</v>
       </c>
       <c r="AU5" s="1">
-        <v>46119.68958333333</v>
+        <v>46175.677777777775</v>
       </c>
       <c r="AV5" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE MNO - Antenne Saint André</v>
       </c>
       <c r="AX5" s="1">
-        <v>46113.69027777778</v>
+        <v>46175.67916666667</v>
       </c>
       <c r="BA5" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB5" t="str">
+        <v>LEVEQUE</v>
+      </c>
+      <c r="BC5" t="str">
+        <v>Coralie</v>
+      </c>
+      <c r="BD5" t="str">
+        <v>23 ALLEE DES PATURELLES 59890 QUESNOY SUR DEULE</v>
+      </c>
+      <c r="BE5" t="str">
+        <v>0629563212</v>
+      </c>
+      <c r="BF5" t="str">
+        <v>coralieleveq@hotmail.fr</v>
       </c>
       <c r="BG5" t="str">
-        <v>16885</v>
-      </c>
-      <c r="BH5" s="1">
-        <v>46091.041666666664</v>
-      </c>
-      <c r="BI5" t="str">
-        <v>5983301N</v>
+        <v>19453</v>
       </c>
       <c r="BJ5" t="str">
-        <v>883c92ed-d293-42f2-b674-981abd97c3b4</v>
+        <v>af1ec817-ca99-4b63-a6e5-b6e068e92dc4</v>
       </c>
       <c r="BK5" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL5" t="str">
         <v/>
       </c>
       <c r="BM5" t="str">
-        <v>desreumauxrachel0@gmail.com</v>
+        <v>melinaphilippe16@gmail.com</v>
       </c>
       <c r="BN5" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_philippe_e2c-grandlille_fr/IgB_e8M62VKhRr8DJjpOrD9LAToVXsaTRObZUS6mQxpHogQ?e=puOcug</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>134990</v>
+        <v>140018</v>
       </c>
       <c r="B6" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C6" t="str">
-        <v>AUTEM</v>
+        <v>EL MAACH</v>
       </c>
       <c r="D6" t="str">
-        <v>Isaac</v>
+        <v>Salma</v>
       </c>
       <c r="E6" t="str">
-        <v>i.autem@e2c-grandlille.fr</v>
+        <v>s.elmaach@e2c-grandlille.fr</v>
       </c>
       <c r="F6" t="str">
-        <v>0767281621</v>
+        <v>0780744199</v>
       </c>
       <c r="G6" t="str">
         <v>Grand Lille</v>
@@ -1298,38 +1283,35 @@
       <c r="H6" t="str">
         <v>Lille</v>
       </c>
-      <c r="K6" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L6" t="str">
-        <v>référés Anne</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M6" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O6" t="str">
-        <v>CAPEAU Anne</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P6">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q6">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R6" s="1">
-        <v>38713</v>
+        <v>39851</v>
       </c>
       <c r="T6" t="str">
-        <v>ARRAS</v>
+        <v>LILLE</v>
       </c>
       <c r="U6" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W6" t="str">
-        <v>47 Rue Pascal</v>
+        <v>3 Rue de la Loire</v>
       </c>
       <c r="X6" t="str">
-        <v>59800</v>
+        <v>59000</v>
       </c>
       <c r="Y6" t="str">
         <v>Lille</v>
@@ -1338,16 +1320,16 @@
         <v>Oui</v>
       </c>
       <c r="AA6" t="str">
-        <v>QN05973M</v>
+        <v>QN05972M</v>
       </c>
       <c r="AB6" t="str">
         <v>Non</v>
       </c>
       <c r="AC6" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD6" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE6" t="str">
         <v>Non</v>
@@ -1365,84 +1347,93 @@
         <v>Non</v>
       </c>
       <c r="AJ6" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AK6" t="str">
-        <v>71h</v>
+        <v>48h30m</v>
       </c>
       <c r="AL6" t="str">
-        <v>0m</v>
+        <v>35h</v>
       </c>
       <c r="AM6" t="str">
-        <v>3h15m</v>
+        <v>35h30m</v>
       </c>
       <c r="AN6" s="1">
-        <v>46160.45247685185</v>
+        <v>46202.477858796294</v>
       </c>
       <c r="AP6" s="1">
-        <v>46436.45208333333</v>
+        <v>46475.620833333334</v>
       </c>
       <c r="AU6" s="1">
-        <v>46112.42569444444</v>
+        <v>46175.65555555555</v>
       </c>
       <c r="AV6" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Lille Sud</v>
       </c>
       <c r="AW6" t="str">
-        <v>Jeanine GORNIAK</v>
+        <v>Séverine LIATARD</v>
       </c>
       <c r="AX6" s="1">
-        <v>46112.427083333336</v>
+        <v>46174.657638888886</v>
       </c>
       <c r="AY6" t="str">
-        <v>j.gorniak@lilleavenirs.fr</v>
+        <v>s.liatard@lilleavenirs.fr</v>
       </c>
       <c r="BA6" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB6" t="str">
+        <v>EL MAACH</v>
+      </c>
+      <c r="BC6" t="str">
+        <v>Latifa</v>
+      </c>
+      <c r="BD6" t="str">
+        <v>3/2 RUE DE LA LOIRE 59000 LILLE</v>
+      </c>
+      <c r="BE6" t="str">
+        <v>0782785384</v>
+      </c>
+      <c r="BF6" t="str">
+        <v>latifamaroco@gmail.com</v>
       </c>
       <c r="BG6" t="str">
-        <v>16882</v>
-      </c>
-      <c r="BH6" s="1">
-        <v>46127.083333333336</v>
-      </c>
-      <c r="BI6" t="str">
-        <v>5993365C</v>
+        <v>19449</v>
       </c>
       <c r="BJ6" t="str">
-        <v>a359a10c-5f41-4974-8cc7-60aa52868aef</v>
+        <v>17f38324-ad75-4a05-ac69-8e2e56ed95b3</v>
       </c>
       <c r="BK6" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL6" t="str">
         <v/>
       </c>
       <c r="BM6" t="str">
-        <v>isaacautem@gmail.com</v>
+        <v>salmaelmaach220@gmail.com</v>
       </c>
       <c r="BN6" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_elmaach_e2c-grandlille_fr/IgDyyyFDR_JPR48MY6fJRUeXAQAS4ZDmim3XRG7FNuBeS9M?e=UWO5in</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>134506</v>
+        <v>139279</v>
       </c>
       <c r="B7" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C7" t="str">
-        <v>VINCENT</v>
+        <v>DAVILA</v>
       </c>
       <c r="D7" t="str">
-        <v>Herinne</v>
+        <v>Roberto-Sebastian</v>
       </c>
       <c r="E7" t="str">
-        <v>h.vincent@e2c-grandlille.fr</v>
+        <v>r.davila@e2c-grandlille.fr</v>
       </c>
       <c r="F7" t="str">
-        <v>0665343855</v>
+        <v>0695346071</v>
       </c>
       <c r="G7" t="str">
         <v>Grand Lille</v>
@@ -1450,56 +1441,50 @@
       <c r="H7" t="str">
         <v>Lille</v>
       </c>
-      <c r="K7" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L7" t="str">
-        <v>référés Anne</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M7" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O7" t="str">
-        <v>CAPEAU Anne</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R7" s="1">
-        <v>39072</v>
+        <v>36768</v>
       </c>
       <c r="T7" t="str">
-        <v>SAINT SAULVE</v>
+        <v>AUBERVILLIER</v>
       </c>
       <c r="U7" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W7" t="str">
-        <v>7 Avenue Denis Cordonnier</v>
+        <v>503 Avenue de la République</v>
       </c>
       <c r="X7" t="str">
-        <v>59000</v>
+        <v>59700</v>
       </c>
       <c r="Y7" t="str">
-        <v>Lille</v>
+        <v>Marcq-en-Barœul</v>
       </c>
       <c r="Z7" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>QN05972M</v>
+        <v>Non</v>
       </c>
       <c r="AB7" t="str">
         <v>Non</v>
       </c>
       <c r="AC7" t="str">
-        <v>NON</v>
+        <v>CEJ_FRANCE_TRAVAIL</v>
       </c>
       <c r="AD7" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE7" t="str">
         <v>Non</v>
@@ -1514,90 +1499,81 @@
         <v>Non</v>
       </c>
       <c r="AI7" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AJ7" t="str">
         <v>Non</v>
       </c>
       <c r="AK7" t="str">
-        <v>65h</v>
+        <v>71h</v>
       </c>
       <c r="AL7" t="str">
-        <v>0m</v>
+        <v>42h</v>
       </c>
       <c r="AM7" t="str">
-        <v>4h45m</v>
+        <v>13h</v>
       </c>
       <c r="AN7" s="1">
-        <v>46160.456608796296</v>
+        <v>46202.47692129629</v>
       </c>
       <c r="AP7" s="1">
-        <v>46436.45625</v>
+        <v>46475.61319444444</v>
       </c>
       <c r="AU7" s="1">
-        <v>46112.46041666667</v>
+        <v>46154.6375</v>
       </c>
       <c r="AV7" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
-      </c>
-      <c r="AW7" t="str">
-        <v>Quentin ROUSSELLE</v>
+        <v>En direct</v>
       </c>
       <c r="AX7" s="1">
-        <v>46104.461805555555</v>
-      </c>
-      <c r="AY7" t="str">
-        <v>q.rousselle@lilleavenirs.fr</v>
-      </c>
-      <c r="AZ7" t="str">
-        <v>0760819934</v>
+        <v>46154.63958333333</v>
       </c>
       <c r="BA7" t="str">
         <v>NON</v>
       </c>
       <c r="BG7" t="str">
-        <v>16898</v>
+        <v>19447</v>
       </c>
       <c r="BH7" s="1">
-        <v>46008.041666666664</v>
+        <v>46202.083333333336</v>
       </c>
       <c r="BI7" t="str">
-        <v>5781604C</v>
+        <v>5822340F</v>
       </c>
       <c r="BJ7" t="str">
-        <v>61ec72c2-3179-4281-8609-1d188b7d770f</v>
+        <v>981469d2-b38e-4755-95d8-9a67ec58cee1</v>
       </c>
       <c r="BK7" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL7" t="str">
         <v/>
       </c>
       <c r="BM7" t="str">
-        <v>herinnevincent@gmail.com</v>
+        <v>robertosebastian3008@gmail.com</v>
       </c>
       <c r="BN7" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_davila_e2c-grandlille_fr/IgDZa7ET9ds5QaI4XDaHKkkpAcotnE1FgiGyoaOE5wYlNPA?e=3vS2VA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>134482</v>
+        <v>139248</v>
       </c>
       <c r="B8" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C8" t="str">
-        <v>MALET</v>
+        <v>MALIK</v>
       </c>
       <c r="D8" t="str">
-        <v>Alexis</v>
+        <v>Rafia</v>
       </c>
       <c r="E8" t="str">
-        <v>a.malet@e2c-grandlille.fr</v>
+        <v>r.malik@e2c-grandlille.fr</v>
       </c>
       <c r="F8" t="str">
-        <v>0635319097</v>
+        <v>0669252280</v>
       </c>
       <c r="G8" t="str">
         <v>Grand Lille</v>
@@ -1605,26 +1581,29 @@
       <c r="H8" t="str">
         <v>Lille</v>
       </c>
+      <c r="I8" t="str">
+        <v>Animateur / Animatrice d'accueil de loisirs (centre de loisirs), Secrétaire médical / Secrétaire médicale</v>
+      </c>
       <c r="K8" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L8" t="str">
-        <v>référés Lucie</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M8" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O8" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R8" s="1">
-        <v>37280</v>
+        <v>38886</v>
       </c>
       <c r="T8" t="str">
         <v>LILLE</v>
@@ -1633,13 +1612,13 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W8" t="str">
-        <v>32 Rue Gambetta</v>
+        <v>21 Rue des Hautes Voies</v>
       </c>
       <c r="X8" t="str">
-        <v>59110</v>
+        <v>59700</v>
       </c>
       <c r="Y8" t="str">
-        <v>La Madeleine</v>
+        <v>Marcq-en-Barœul</v>
       </c>
       <c r="Z8" t="str">
         <v>Non</v>
@@ -1648,10 +1627,10 @@
         <v>Non</v>
       </c>
       <c r="AC8" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD8" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE8" t="str">
         <v>Non</v>
@@ -1660,7 +1639,7 @@
         <v>Non</v>
       </c>
       <c r="AG8" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH8" t="str">
         <v>Non</v>
@@ -1672,84 +1651,78 @@
         <v>Non</v>
       </c>
       <c r="AK8" t="str">
-        <v>74h</v>
+        <v>75h45m</v>
       </c>
       <c r="AL8" t="str">
-        <v>0m</v>
+        <v>35h</v>
       </c>
       <c r="AM8" t="str">
-        <v>3h15m</v>
+        <v>8h15m</v>
       </c>
       <c r="AN8" s="1">
-        <v>46160.45515046296</v>
+        <v>46202.47837962963</v>
       </c>
       <c r="AP8" s="1">
-        <v>46436.45486111111</v>
+        <v>46475.62569444445</v>
       </c>
       <c r="AU8" s="1">
-        <v>46105.41111111111</v>
+        <v>46147.603472222225</v>
       </c>
       <c r="AV8" t="str">
-        <v>FCP Secteur Atelier de Préformation</v>
+        <v>MISSION LOCALE MNO - Antenne de Marcq en Baroeul</v>
       </c>
       <c r="AW8" t="str">
-        <v>Christelle DEGROUX</v>
+        <v>Tiphaine DHALLUIN</v>
       </c>
       <c r="AX8" s="1">
-        <v>46099.413194444445</v>
-      </c>
-      <c r="AY8" t="str">
-        <v>cdegroux@fcp-asso.org</v>
-      </c>
-      <c r="AZ8" t="str">
-        <v>0685445606</v>
+        <v>46147.60625</v>
       </c>
       <c r="BA8" t="str">
         <v>NON</v>
       </c>
       <c r="BG8" t="str">
-        <v>16890</v>
+        <v>19451</v>
       </c>
       <c r="BH8" s="1">
-        <v>45641.041666666664</v>
+        <v>45771.083333333336</v>
       </c>
       <c r="BI8" t="str">
-        <v>5600137F</v>
+        <v>5904868K</v>
       </c>
       <c r="BJ8" t="str">
-        <v>52b2db28-1f2a-4db9-9f2b-8f41b7641b9c</v>
+        <v>75a16ca5-6006-4a31-a8d9-ab229ad593de</v>
       </c>
       <c r="BK8" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL8" t="str">
         <v/>
       </c>
       <c r="BM8" t="str">
-        <v>alexis.malet1992@gmail.com</v>
+        <v>rmk94r@gmail.com</v>
       </c>
       <c r="BN8" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_malik_e2c-grandlille_fr/IgAe9raOfCKaQoihRMtEg2nnAVHS49DzQRurh8wZWyEKcSM?e=4Pok17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>134435</v>
+        <v>137330</v>
       </c>
       <c r="B9" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C9" t="str">
-        <v>LARGERSIE</v>
+        <v>SOUARE</v>
       </c>
       <c r="D9" t="str">
-        <v>Timéo</v>
+        <v>Tate</v>
       </c>
       <c r="E9" t="str">
-        <v>t.lagersie@e2c-grandlille.fr</v>
+        <v>t.souare@e2c-grandlille.fr</v>
       </c>
       <c r="F9" t="str">
-        <v>0749766566</v>
+        <v>0759783030</v>
       </c>
       <c r="G9" t="str">
         <v>Grand Lille</v>
@@ -1757,47 +1730,44 @@
       <c r="H9" t="str">
         <v>Lille</v>
       </c>
-      <c r="I9" t="str">
-        <v>Cuisinier / Cuisinière</v>
-      </c>
-      <c r="K9" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L9" t="str">
-        <v>référés Camille</v>
+        <v>référés Sura</v>
       </c>
       <c r="M9" t="str">
-        <v>2605/mai 2026 LIL</v>
+        <v>2606/juin 2026 LIL</v>
       </c>
       <c r="O9" t="str">
-        <v>PEAU Camille</v>
+        <v>JAMIL HUSSAIN Sura</v>
       </c>
       <c r="P9">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q9">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R9" s="1">
-        <v>39976</v>
+        <v>38131</v>
       </c>
       <c r="T9" t="str">
-        <v>VILLENEUVE D'ASCQ</v>
+        <v>LILLE</v>
       </c>
       <c r="U9" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W9" t="str">
-        <v>541 Rue Anatole France</v>
+        <v>13 Rue Jules Breton</v>
       </c>
       <c r="X9" t="str">
-        <v>59162</v>
+        <v>59000</v>
       </c>
       <c r="Y9" t="str">
-        <v>Ostricourt</v>
+        <v>Lille</v>
       </c>
       <c r="Z9" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>QN05972M</v>
       </c>
       <c r="AB9" t="str">
         <v>Non</v>
@@ -1806,7 +1776,7 @@
         <v>NON</v>
       </c>
       <c r="AD9" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE9" t="str">
         <v>Non</v>
@@ -1827,84 +1797,75 @@
         <v>Non</v>
       </c>
       <c r="AK9" t="str">
-        <v>67h45m</v>
+        <v>64h30m</v>
       </c>
       <c r="AL9" t="str">
-        <v>0m</v>
+        <v>20h</v>
       </c>
       <c r="AM9" t="str">
-        <v>6h30m</v>
+        <v>22h45m</v>
       </c>
       <c r="AN9" s="1">
-        <v>46160.45482638889</v>
+        <v>46202.48024305556</v>
       </c>
       <c r="AP9" s="1">
-        <v>46436.45416666667</v>
+        <v>46475.479166666664</v>
       </c>
       <c r="AU9" s="1">
-        <v>46098.66875</v>
+        <v>46140.436111111114</v>
       </c>
       <c r="AV9" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne d'Ostricourt</v>
+        <v>FRANCE TRAVAIL - Lille Grand Sud</v>
       </c>
       <c r="AX9" s="1">
-        <v>46098.67013888889</v>
+        <v>46140.4375</v>
       </c>
       <c r="BA9" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB9" t="str">
-        <v>LAGERSIE</v>
-      </c>
-      <c r="BC9" t="str">
-        <v>Julien</v>
-      </c>
-      <c r="BD9" t="str">
-        <v>541 RUE ANATOLE FRANCE 59162 OSTRICOURT</v>
-      </c>
-      <c r="BE9" t="str">
-        <v>0749724416</v>
-      </c>
-      <c r="BF9" t="str">
-        <v>julienlagersie@hotmail.com</v>
+        <v>NON</v>
       </c>
       <c r="BG9" t="str">
-        <v>16889</v>
+        <v>19457</v>
+      </c>
+      <c r="BH9" s="1">
+        <v>45786.083333333336</v>
+      </c>
+      <c r="BI9" t="str">
+        <v>5757958A</v>
       </c>
       <c r="BJ9" t="str">
-        <v>b22c2569-cc09-49de-861d-8642f0af0773</v>
+        <v>4eb36f37-288b-46a4-bf8d-c0860cb7bb5e</v>
       </c>
       <c r="BK9" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL9" t="str">
         <v/>
       </c>
       <c r="BM9" t="str">
-        <v>timeolagersie@gmail.com</v>
+        <v>tatesouare59@gmail.com</v>
       </c>
       <c r="BN9" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_souare_e2c-grandlille_fr/IgCc60O2-3PERb09GSEETMvQAbtjTPvq9qSS4equqmzSdF8?e=xuMzxf</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>134433</v>
+        <v>136959</v>
       </c>
       <c r="B10" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C10" t="str">
-        <v>VANEECKHOUTTE</v>
+        <v>ALI</v>
       </c>
       <c r="D10" t="str">
-        <v>Agathe</v>
+        <v>Ilyas</v>
       </c>
       <c r="E10" t="str">
-        <v>a.vaneeckhoutte@e2c-grandlille.fr</v>
+        <v>i.ali@e2c-grandlille.fr</v>
       </c>
       <c r="F10" t="str">
-        <v>0778403411</v>
+        <v>0744977269</v>
       </c>
       <c r="G10" t="str">
         <v>Grand Lille</v>
@@ -1912,38 +1873,35 @@
       <c r="H10" t="str">
         <v>Lille</v>
       </c>
-      <c r="I10" t="str">
-        <v>Agent / Agente de sécurité, Esthéticien-manucure / Esthéticienne-manucure, Hôte / Hôtesse de caisse</v>
-      </c>
       <c r="K10" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L10" t="str">
-        <v>référés German</v>
+        <v>référés Anne</v>
       </c>
       <c r="M10" t="str">
         <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O10" t="str">
-        <v>LEON QUERO German</v>
+        <v>CAPEAU Anne</v>
       </c>
       <c r="P10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R10" s="1">
-        <v>38712</v>
+        <v>37610</v>
       </c>
       <c r="T10" t="str">
-        <v>ROUBAIX</v>
+        <v>KOLYOLEY (SOMALIE)</v>
       </c>
       <c r="U10" t="str">
-        <v>FRANCAISE</v>
+        <v>AUTRE</v>
       </c>
       <c r="W10" t="str">
-        <v>16 Allee des Foyers</v>
+        <v>33 Chemin des Visiteurs</v>
       </c>
       <c r="X10" t="str">
         <v>59650</v>
@@ -1952,16 +1910,19 @@
         <v>Villeneuve-d'Ascq</v>
       </c>
       <c r="Z10" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>QN05965M</v>
       </c>
       <c r="AB10" t="str">
         <v>Non</v>
       </c>
       <c r="AC10" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD10" t="str">
-        <v>3 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE10" t="str">
         <v>Non</v>
@@ -1982,78 +1943,81 @@
         <v>Non</v>
       </c>
       <c r="AK10" t="str">
-        <v>67h45m</v>
+        <v>203h30m</v>
       </c>
       <c r="AL10" t="str">
-        <v>0m</v>
+        <v>105h</v>
       </c>
       <c r="AM10" t="str">
-        <v>6h30m</v>
+        <v>3h15m</v>
       </c>
       <c r="AN10" s="1">
-        <v>46160.456296296295</v>
+        <v>46160.44532407408</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>46203.42986111111</v>
       </c>
       <c r="AP10" s="1">
-        <v>46436.455555555556</v>
+        <v>46436.44375</v>
       </c>
       <c r="AU10" s="1">
-        <v>46098.66388888889</v>
+        <v>46133.67013888889</v>
       </c>
       <c r="AV10" t="str">
-        <v>Mission Locale de l'Artois - Antenne de Béthune</v>
+        <v>MISSION LOCALE MÉTROPOLE EST - Antenne de Villeneuve d'Ascq</v>
       </c>
       <c r="AW10" t="str">
-        <v>Jordan TAFFIN</v>
+        <v>Rachel TILIER</v>
       </c>
       <c r="AX10" s="1">
-        <v>46093.666666666664</v>
-      </c>
-      <c r="AY10" t="str">
-        <v>jordan.taffin@mlartois.org</v>
-      </c>
-      <c r="AZ10" t="str">
-        <v>0321644940</v>
+        <v>46111.675</v>
       </c>
       <c r="BA10" t="str">
         <v>NON</v>
       </c>
       <c r="BG10" t="str">
-        <v>16895</v>
+        <v>16881</v>
+      </c>
+      <c r="BH10" s="1">
+        <v>45950.083333333336</v>
+      </c>
+      <c r="BI10" t="str">
+        <v>5954620N</v>
       </c>
       <c r="BJ10" t="str">
-        <v>91a62049-439f-4bf7-8ad8-9f5a1a1615d6</v>
+        <v>5d2e3311-ed98-4b42-b7a9-5715f1406f2f</v>
       </c>
       <c r="BK10" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL10" t="str">
         <v/>
       </c>
       <c r="BM10" t="str">
-        <v>agathe.vaneeckhoutte@gmail.com</v>
+        <v>ilyasmahamoudo7@outlook.com</v>
       </c>
       <c r="BN10" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/i_ali_e2c-grandlille_fr/IgAkP9qjH5k9T5g8-GrA7duXAaUlZNLG__vx9vsdHr84haw?e=1DglNe</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>134425</v>
+        <v>136511</v>
       </c>
       <c r="B11" t="str">
         <v>Femme</v>
       </c>
       <c r="C11" t="str">
-        <v>BELINE</v>
+        <v>FERDI</v>
       </c>
       <c r="D11" t="str">
-        <v>Emma</v>
+        <v>Sofia</v>
       </c>
       <c r="E11" t="str">
-        <v>e.beline@e2c-grandlille.fr</v>
+        <v>s.ferdi@e2c-grandlille.fr</v>
       </c>
       <c r="F11" t="str">
-        <v>0760632298</v>
+        <v>0636134787</v>
       </c>
       <c r="G11" t="str">
         <v>Grand Lille</v>
@@ -2062,35 +2026,44 @@
         <v>Lille</v>
       </c>
       <c r="I11" t="str">
-        <v>Cuisinier / Cuisinière</v>
+        <v>Moniteur éducateur / Monitrice éducatrice</v>
       </c>
       <c r="K11" t="str">
-        <v>Je sais</v>
+        <v>J'explore</v>
       </c>
       <c r="L11" t="str">
-        <v>référés Sura</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M11" t="str">
         <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O11" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R11" s="1">
-        <v>39739</v>
+        <v>39482</v>
       </c>
       <c r="T11" t="str">
-        <v>LILLE</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U11" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="W11" t="str">
+        <v>647 Rue du Bazinghien</v>
+      </c>
+      <c r="X11" t="str">
+        <v>59120</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Loos</v>
+      </c>
       <c r="Z11" t="str">
         <v>Non</v>
       </c>
@@ -2098,7 +2071,7 @@
         <v>Non</v>
       </c>
       <c r="AC11" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD11" t="str">
         <v>Infra 3</v>
@@ -2116,93 +2089,84 @@
         <v>Non</v>
       </c>
       <c r="AI11" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AJ11" t="str">
         <v>Non</v>
       </c>
       <c r="AK11" t="str">
-        <v>66h15m</v>
+        <v>130h45m</v>
       </c>
       <c r="AL11" t="str">
-        <v>0m</v>
+        <v>48h</v>
       </c>
       <c r="AM11" t="str">
-        <v>13h</v>
+        <v>79h</v>
       </c>
       <c r="AN11" s="1">
-        <v>46160.4531712963</v>
+        <v>46160.454050925924</v>
       </c>
       <c r="AP11" s="1">
-        <v>46436.45277777778</v>
+        <v>46436.45347222222</v>
       </c>
       <c r="AU11" s="1">
-        <v>46098.64722222222</v>
+        <v>46133.635416666664</v>
       </c>
       <c r="AV11" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne de Loos-</v>
+        <v>LES APPRENTIS D'AUTEUIL - Loos</v>
       </c>
       <c r="AW11" t="str">
-        <v>Madame BUYSSCHAERT</v>
+        <v>Audrey DAVOINE</v>
       </c>
       <c r="AX11" s="1">
-        <v>46098.65</v>
+        <v>46128.63680555556</v>
+      </c>
+      <c r="AY11" t="str">
+        <v>audrey.davoine@apprentis-auteuil.org</v>
+      </c>
+      <c r="AZ11" t="str">
+        <v>0669912158</v>
       </c>
       <c r="BA11" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB11" t="str">
-        <v>CARLIER</v>
-      </c>
-      <c r="BC11" t="str">
-        <v>Jessica</v>
-      </c>
-      <c r="BD11" t="str">
-        <v>1 AVENUE DE FLANDRE TOUR ILE DE FRANCE APPT 92 59120 LOOS</v>
-      </c>
-      <c r="BE11" t="str">
-        <v>0602684745</v>
-      </c>
-      <c r="BF11" t="str">
-        <v>jessica-carlier@live.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG11" t="str">
-        <v>16941</v>
+        <v>16886</v>
       </c>
       <c r="BJ11" t="str">
-        <v>78855ef5-2bd3-4552-b672-3fa77f274033</v>
+        <v>3c282c36-3b0d-43e9-8473-ecdc2269a7c6</v>
       </c>
       <c r="BK11" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL11" t="str">
         <v/>
       </c>
       <c r="BM11" t="str">
-        <v>belineemma5@gmail.com</v>
+        <v>fbaiou87@gmail.com</v>
       </c>
       <c r="BN11" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_ferdi_e2c-grandlille_fr/IgD12rXE366-Sr1TufzV4GumAWgcEtMRhY1pSpb82THiS38?e=JlulVa</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>101419</v>
+        <v>135154</v>
       </c>
       <c r="B12" t="str">
         <v>Femme</v>
       </c>
       <c r="C12" t="str">
-        <v>NEVE SCHRYVE</v>
+        <v>DESREUMAUX</v>
       </c>
       <c r="D12" t="str">
-        <v>Liléa</v>
+        <v>Rachel</v>
       </c>
       <c r="E12" t="str">
-        <v>l.neveschryve@e2c-grandlille.fr</v>
+        <v>r.desreumaux@e2c-grandlille.fr</v>
       </c>
       <c r="F12" t="str">
-        <v>0782538960</v>
+        <v>0749417478</v>
       </c>
       <c r="G12" t="str">
         <v>Grand Lille</v>
@@ -2210,41 +2174,41 @@
       <c r="H12" t="str">
         <v>Lille</v>
       </c>
+      <c r="I12" t="str">
+        <v>Secrétaire bureautique, Serveur / Serveuse en restauration, Animateur / Animatrice petite enfance</v>
+      </c>
       <c r="K12" t="str">
-        <v>J'explore</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L12" t="str">
-        <v>référés Fanny</v>
+        <v>référés Camille</v>
       </c>
       <c r="M12" t="str">
         <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O12" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>PEAU Camille</v>
       </c>
       <c r="P12">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q12">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R12" s="1">
-        <v>37535</v>
+        <v>39437</v>
       </c>
       <c r="T12" t="str">
-        <v>LYON 7ème</v>
+        <v>ARMENTIERES</v>
       </c>
       <c r="U12" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="W12" t="str">
-        <v>874 Rue de Gonnehem</v>
-      </c>
       <c r="X12" t="str">
-        <v>62920</v>
+        <v>59120</v>
       </c>
       <c r="Y12" t="str">
-        <v>Chocques</v>
+        <v>Loos</v>
       </c>
       <c r="Z12" t="str">
         <v>Non</v>
@@ -2256,7 +2220,7 @@
         <v>NON</v>
       </c>
       <c r="AD12" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE12" t="str">
         <v>Non</v>
@@ -2265,7 +2229,7 @@
         <v>Non</v>
       </c>
       <c r="AG12" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH12" t="str">
         <v>Non</v>
@@ -2277,75 +2241,75 @@
         <v>Non</v>
       </c>
       <c r="AK12" t="str">
-        <v>63h15m</v>
+        <v>193h45m</v>
       </c>
       <c r="AL12" t="str">
-        <v>0m</v>
+        <v>70h</v>
       </c>
       <c r="AM12" t="str">
-        <v>6h30m</v>
+        <v>16h</v>
       </c>
       <c r="AN12" s="1">
-        <v>46160.45591435185</v>
+        <v>46160.45359953704</v>
       </c>
       <c r="AP12" s="1">
-        <v>46436.455555555556</v>
+        <v>46436.45277777778</v>
       </c>
       <c r="AU12" s="1">
-        <v>46091.65694444445</v>
+        <v>46119.68958333333</v>
       </c>
       <c r="AV12" t="str">
         <v>En direct</v>
       </c>
       <c r="AX12" s="1">
-        <v>46091.65833333333</v>
+        <v>46113.69027777778</v>
       </c>
       <c r="BA12" t="str">
         <v>NON</v>
       </c>
       <c r="BG12" t="str">
-        <v>16911</v>
+        <v>16885</v>
       </c>
       <c r="BH12" s="1">
-        <v>45687.041666666664</v>
+        <v>46091.041666666664</v>
       </c>
       <c r="BI12" t="str">
-        <v>1664877Z</v>
+        <v>5983301N</v>
       </c>
       <c r="BJ12" t="str">
-        <v>0946fb10-e8c6-458b-8a30-ce449aee830f</v>
+        <v>883c92ed-d293-42f2-b674-981abd97c3b4</v>
       </c>
       <c r="BK12" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL12" t="str">
         <v/>
       </c>
       <c r="BM12" t="str">
-        <v>lilea.neveschryve@protommail.com</v>
+        <v>desreumauxrachel0@gmail.com</v>
       </c>
       <c r="BN12" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_desreumaux_e2c-grandlille_fr/IgAF3IM8u_veSp8aqRxUDcR1AVgao1mCZwuFB1xA1Sg_SBo?e=GIRQ4N</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>101329</v>
+        <v>134990</v>
       </c>
       <c r="B13" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C13" t="str">
-        <v>POUILLY</v>
+        <v>AUTEM</v>
       </c>
       <c r="D13" t="str">
-        <v>Melinda</v>
+        <v>Isaac</v>
       </c>
       <c r="E13" t="str">
-        <v>m.pouilly@e2c-grandlille.fr</v>
+        <v>i.autem@e2c-grandlille.fr</v>
       </c>
       <c r="F13" t="str">
-        <v>0666505782</v>
+        <v>0767281621</v>
       </c>
       <c r="G13" t="str">
         <v>Grand Lille</v>
@@ -2357,37 +2321,43 @@
         <v>J'ai des idées</v>
       </c>
       <c r="L13" t="str">
-        <v>référés German</v>
+        <v>référés Anne</v>
       </c>
       <c r="M13" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O13" t="str">
-        <v>LEON QUERO German</v>
+        <v>CAPEAU Anne</v>
       </c>
       <c r="P13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R13" s="1">
-        <v>40074</v>
+        <v>38713</v>
       </c>
       <c r="T13" t="str">
-        <v>LILLE</v>
+        <v>ARRAS</v>
       </c>
       <c r="U13" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="W13" t="str">
+        <v>47 Rue Pascal</v>
+      </c>
       <c r="X13" t="str">
-        <v>59700</v>
+        <v>59800</v>
       </c>
       <c r="Y13" t="str">
-        <v>Marcq-en-Barœul</v>
+        <v>Lille</v>
       </c>
       <c r="Z13" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>QN05973M</v>
       </c>
       <c r="AB13" t="str">
         <v>Non</v>
@@ -2396,7 +2366,7 @@
         <v>NON</v>
       </c>
       <c r="AD13" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE13" t="str">
         <v>Non</v>
@@ -2417,55 +2387,52 @@
         <v>Non</v>
       </c>
       <c r="AK13" t="str">
-        <v>123h15m</v>
+        <v>166h30m</v>
       </c>
       <c r="AL13" t="str">
-        <v>119h</v>
+        <v>98h</v>
       </c>
       <c r="AM13" t="str">
-        <v>9h45m</v>
+        <v>40h</v>
       </c>
       <c r="AN13" s="1">
-        <v>46125.594988425924</v>
+        <v>46160.45247685185</v>
       </c>
       <c r="AO13" s="1">
-        <v>46168.50486111111</v>
+        <v>46203.43541666667</v>
       </c>
       <c r="AP13" s="1">
-        <v>46400.70625</v>
+        <v>46436.45208333333</v>
       </c>
       <c r="AU13" s="1">
-        <v>46091.643055555556</v>
+        <v>46112.42569444444</v>
       </c>
       <c r="AV13" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
+      </c>
+      <c r="AW13" t="str">
+        <v>Jeanine GORNIAK</v>
       </c>
       <c r="AX13" s="1">
-        <v>46091.64513888889</v>
+        <v>46112.427083333336</v>
+      </c>
+      <c r="AY13" t="str">
+        <v>j.gorniak@lilleavenirs.fr</v>
       </c>
       <c r="BA13" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB13" t="str">
-        <v>POUILLY</v>
-      </c>
-      <c r="BC13" t="str">
-        <v>Cathy</v>
-      </c>
-      <c r="BD13" t="str">
-        <v>11/37 RUE DES COTONNIERS 59700 MARCQ EN BAROEUL</v>
-      </c>
-      <c r="BE13" t="str">
-        <v>0611333451</v>
-      </c>
-      <c r="BF13" t="str">
-        <v>doudoune0503@hotmail.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG13" t="str">
-        <v>14739</v>
+        <v>16882</v>
+      </c>
+      <c r="BH13" s="1">
+        <v>46127.083333333336</v>
+      </c>
+      <c r="BI13" t="str">
+        <v>5993365C</v>
       </c>
       <c r="BJ13" t="str">
-        <v>1fbec1cf-3329-4450-bea5-67aa89defa9c</v>
+        <v>a359a10c-5f41-4974-8cc7-60aa52868aef</v>
       </c>
       <c r="BK13" t="str">
         <v>Accepted</v>
@@ -2474,30 +2441,30 @@
         <v/>
       </c>
       <c r="BM13" t="str">
-        <v>melinapouilly@icloud.com</v>
+        <v>isaacautem@gmail.com</v>
       </c>
       <c r="BN13" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_pouilly_e2c-grandlille_fr/IgBclX72W74AR49rnexSyw7eARxVfuu3ou_99kHz4Hpc768?e=6cnrWP</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/i_autem_e2c-grandlille_fr/IgAJx9Ye7-zTTpUlbqMcN_MiAcD8qLBz5zM633cFb-c7Iyw?e=nH7n8c</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>101157</v>
+        <v>134506</v>
       </c>
       <c r="B14" t="str">
         <v>Femme</v>
       </c>
       <c r="C14" t="str">
-        <v>ROUSSEL</v>
+        <v>VINCENT</v>
       </c>
       <c r="D14" t="str">
-        <v>Sophia</v>
+        <v>Herinne</v>
       </c>
       <c r="E14" t="str">
-        <v>s.roussel@e2c-grandlille.fr</v>
+        <v>h.vincent@e2c-grandlille.fr</v>
       </c>
       <c r="F14" t="str">
-        <v>0768373343</v>
+        <v>0665343855</v>
       </c>
       <c r="G14" t="str">
         <v>Grand Lille</v>
@@ -2505,47 +2472,47 @@
       <c r="H14" t="str">
         <v>Lille</v>
       </c>
-      <c r="I14" t="str">
-        <v>Enseignant / Enseignante des écoles, Coach sportif, Professeur / Professeure d'éducation physique et sportive (EPS)</v>
-      </c>
       <c r="K14" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L14" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés Anne</v>
       </c>
       <c r="M14" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O14" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>CAPEAU Anne</v>
       </c>
       <c r="P14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R14" s="1">
-        <v>39352</v>
+        <v>39072</v>
       </c>
       <c r="T14" t="str">
-        <v>DIJON</v>
+        <v>SAINT SAULVE</v>
       </c>
       <c r="U14" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W14" t="str">
-        <v>66 Rue Jean Bart (Hellemmes)</v>
+        <v>7 Avenue Denis Cordonnier</v>
       </c>
       <c r="X14" t="str">
-        <v>59260</v>
+        <v>59000</v>
       </c>
       <c r="Y14" t="str">
         <v>Lille</v>
       </c>
       <c r="Z14" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>QN05972M</v>
       </c>
       <c r="AB14" t="str">
         <v>Non</v>
@@ -2554,7 +2521,7 @@
         <v>NON</v>
       </c>
       <c r="AD14" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE14" t="str">
         <v>Non</v>
@@ -2569,61 +2536,58 @@
         <v>Non</v>
       </c>
       <c r="AI14" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AJ14" t="str">
         <v>Non</v>
       </c>
       <c r="AK14" t="str">
-        <v>116h15m</v>
+        <v>80h45m</v>
       </c>
       <c r="AL14" t="str">
-        <v>84h</v>
+        <v>49h</v>
       </c>
       <c r="AM14" t="str">
-        <v>13h</v>
+        <v>127h30m</v>
       </c>
       <c r="AN14" s="1">
-        <v>46125.595289351855</v>
-      </c>
-      <c r="AO14" s="1">
-        <v>46168.50625</v>
+        <v>46160.456608796296</v>
       </c>
       <c r="AP14" s="1">
-        <v>46400.70347222222</v>
+        <v>46436.45625</v>
       </c>
       <c r="AU14" s="1">
-        <v>46091.61736111111</v>
+        <v>46112.46041666667</v>
       </c>
       <c r="AV14" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Hellemmes</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
       </c>
       <c r="AW14" t="str">
-        <v>Gwenaëlle GOETGHELUCK</v>
+        <v>Quentin ROUSSELLE</v>
       </c>
       <c r="AX14" s="1">
-        <v>46090.61944444444</v>
+        <v>46104.461805555555</v>
       </c>
       <c r="AY14" t="str">
-        <v>g.goetgheluck@lilleavenirs.fr</v>
+        <v>q.rousselle@lilleavenirs.fr</v>
       </c>
       <c r="AZ14" t="str">
-        <v>0762671622</v>
+        <v>0760819934</v>
       </c>
       <c r="BA14" t="str">
         <v>NON</v>
       </c>
       <c r="BG14" t="str">
-        <v>14741</v>
+        <v>16898</v>
       </c>
       <c r="BH14" s="1">
-        <v>46120.083333333336</v>
+        <v>46008.041666666664</v>
       </c>
       <c r="BI14" t="str">
-        <v>5991883S</v>
+        <v>5781604C</v>
       </c>
       <c r="BJ14" t="str">
-        <v>32f68e63-17ee-4ece-aae0-e884334779d2</v>
+        <v>61ec72c2-3179-4281-8609-1d188b7d770f</v>
       </c>
       <c r="BK14" t="str">
         <v>Accepted</v>
@@ -2632,30 +2596,30 @@
         <v/>
       </c>
       <c r="BM14" t="str">
-        <v>sophia.i.roussel2709@gmail.com</v>
+        <v>herinnevincent@gmail.com</v>
       </c>
       <c r="BN14" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_roussel_e2c-grandlille_fr/IgAIqpVHe2BLSoCyGbwDs7DXAd9CSnDXDxC5iCzRzjwBxgE?e=p9CZ7n</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/h_vincent_e2c-grandlille_fr/IgD1oO9dpldKTKTfrF4WXSm3ATrywiqzkg2ZC0n6NgdljsU?e=NxobKA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>101130</v>
+        <v>134482</v>
       </c>
       <c r="B15" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C15" t="str">
-        <v>BERTRAND</v>
+        <v>MALET</v>
       </c>
       <c r="D15" t="str">
-        <v>Ophélie</v>
+        <v>Alexis</v>
       </c>
       <c r="E15" t="str">
-        <v>o.bertrand@e2c-grandlille.fr</v>
+        <v>a.malet@e2c-grandlille.fr</v>
       </c>
       <c r="F15" t="str">
-        <v>0744558740</v>
+        <v>0635319097</v>
       </c>
       <c r="G15" t="str">
         <v>Grand Lille</v>
@@ -2664,46 +2628,43 @@
         <v>Lille</v>
       </c>
       <c r="I15" t="str">
-        <v>Psychologue-psychothérapeute, Préparateur / Préparatrice en pharmacie</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, CDI Intérimaire</v>
+        <v>Employé / Employée de libre-service</v>
       </c>
       <c r="K15" t="str">
         <v>Je sais</v>
       </c>
       <c r="L15" t="str">
-        <v>référés German</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M15" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O15" t="str">
-        <v>LEON QUERO German</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R15" s="1">
-        <v>38930</v>
+        <v>37280</v>
       </c>
       <c r="T15" t="str">
-        <v>CATEAU CAMBRESIS</v>
+        <v>LILLE</v>
       </c>
       <c r="U15" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W15" t="str">
-        <v>11 Rue Abélard</v>
+        <v>32 Rue Gambetta</v>
       </c>
       <c r="X15" t="str">
-        <v>59000</v>
+        <v>59110</v>
       </c>
       <c r="Y15" t="str">
-        <v>Lille</v>
+        <v>La Madeleine</v>
       </c>
       <c r="Z15" t="str">
         <v>Non</v>
@@ -2715,7 +2676,7 @@
         <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD15" t="str">
-        <v>4 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE15" t="str">
         <v>Non</v>
@@ -2724,52 +2685,67 @@
         <v>Non</v>
       </c>
       <c r="AG15" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH15" t="str">
         <v>Non</v>
       </c>
       <c r="AI15" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AJ15" t="str">
         <v>Non</v>
       </c>
       <c r="AK15" t="str">
-        <v>113h</v>
+        <v>190h30m</v>
       </c>
       <c r="AL15" t="str">
-        <v>84h</v>
+        <v>105h</v>
       </c>
       <c r="AM15" t="str">
         <v>16h15m</v>
       </c>
       <c r="AN15" s="1">
-        <v>46125.59216435185</v>
+        <v>46160.45515046296</v>
       </c>
       <c r="AO15" s="1">
-        <v>46168.498611111114</v>
+        <v>46203.43194444444</v>
       </c>
       <c r="AP15" s="1">
-        <v>46400.70486111111</v>
+        <v>46436.45486111111</v>
       </c>
       <c r="AU15" s="1">
-        <v>46091.61041666667</v>
+        <v>46105.41111111111</v>
       </c>
       <c r="AV15" t="str">
-        <v>En direct</v>
+        <v>FCP Secteur Atelier de Préformation</v>
+      </c>
+      <c r="AW15" t="str">
+        <v>Christelle DEGROUX</v>
       </c>
       <c r="AX15" s="1">
-        <v>46091.6125</v>
+        <v>46099.413194444445</v>
+      </c>
+      <c r="AY15" t="str">
+        <v>cdegroux@fcp-asso.org</v>
+      </c>
+      <c r="AZ15" t="str">
+        <v>0685445606</v>
       </c>
       <c r="BA15" t="str">
         <v>NON</v>
       </c>
       <c r="BG15" t="str">
-        <v>14723</v>
+        <v>16890</v>
+      </c>
+      <c r="BH15" s="1">
+        <v>45641.041666666664</v>
+      </c>
+      <c r="BI15" t="str">
+        <v>5600137F</v>
       </c>
       <c r="BJ15" t="str">
-        <v>09e12b15-255c-4c69-b300-2e6a87f62d03</v>
+        <v>52b2db28-1f2a-4db9-9f2b-8f41b7641b9c</v>
       </c>
       <c r="BK15" t="str">
         <v>Accepted</v>
@@ -2778,30 +2754,30 @@
         <v/>
       </c>
       <c r="BM15" t="str">
-        <v>bertrandophelie66@gmail.com</v>
+        <v>alexis.malet1992@gmail.com</v>
       </c>
       <c r="BN15" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/o_bertrand_e2c-grandlille_fr/IgCOa2wsa257Ra8oRlexayeJAW2ZBcynh3TVWf61snjQUCA?e=535Htf</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_malet_e2c-grandlille_fr/IgCwCLjJEYdqR4BAZIGK-E7EAckf9Nmc_1qq7Vom5IgfRDo?e=cxpBEf</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>83146</v>
+        <v>134435</v>
       </c>
       <c r="B16" t="str">
         <v>Homme</v>
       </c>
       <c r="C16" t="str">
-        <v>HENNETON</v>
+        <v>LARGERSIE</v>
       </c>
       <c r="D16" t="str">
-        <v>Pierrick</v>
+        <v>Timéo</v>
       </c>
       <c r="E16" t="str">
-        <v>p.henneton@e2c-grandlille.fr</v>
+        <v>t.lagersie@e2c-grandlille.fr</v>
       </c>
       <c r="F16" t="str">
-        <v>0643808541</v>
+        <v>0749766566</v>
       </c>
       <c r="G16" t="str">
         <v>Grand Lille</v>
@@ -2809,38 +2785,44 @@
       <c r="H16" t="str">
         <v>Lille</v>
       </c>
+      <c r="I16" t="str">
+        <v>Cuisinier / Cuisinière</v>
+      </c>
       <c r="K16" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L16" t="str">
-        <v>référés Fanny</v>
+        <v>référés Camille</v>
       </c>
       <c r="M16" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O16" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>PEAU Camille</v>
       </c>
       <c r="P16">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q16">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R16" s="1">
-        <v>37583</v>
+        <v>39976</v>
       </c>
       <c r="T16" t="str">
-        <v>LILLE</v>
+        <v>VILLENEUVE D'ASCQ</v>
+      </c>
+      <c r="U16" t="str">
+        <v>FRANCAISE</v>
       </c>
       <c r="W16" t="str">
-        <v>30 Rue du Buisson</v>
+        <v>541 Rue Anatole France</v>
       </c>
       <c r="X16" t="str">
-        <v>59800</v>
+        <v>59162</v>
       </c>
       <c r="Y16" t="str">
-        <v>Lille</v>
+        <v>Ostricourt</v>
       </c>
       <c r="Z16" t="str">
         <v>Non</v>
@@ -2852,7 +2834,7 @@
         <v>NON</v>
       </c>
       <c r="AD16" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE16" t="str">
         <v>Non</v>
@@ -2873,46 +2855,52 @@
         <v>Non</v>
       </c>
       <c r="AK16" t="str">
-        <v>95h15m</v>
+        <v>171h15m</v>
       </c>
       <c r="AL16" t="str">
-        <v>97h30m</v>
+        <v>98h</v>
       </c>
       <c r="AM16" t="str">
-        <v>32h30m</v>
+        <v>35h30m</v>
       </c>
       <c r="AN16" s="1">
-        <v>46125.593460648146</v>
-      </c>
-      <c r="AO16" s="1">
-        <v>46168.50277777778</v>
+        <v>46160.45482638889</v>
       </c>
       <c r="AP16" s="1">
-        <v>46400.70763888889</v>
+        <v>46436.45416666667</v>
       </c>
       <c r="AU16" s="1">
-        <v>46084.48333333333</v>
+        <v>46098.66875</v>
       </c>
       <c r="AV16" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Centre Ville</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne d'Ostricourt</v>
       </c>
       <c r="AX16" s="1">
-        <v>46080.48402777778</v>
+        <v>46098.67013888889</v>
       </c>
       <c r="BA16" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB16" t="str">
+        <v>LAGERSIE</v>
+      </c>
+      <c r="BC16" t="str">
+        <v>Julien</v>
+      </c>
+      <c r="BD16" t="str">
+        <v>541 RUE ANATOLE FRANCE 59162 OSTRICOURT</v>
+      </c>
+      <c r="BE16" t="str">
+        <v>0749724416</v>
+      </c>
+      <c r="BF16" t="str">
+        <v>julienlagersie@hotmail.com</v>
       </c>
       <c r="BG16" t="str">
-        <v>14732</v>
-      </c>
-      <c r="BH16" s="1">
-        <v>46024.041666666664</v>
-      </c>
-      <c r="BI16" t="str">
-        <v>5863777W</v>
+        <v>16889</v>
       </c>
       <c r="BJ16" t="str">
-        <v>2ef875c7-fdef-4992-a73d-cb3a14d9eedf</v>
+        <v>b22c2569-cc09-49de-861d-8642f0af0773</v>
       </c>
       <c r="BK16" t="str">
         <v>Accepted</v>
@@ -2921,30 +2909,30 @@
         <v/>
       </c>
       <c r="BM16" t="str">
-        <v>pierrickhenneton2311@gmail.com</v>
+        <v>timeolagersie@gmail.com</v>
       </c>
       <c r="BN16" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/p_henneton_e2c-grandlille_fr/IgDnbwVP4r6hSocjwhe2_owJASy_HPFxsOL3APPGJ5LH5uM?e=3z3wMR</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_lagersie_e2c-grandlille_fr/IgA8eMLumWGZRJUbf3nz6OB2Afp5cKjCqrzJmBsvd8tB7Mg?e=jgeInB</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>83143</v>
+        <v>134433</v>
       </c>
       <c r="B17" t="str">
         <v>Femme</v>
       </c>
       <c r="C17" t="str">
-        <v>ZOUTE</v>
+        <v>VANEECKHOUTTE</v>
       </c>
       <c r="D17" t="str">
-        <v>Sophie</v>
+        <v>Agathe</v>
       </c>
       <c r="E17" t="str">
-        <v>s.zoute@e2c-grandlille.fr</v>
+        <v>a.vaneeckhoutte@e2c-grandlille.fr</v>
       </c>
       <c r="F17" t="str">
-        <v>0601121601</v>
+        <v>0778403411</v>
       </c>
       <c r="G17" t="str">
         <v>Grand Lille</v>
@@ -2953,28 +2941,28 @@
         <v>Lille</v>
       </c>
       <c r="I17" t="str">
-        <v>Fleuriste</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
+        <v>Agent / Agente de sécurité, Esthéticien-manucure / Esthéticienne-manucure, Hôte / Hôtesse de caisse</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Je sais</v>
       </c>
       <c r="L17" t="str">
         <v>référés German</v>
       </c>
       <c r="M17" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O17" t="str">
         <v>LEON QUERO German</v>
       </c>
       <c r="P17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R17" s="1">
-        <v>39282</v>
+        <v>38712</v>
       </c>
       <c r="T17" t="str">
         <v>ROUBAIX</v>
@@ -2983,13 +2971,13 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W17" t="str">
-        <v>10 Allee des Tourelles</v>
+        <v>16 Allee des Foyers</v>
       </c>
       <c r="X17" t="str">
-        <v>59780</v>
+        <v>59650</v>
       </c>
       <c r="Y17" t="str">
-        <v>Willems</v>
+        <v>Villeneuve-d'Ascq</v>
       </c>
       <c r="Z17" t="str">
         <v>Non</v>
@@ -2998,10 +2986,10 @@
         <v>Non</v>
       </c>
       <c r="AC17" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD17" t="str">
-        <v>4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE17" t="str">
         <v>Non</v>
@@ -3022,46 +3010,46 @@
         <v>Non</v>
       </c>
       <c r="AK17" t="str">
-        <v>120h45m</v>
+        <v>177h45m</v>
       </c>
       <c r="AL17" t="str">
-        <v>28h</v>
+        <v>96h30m</v>
       </c>
       <c r="AM17" t="str">
-        <v>13h</v>
+        <v>29h</v>
       </c>
       <c r="AN17" s="1">
-        <v>46125.595601851855</v>
+        <v>46160.456296296295</v>
       </c>
       <c r="AP17" s="1">
-        <v>46400.705555555556</v>
+        <v>46436.455555555556</v>
       </c>
       <c r="AU17" s="1">
-        <v>46084.478472222225</v>
+        <v>46098.66388888889</v>
       </c>
       <c r="AV17" t="str">
-        <v>MISSION LOCALE MÉTROPOLE EST - Antenne de Villeneuve d'Ascq</v>
+        <v>Mission Locale de l'Artois - Antenne de Béthune</v>
       </c>
       <c r="AW17" t="str">
-        <v>Mathilde RULANCE</v>
+        <v>Jordan TAFFIN</v>
       </c>
       <c r="AX17" s="1">
-        <v>46084.47986111111</v>
+        <v>46093.666666666664</v>
+      </c>
+      <c r="AY17" t="str">
+        <v>jordan.taffin@mlartois.org</v>
+      </c>
+      <c r="AZ17" t="str">
+        <v>0321644940</v>
       </c>
       <c r="BA17" t="str">
         <v>NON</v>
       </c>
       <c r="BG17" t="str">
-        <v>14744</v>
-      </c>
-      <c r="BH17" s="1">
-        <v>46041.041666666664</v>
-      </c>
-      <c r="BI17" t="str">
-        <v>5975695W</v>
+        <v>16895</v>
       </c>
       <c r="BJ17" t="str">
-        <v>4add060d-a7d3-467b-93c0-9238f934cb95</v>
+        <v>91a62049-439f-4bf7-8ad8-9f5a1a1615d6</v>
       </c>
       <c r="BK17" t="str">
         <v>Accepted</v>
@@ -3070,30 +3058,30 @@
         <v/>
       </c>
       <c r="BM17" t="str">
-        <v>sophiezoute@gmail.com</v>
+        <v>agathe.vaneeckhoutte@gmail.com</v>
       </c>
       <c r="BN17" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_zoute_e2c-grandlille_fr/IgALGyPxWf-8RZtTdlsBSr6XAVIQx8ingPu3I2AsFmpx2z0?e=a3kQiP</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_vaneeckhoutte_e2c-grandlille_fr/IgCQseTjBwYjQLogjpnm9Jk-AeK9gPeWX50sV4gu93Z9lf0?e=1flJld</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>82674</v>
+        <v>134425</v>
       </c>
       <c r="B18" t="str">
         <v>Femme</v>
       </c>
       <c r="C18" t="str">
-        <v>AKOUGNI</v>
+        <v>BELINE</v>
       </c>
       <c r="D18" t="str">
-        <v>Germaine</v>
+        <v>Emma</v>
       </c>
       <c r="E18" t="str">
-        <v>g.akougni@e2c-grandlille.fr</v>
+        <v>e.beline@e2c-grandlille.fr</v>
       </c>
       <c r="F18" t="str">
-        <v>0648537574</v>
+        <v>06 99 19 33 49</v>
       </c>
       <c r="G18" t="str">
         <v>Grand Lille</v>
@@ -3101,53 +3089,59 @@
       <c r="H18" t="str">
         <v>Lille</v>
       </c>
+      <c r="I18" t="str">
+        <v>Cuisinier / Cuisinière</v>
+      </c>
       <c r="K18" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L18" t="str">
-        <v>référés Fanny</v>
+        <v>référés Sura</v>
       </c>
       <c r="M18" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O18" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>JAMIL HUSSAIN Sura</v>
       </c>
       <c r="P18">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q18">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R18" s="1">
-        <v>39183</v>
+        <v>39739</v>
       </c>
       <c r="T18" t="str">
-        <v>NOUMEA</v>
+        <v>LILLE</v>
       </c>
       <c r="U18" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W18" t="str">
-        <v>1 Rue de la Brasserie</v>
+        <v>1 Rue de Flandre</v>
       </c>
       <c r="X18" t="str">
-        <v>59790</v>
+        <v>59000</v>
       </c>
       <c r="Y18" t="str">
-        <v>Ronchin</v>
+        <v>Lille</v>
       </c>
       <c r="Z18" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>QN05972M</v>
       </c>
       <c r="AB18" t="str">
         <v>Non</v>
       </c>
       <c r="AC18" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD18" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE18" t="str">
         <v>Non</v>
@@ -3168,46 +3162,55 @@
         <v>Non</v>
       </c>
       <c r="AK18" t="str">
-        <v>109h30m</v>
+        <v>145h15m</v>
       </c>
       <c r="AL18" t="str">
-        <v>66h30m</v>
+        <v>71h</v>
       </c>
       <c r="AM18" t="str">
-        <v>19h30m</v>
+        <v>61h30m</v>
       </c>
       <c r="AN18" s="1">
-        <v>46125.58611111111</v>
-      </c>
-      <c r="AO18" s="1">
-        <v>46168.495833333334</v>
+        <v>46160.4531712963</v>
       </c>
       <c r="AP18" s="1">
-        <v>46400.70625</v>
+        <v>46436.45277777778</v>
       </c>
       <c r="AU18" s="1">
-        <v>46077.404861111114</v>
+        <v>46098.64722222222</v>
       </c>
       <c r="AV18" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne de Loos-</v>
+      </c>
+      <c r="AW18" t="str">
+        <v>Madame BUYSSCHAERT</v>
       </c>
       <c r="AX18" s="1">
-        <v>46077.40625</v>
+        <v>46098.65</v>
       </c>
       <c r="BA18" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB18" t="str">
+        <v>CARLIER</v>
+      </c>
+      <c r="BC18" t="str">
+        <v>Jessica</v>
+      </c>
+      <c r="BD18" t="str">
+        <v>1 AVENUE DE FLANDRE TOUR ILE DE FRANCE APPT 92 59120 LOOS</v>
+      </c>
+      <c r="BE18" t="str">
+        <v>0602684745</v>
+      </c>
+      <c r="BF18" t="str">
+        <v>jessica-carlier@live.fr</v>
       </c>
       <c r="BG18" t="str">
-        <v>14717</v>
-      </c>
-      <c r="BH18" s="1">
-        <v>45889.083333333336</v>
-      </c>
-      <c r="BI18" t="str">
-        <v>5928480A</v>
+        <v>16941</v>
       </c>
       <c r="BJ18" t="str">
-        <v>fe5352b3-71a5-498b-b965-d941e357a743</v>
+        <v>78855ef5-2bd3-4552-b672-3fa77f274033</v>
       </c>
       <c r="BK18" t="str">
         <v>Accepted</v>
@@ -3216,30 +3219,30 @@
         <v/>
       </c>
       <c r="BM18" t="str">
-        <v>akougnigermaine@gmail.com</v>
+        <v>belineemma5@gmail.com</v>
       </c>
       <c r="BN18" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/g_akougni_e2c-grandlille_fr/IgCBBCBHbn0pR5R2Xl45gfLNAV5MmW4Q4kTp8enccFMP3wM?e=Ik47Ae</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_beline_e2c-grandlille_fr/IgCfXV6esvBuQKqw0BZNaCrDAZ0iIZZ--3eP0roLN7OYW_A?e=mC9Vj3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>82115</v>
+        <v>101419</v>
       </c>
       <c r="B19" t="str">
         <v>Femme</v>
       </c>
       <c r="C19" t="str">
-        <v>LACQUEMENT</v>
+        <v>NEVE SCHRYVE</v>
       </c>
       <c r="D19" t="str">
-        <v>Laura</v>
+        <v>Liléa</v>
       </c>
       <c r="E19" t="str">
-        <v>l.lacquement@e2c-grandlille.fr</v>
+        <v>l.neveschryve@e2c-grandlille.fr</v>
       </c>
       <c r="F19" t="str">
-        <v>0614401952</v>
+        <v>0782538960</v>
       </c>
       <c r="G19" t="str">
         <v>Grand Lille</v>
@@ -3248,43 +3251,43 @@
         <v>Lille</v>
       </c>
       <c r="I19" t="str">
-        <v>Esthéticien / Esthéticienne</v>
+        <v>Ecrivain public / Ecrivaine publique, Animateur coordinateur socioculturel / Animatrice coordinatrice socioculturelle</v>
       </c>
       <c r="K19" t="str">
-        <v>Je sais</v>
+        <v>J'explore</v>
       </c>
       <c r="L19" t="str">
-        <v>référés Sura</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M19" t="str">
-        <v>2604/avril 2026 LIL</v>
+        <v>2605/mai 2026 LIL</v>
       </c>
       <c r="O19" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R19" s="1">
-        <v>39759</v>
+        <v>37535</v>
       </c>
       <c r="T19" t="str">
-        <v>LILLE</v>
+        <v>LYON 7ème</v>
       </c>
       <c r="U19" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W19" t="str">
-        <v>332 Rue Jean-baptiste Lebas</v>
+        <v>874 Rue de Gonnehem</v>
       </c>
       <c r="X19" t="str">
-        <v>59830</v>
+        <v>62920</v>
       </c>
       <c r="Y19" t="str">
-        <v>Cysoing</v>
+        <v>Chocques</v>
       </c>
       <c r="Z19" t="str">
         <v>Non</v>
@@ -3293,10 +3296,10 @@
         <v>Non</v>
       </c>
       <c r="AC19" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD19" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE19" t="str">
         <v>Non</v>
@@ -3305,7 +3308,7 @@
         <v>Non</v>
       </c>
       <c r="AG19" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH19" t="str">
         <v>Non</v>
@@ -3317,67 +3320,46 @@
         <v>Non</v>
       </c>
       <c r="AK19" t="str">
-        <v>61h30m</v>
+        <v>161h15m</v>
       </c>
       <c r="AL19" t="str">
-        <v>69h</v>
+        <v>84h30m</v>
       </c>
       <c r="AM19" t="str">
-        <v>49h45m</v>
+        <v>48h30m</v>
       </c>
       <c r="AN19" s="1">
-        <v>46125.59415509259</v>
+        <v>46160.45591435185</v>
       </c>
       <c r="AO19" s="1">
-        <v>46168.50347222222</v>
+        <v>46203.433333333334</v>
       </c>
       <c r="AP19" s="1">
-        <v>46400.7</v>
+        <v>46436.455555555556</v>
       </c>
       <c r="AU19" s="1">
-        <v>46070.584027777775</v>
+        <v>46091.65694444445</v>
       </c>
       <c r="AV19" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
-      </c>
-      <c r="AW19" t="str">
-        <v>Anne BRACKE</v>
+        <v>En direct</v>
       </c>
       <c r="AX19" s="1">
-        <v>46056.58472222222</v>
-      </c>
-      <c r="AY19" t="str">
-        <v>abracke@impulsions-ms.fr</v>
-      </c>
-      <c r="AZ19" t="str">
-        <v>0754383009</v>
+        <v>46091.65833333333</v>
       </c>
       <c r="BA19" t="str">
         <v>NON</v>
       </c>
-      <c r="BB19" t="str">
-        <v>LACQUEMENT</v>
-      </c>
-      <c r="BC19" t="str">
-        <v>Aurélie</v>
-      </c>
-      <c r="BD19" t="str">
-        <v>332 D RUE JEAN BAPTISTE LEBAS 59830 CYSOING</v>
-      </c>
-      <c r="BE19" t="str">
-        <v>0620618590</v>
-      </c>
-      <c r="BF19" t="str">
-        <v>fraulaju.l@gmail.com</v>
-      </c>
       <c r="BG19" t="str">
-        <v>14734</v>
+        <v>16911</v>
       </c>
       <c r="BH19" s="1">
-        <v>46104.041666666664</v>
+        <v>45687.041666666664</v>
+      </c>
+      <c r="BI19" t="str">
+        <v>1664877Z</v>
       </c>
       <c r="BJ19" t="str">
-        <v>73331821-8f69-4b98-8ad0-b728c88386e5</v>
+        <v>0946fb10-e8c6-458b-8a30-ce449aee830f</v>
       </c>
       <c r="BK19" t="str">
         <v>Accepted</v>
@@ -3386,30 +3368,30 @@
         <v/>
       </c>
       <c r="BM19" t="str">
-        <v>l.lauralact@gmail.com</v>
+        <v>lilea.neveschryve@protommail.com</v>
       </c>
       <c r="BN19" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_lacquement_e2c-grandlille_fr/IgD8CennTiSSTbSQnvap_WT7AX8xSA4WlLWEvyp33fyU-l0?e=rdANQf</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_neveschryve_e2c-grandlille_fr/IgD-epqrwKOGSZDP8a9VFwCKASltW3E9zR3dDdfDrPHyBGs?e=VbEbnK</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>82113</v>
+        <v>101329</v>
       </c>
       <c r="B20" t="str">
         <v>Femme</v>
       </c>
       <c r="C20" t="str">
-        <v>BELFARH</v>
+        <v>POUILLY</v>
       </c>
       <c r="D20" t="str">
-        <v>Nihed</v>
+        <v>Melinda</v>
       </c>
       <c r="E20" t="str">
-        <v>n.belfarh@e2c-grandlille.fr</v>
+        <v>m.pouilly@e2c-grandlille.fr</v>
       </c>
       <c r="F20" t="str">
-        <v>0638037438</v>
+        <v>0666505782</v>
       </c>
       <c r="G20" t="str">
         <v>Grand Lille</v>
@@ -3417,44 +3399,38 @@
       <c r="H20" t="str">
         <v>Lille</v>
       </c>
-      <c r="I20" t="str">
-        <v>Vendeur / Vendeuse en boulangerie-pâtisserie</v>
-      </c>
       <c r="K20" t="str">
         <v>Je sais</v>
       </c>
       <c r="L20" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés German</v>
       </c>
       <c r="M20" t="str">
         <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O20" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P20">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q20">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R20" s="1">
-        <v>37293</v>
+        <v>40074</v>
       </c>
       <c r="T20" t="str">
-        <v>ORAN</v>
+        <v>LILLE</v>
       </c>
       <c r="U20" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="W20" t="str">
-        <v>17 Rue Jean Moulin</v>
-      </c>
       <c r="X20" t="str">
-        <v>59130</v>
+        <v>59700</v>
       </c>
       <c r="Y20" t="str">
-        <v>Lambersart</v>
+        <v>Marcq-en-Barœul</v>
       </c>
       <c r="Z20" t="str">
         <v>Non</v>
@@ -3463,10 +3439,10 @@
         <v>Non</v>
       </c>
       <c r="AC20" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD20" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE20" t="str">
         <v>Non</v>
@@ -3487,52 +3463,55 @@
         <v>Non</v>
       </c>
       <c r="AK20" t="str">
-        <v>128h45m</v>
+        <v>243h45m</v>
       </c>
       <c r="AL20" t="str">
-        <v>72h</v>
+        <v>182h</v>
       </c>
       <c r="AM20" t="str">
-        <v>6h30m</v>
+        <v>20h45m</v>
       </c>
       <c r="AN20" s="1">
-        <v>46125.59168981481</v>
+        <v>46125.594988425924</v>
       </c>
       <c r="AO20" s="1">
-        <v>46168.49722222222</v>
+        <v>46168.50486111111</v>
       </c>
       <c r="AP20" s="1">
-        <v>46400.70416666667</v>
+        <v>46400.70625</v>
       </c>
       <c r="AU20" s="1">
-        <v>46070.57152777778</v>
+        <v>46091.643055555556</v>
       </c>
       <c r="AV20" t="str">
-        <v>MISSION LOCALE MNO - Antenne Lambersart</v>
-      </c>
-      <c r="AW20" t="str">
-        <v>Sébastien FOUQUET</v>
+        <v>En direct</v>
       </c>
       <c r="AX20" s="1">
-        <v>46069.572916666664</v>
-      </c>
-      <c r="AY20" t="str">
-        <v>sebastien.fouquet@mlmno.fr</v>
+        <v>46091.64513888889</v>
       </c>
       <c r="BA20" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB20" t="str">
+        <v>POUILLY</v>
+      </c>
+      <c r="BC20" t="str">
+        <v>Cathy</v>
+      </c>
+      <c r="BD20" t="str">
+        <v>11/37 RUE DES COTONNIERS 59700 MARCQ EN BAROEUL</v>
+      </c>
+      <c r="BE20" t="str">
+        <v>0611333451</v>
+      </c>
+      <c r="BF20" t="str">
+        <v>doudoune0503@hotmail.fr</v>
       </c>
       <c r="BG20" t="str">
-        <v>14719</v>
-      </c>
-      <c r="BH20" s="1">
-        <v>45892.083333333336</v>
-      </c>
-      <c r="BI20" t="str">
-        <v>5907923F</v>
+        <v>14739</v>
       </c>
       <c r="BJ20" t="str">
-        <v>d3940fc7-f9af-4b51-80a1-e214905242ad</v>
+        <v>1fbec1cf-3329-4450-bea5-67aa89defa9c</v>
       </c>
       <c r="BK20" t="str">
         <v>Accepted</v>
@@ -3541,30 +3520,30 @@
         <v/>
       </c>
       <c r="BM20" t="str">
-        <v>belfarhnihed@gmail.com</v>
+        <v>melinapouilly@icloud.com</v>
       </c>
       <c r="BN20" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_belfarh_e2c-grandlille_fr/IgDREh-6hXS-T5ULHKMeY_sgARm1V_OEOzOaQSBKbaE03u8?e=J6rEMJ</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_pouilly_e2c-grandlille_fr/IgBclX72W74AR49rnexSyw7eARxVfuu3ou_99kHz4Hpc768?e=6cnrWP</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>82109</v>
+        <v>101157</v>
       </c>
       <c r="B21" t="str">
         <v>Femme</v>
       </c>
       <c r="C21" t="str">
-        <v>DELOS</v>
+        <v>ROUSSEL</v>
       </c>
       <c r="D21" t="str">
-        <v>Célia</v>
+        <v>Sophia</v>
       </c>
       <c r="E21" t="str">
-        <v>c.delos@e2c-grandlille.fr</v>
+        <v>s.roussel@e2c-grandlille.fr</v>
       </c>
       <c r="F21" t="str">
-        <v>0629810326</v>
+        <v>0768373343</v>
       </c>
       <c r="G21" t="str">
         <v>Grand Lille</v>
@@ -3572,41 +3551,44 @@
       <c r="H21" t="str">
         <v>Lille</v>
       </c>
+      <c r="I21" t="str">
+        <v>Enseignant / Enseignante des écoles, Coach sportif, Professeur / Professeure d'éducation physique et sportive (EPS)</v>
+      </c>
       <c r="K21" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L21" t="str">
-        <v>référés Fanny</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M21" t="str">
         <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O21" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P21">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q21">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R21" s="1">
-        <v>37865</v>
+        <v>39352</v>
       </c>
       <c r="T21" t="str">
-        <v>LILLE</v>
+        <v>DIJON</v>
       </c>
       <c r="U21" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W21" t="str">
-        <v>67 Rue des Fossés</v>
+        <v>66 Rue Jean Bart (Hellemmes)</v>
       </c>
       <c r="X21" t="str">
-        <v>59480</v>
+        <v>59260</v>
       </c>
       <c r="Y21" t="str">
-        <v>La Bassée</v>
+        <v>Lille</v>
       </c>
       <c r="Z21" t="str">
         <v>Non</v>
@@ -3615,10 +3597,10 @@
         <v>Non</v>
       </c>
       <c r="AC21" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD21" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE21" t="str">
         <v>Non</v>
@@ -3639,46 +3621,55 @@
         <v>Non</v>
       </c>
       <c r="AK21" t="str">
-        <v>120h45m</v>
+        <v>180h45m</v>
       </c>
       <c r="AL21" t="str">
-        <v>67h30m</v>
+        <v>154h</v>
       </c>
       <c r="AM21" t="str">
-        <v>18h30m</v>
+        <v>84h</v>
       </c>
       <c r="AN21" s="1">
-        <v>46125.593090277776</v>
+        <v>46125.595289351855</v>
       </c>
       <c r="AO21" s="1">
-        <v>46168.501388888886</v>
+        <v>46168.50625</v>
       </c>
       <c r="AP21" s="1">
-        <v>46400.70694444444</v>
+        <v>46400.70347222222</v>
       </c>
       <c r="AU21" s="1">
-        <v>46070.51111111111</v>
+        <v>46091.61736111111</v>
       </c>
       <c r="AV21" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne de La Bassée</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Hellemmes</v>
       </c>
       <c r="AW21" t="str">
-        <v>Hervé DUMEZ</v>
+        <v>Gwenaëlle GOETGHELUCK</v>
       </c>
       <c r="AX21" s="1">
-        <v>46062.5125</v>
+        <v>46090.61944444444</v>
       </c>
       <c r="AY21" t="str">
-        <v>hdumez@impulsions-ms.fr</v>
+        <v>g.goetgheluck@lilleavenirs.fr</v>
+      </c>
+      <c r="AZ21" t="str">
+        <v>0762671622</v>
       </c>
       <c r="BA21" t="str">
         <v>NON</v>
       </c>
       <c r="BG21" t="str">
-        <v>14730</v>
+        <v>14741</v>
+      </c>
+      <c r="BH21" s="1">
+        <v>46120.083333333336</v>
+      </c>
+      <c r="BI21" t="str">
+        <v>5991883S</v>
       </c>
       <c r="BJ21" t="str">
-        <v>79387dbe-4c23-4e0e-a3c0-b3b27d852e8b</v>
+        <v>32f68e63-17ee-4ece-aae0-e884334779d2</v>
       </c>
       <c r="BK21" t="str">
         <v>Accepted</v>
@@ -3687,30 +3678,30 @@
         <v/>
       </c>
       <c r="BM21" t="str">
-        <v>deloscelia@icloud.com</v>
+        <v>sophia.i.roussel2709@gmail.com</v>
       </c>
       <c r="BN21" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_delos_e2c-grandlille_fr/IgB9mXK_OFJ7Qr4wLsP5PEolAe1iZp482MziT3M-YBtEMG4?e=HZB6on</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_roussel_e2c-grandlille_fr/IgAIqpVHe2BLSoCyGbwDs7DXAd9CSnDXDxC5iCzRzjwBxgE?e=p9CZ7n</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>82108</v>
+        <v>101130</v>
       </c>
       <c r="B22" t="str">
         <v>Femme</v>
       </c>
       <c r="C22" t="str">
-        <v>GUETTAL</v>
+        <v>BERTRAND</v>
       </c>
       <c r="D22" t="str">
-        <v>Laïla</v>
+        <v>Ophélie</v>
       </c>
       <c r="E22" t="str">
-        <v>l.guettal@e2c-grandlille.fr</v>
+        <v>o.bertrand@e2c-grandlille.fr</v>
       </c>
       <c r="F22" t="str">
-        <v>0670260140</v>
+        <v>0744558740</v>
       </c>
       <c r="G22" t="str">
         <v>Grand Lille</v>
@@ -3719,37 +3710,40 @@
         <v>Lille</v>
       </c>
       <c r="I22" t="str">
-        <v>Secrétaire médical / Secrétaire médicale</v>
+        <v>Préparateur / Préparatrice en pharmacie</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Contrat à durée indéterminée, Contrat à durée déterminée, CDI Intérimaire</v>
       </c>
       <c r="K22" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L22" t="str">
-        <v>référés Camille</v>
+        <v>référés German</v>
       </c>
       <c r="M22" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O22" t="str">
-        <v>PEAU Camille</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P22">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q22">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R22" s="1">
-        <v>37410</v>
+        <v>38930</v>
       </c>
       <c r="T22" t="str">
-        <v>ISSOIRE</v>
+        <v>CATEAU CAMBRESIS</v>
       </c>
       <c r="U22" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W22" t="str">
-        <v>3 Rue des Myosotis</v>
+        <v>11 Rue Abélard</v>
       </c>
       <c r="X22" t="str">
         <v>59000</v>
@@ -3758,111 +3752,102 @@
         <v>Lille</v>
       </c>
       <c r="Z22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AC22" t="str">
+        <v>CEJ_MISSION_LOCALE</v>
+      </c>
+      <c r="AD22" t="str">
+        <v>4 non validé</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AG22" t="str">
+        <v>SANS</v>
+      </c>
+      <c r="AH22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AI22" t="str">
         <v>Oui</v>
       </c>
-      <c r="AA22" t="str">
-        <v>QN05972M</v>
-      </c>
-      <c r="AB22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC22" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD22" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG22" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>Non</v>
-      </c>
       <c r="AJ22" t="str">
         <v>Non</v>
       </c>
       <c r="AK22" t="str">
-        <v>184h30m</v>
+        <v>170h45m</v>
       </c>
       <c r="AL22" t="str">
-        <v>139h30m</v>
+        <v>189h</v>
       </c>
       <c r="AM22" t="str">
-        <v>42h</v>
+        <v>94h</v>
       </c>
       <c r="AN22" s="1">
-        <v>46090.62322916667</v>
+        <v>46125.59216435185</v>
       </c>
       <c r="AO22" s="1">
-        <v>46133.4875</v>
+        <v>46168.498611111114</v>
       </c>
       <c r="AP22" s="1">
-        <v>46365.41388888889</v>
+        <v>46400.70486111111</v>
       </c>
       <c r="AU22" s="1">
-        <v>46070.506944444445</v>
+        <v>46091.61041666667</v>
       </c>
       <c r="AV22" t="str">
         <v>En direct</v>
       </c>
       <c r="AX22" s="1">
-        <v>46063.50833333333</v>
+        <v>46091.6125</v>
       </c>
       <c r="BA22" t="str">
         <v>NON</v>
       </c>
       <c r="BG22" t="str">
-        <v>11235</v>
-      </c>
-      <c r="BH22" s="1">
-        <v>45509.083333333336</v>
-      </c>
-      <c r="BI22" t="str">
-        <v>5527753C</v>
+        <v>14723</v>
       </c>
       <c r="BJ22" t="str">
-        <v>cc63dba1-497a-4558-91ba-734dbed2f357</v>
+        <v>09e12b15-255c-4c69-b300-2e6a87f62d03</v>
       </c>
       <c r="BK22" t="str">
         <v>Accepted</v>
       </c>
       <c r="BL22" t="str">
-        <v>Secrétaire médicale</v>
+        <v/>
       </c>
       <c r="BM22" t="str">
-        <v>lailaguettal0306@gmail.com</v>
+        <v>bertrandophelie66@gmail.com</v>
       </c>
       <c r="BN22" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_guettal_e2c-grandlille_fr/IgCgcsPw1GPkR77FWofbB0ygAcYSLy9bdsLR0Ccrz9OzpvI?e=BggVq8</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/o_bertrand_e2c-grandlille_fr/IgCOa2wsa257Ra8oRlexayeJAW2ZBcynh3TVWf61snjQUCA?e=535Htf</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>81017</v>
+        <v>83146</v>
       </c>
       <c r="B23" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C23" t="str">
-        <v>DELACROIX</v>
+        <v>HENNETON</v>
       </c>
       <c r="D23" t="str">
-        <v>Maylis</v>
+        <v>Pierrick</v>
       </c>
       <c r="E23" t="str">
-        <v>m.delacroix@e2c-grandlille.fr</v>
+        <v>p.henneton@e2c-grandlille.fr</v>
       </c>
       <c r="F23" t="str">
-        <v>0661243555</v>
+        <v>0643808541</v>
       </c>
       <c r="G23" t="str">
         <v>Grand Lille</v>
@@ -3871,7 +3856,7 @@
         <v>Lille</v>
       </c>
       <c r="I23" t="str">
-        <v>Agent / Agente d'accueil, Vendeur / Vendeuse en librairie, Vendeur / Vendeuse en animalerie</v>
+        <v>Scénariste</v>
       </c>
       <c r="K23" t="str">
         <v>J'ai des idées</v>
@@ -3880,19 +3865,19 @@
         <v>référés Fanny</v>
       </c>
       <c r="M23" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O23" t="str">
         <v>DUFOUR Fanny</v>
       </c>
       <c r="P23">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q23">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R23" s="1">
-        <v>39269</v>
+        <v>37583</v>
       </c>
       <c r="T23" t="str">
         <v>LILLE</v>
@@ -3901,10 +3886,10 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W23" t="str">
-        <v>12 Rue Rene Grauwin</v>
+        <v>30 Rue du Buisson</v>
       </c>
       <c r="X23" t="str">
-        <v>59160</v>
+        <v>59800</v>
       </c>
       <c r="Y23" t="str">
         <v>Lille</v>
@@ -3919,7 +3904,7 @@
         <v>NON</v>
       </c>
       <c r="AD23" t="str">
-        <v>3 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE23" t="str">
         <v>Non</v>
@@ -3940,55 +3925,46 @@
         <v>Non</v>
       </c>
       <c r="AK23" t="str">
-        <v>227h</v>
+        <v>154h30m</v>
       </c>
       <c r="AL23" t="str">
-        <v>168h</v>
+        <v>97h30m</v>
       </c>
       <c r="AM23" t="str">
-        <v>0m</v>
+        <v>113h15m</v>
       </c>
       <c r="AN23" s="1">
-        <v>46090.61549768518</v>
+        <v>46125.593460648146</v>
       </c>
       <c r="AO23" s="1">
-        <v>46133.48125</v>
+        <v>46168.50277777778</v>
       </c>
       <c r="AP23" s="1">
-        <v>46365.39027777778</v>
+        <v>46400.70763888889</v>
       </c>
       <c r="AU23" s="1">
-        <v>46063.68680555555</v>
+        <v>46084.48333333333</v>
       </c>
       <c r="AV23" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Lomme</v>
-      </c>
-      <c r="AW23" t="str">
-        <v>Elisa BOULIN</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Centre Ville</v>
       </c>
       <c r="AX23" s="1">
-        <v>46058.68819444445</v>
-      </c>
-      <c r="AY23" t="str">
-        <v>e.boulin@lilleavenirs.fr</v>
-      </c>
-      <c r="AZ23" t="str">
-        <v>0762762166</v>
+        <v>46080.48402777778</v>
       </c>
       <c r="BA23" t="str">
         <v>NON</v>
       </c>
       <c r="BG23" t="str">
-        <v>11219</v>
+        <v>14732</v>
       </c>
       <c r="BH23" s="1">
-        <v>46030.041666666664</v>
+        <v>46024.041666666664</v>
       </c>
       <c r="BI23" t="str">
-        <v>5973107H</v>
+        <v>5863777W</v>
       </c>
       <c r="BJ23" t="str">
-        <v>0f81fff5-bd89-4cb9-a274-04f87cd72186</v>
+        <v>2ef875c7-fdef-4992-a73d-cb3a14d9eedf</v>
       </c>
       <c r="BK23" t="str">
         <v>Accepted</v>
@@ -3997,30 +3973,30 @@
         <v/>
       </c>
       <c r="BM23" t="str">
-        <v>maylisdelacroix@hotmail.com</v>
+        <v>pierrickhenneton2311@gmail.com</v>
       </c>
       <c r="BN23" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_delacroix_e2c-grandlille_fr/IgDUM-raFMa3TKbjNvKo359jAVOtfh9rLr2Ux1fFu152fmw?e=360UBU</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/p_henneton_e2c-grandlille_fr/IgDnbwVP4r6hSocjwhe2_owJASy_HPFxsOL3APPGJ5LH5uM?e=3z3wMR</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>81016</v>
+        <v>83143</v>
       </c>
       <c r="B24" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C24" t="str">
-        <v>FLIN</v>
+        <v>ZOUTE</v>
       </c>
       <c r="D24" t="str">
-        <v>Mathéo</v>
+        <v>Sophie</v>
       </c>
       <c r="E24" t="str">
-        <v>m.flin@e2c-grandlille.fr</v>
+        <v>s.zoute@e2c-grandlille.fr</v>
       </c>
       <c r="F24" t="str">
-        <v>06 33 47 04 08</v>
+        <v>0601121601</v>
       </c>
       <c r="G24" t="str">
         <v>Grand Lille</v>
@@ -4029,28 +4005,31 @@
         <v>Lille</v>
       </c>
       <c r="I24" t="str">
-        <v>Administrateur / Administratrice sécurité informatique</v>
+        <v>Fleuriste</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
       </c>
       <c r="K24" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L24" t="str">
-        <v>référés Lucie</v>
+        <v>référés German</v>
       </c>
       <c r="M24" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O24" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q24">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R24" s="1">
-        <v>38262</v>
+        <v>39282</v>
       </c>
       <c r="T24" t="str">
         <v>ROUBAIX</v>
@@ -4059,13 +4038,13 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W24" t="str">
-        <v>220 Rue Charles Pollet</v>
+        <v>10 Allee des Tourelles</v>
       </c>
       <c r="X24" t="str">
-        <v>59830</v>
+        <v>59780</v>
       </c>
       <c r="Y24" t="str">
-        <v>Wannehain</v>
+        <v>Willems</v>
       </c>
       <c r="Z24" t="str">
         <v>Non</v>
@@ -4098,55 +4077,49 @@
         <v>Non</v>
       </c>
       <c r="AK24" t="str">
-        <v>212h45m</v>
+        <v>219h15m</v>
       </c>
       <c r="AL24" t="str">
-        <v>106h</v>
+        <v>126h</v>
       </c>
       <c r="AM24" t="str">
-        <v>16h15m</v>
+        <v>48h30m</v>
       </c>
       <c r="AN24" s="1">
-        <v>46090.62105324074</v>
+        <v>46125.595601851855</v>
       </c>
       <c r="AO24" s="1">
-        <v>46133.48472222222</v>
+        <v>46203.42569444444</v>
       </c>
       <c r="AP24" s="1">
-        <v>46365.40694444445</v>
+        <v>46400.705555555556</v>
       </c>
       <c r="AU24" s="1">
-        <v>46063.68402777778</v>
+        <v>46084.478472222225</v>
       </c>
       <c r="AV24" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
+        <v>MISSION LOCALE MÉTROPOLE EST - Antenne de Villeneuve d'Ascq</v>
       </c>
       <c r="AW24" t="str">
-        <v>Anne BRACKE</v>
+        <v>Mathilde RULANCE</v>
       </c>
       <c r="AX24" s="1">
-        <v>46057.686111111114</v>
-      </c>
-      <c r="AY24" t="str">
-        <v>abracke@impulsions-ms.fr</v>
-      </c>
-      <c r="AZ24" t="str">
-        <v>0754383009</v>
+        <v>46084.47986111111</v>
       </c>
       <c r="BA24" t="str">
         <v>NON</v>
       </c>
       <c r="BG24" t="str">
-        <v>11293</v>
+        <v>14744</v>
       </c>
       <c r="BH24" s="1">
-        <v>46035.041666666664</v>
+        <v>46041.041666666664</v>
       </c>
       <c r="BI24" t="str">
-        <v>5974250A</v>
+        <v>5975695W</v>
       </c>
       <c r="BJ24" t="str">
-        <v>c4ab81e2-9452-4251-95f6-6e3a309b04fa</v>
+        <v>4add060d-a7d3-467b-93c0-9238f934cb95</v>
       </c>
       <c r="BK24" t="str">
         <v>Accepted</v>
@@ -4155,30 +4128,30 @@
         <v/>
       </c>
       <c r="BM24" t="str">
-        <v>matheoflin@gmail.com</v>
+        <v>sophiezoute@gmail.com</v>
       </c>
       <c r="BN24" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_flin_e2c-grandlille_fr/IgB6V-bIRQaFR5chZex-OPnXAe4WCCcv9ICxT3vvMB1-2J8?e=uzHAj0</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_zoute_e2c-grandlille_fr/IgALGyPxWf-8RZtTdlsBSr6XAVIQx8ingPu3I2AsFmpx2z0?e=a3kQiP</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>81011</v>
+        <v>82674</v>
       </c>
       <c r="B25" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C25" t="str">
-        <v>PENNEL--SANCHEZ</v>
+        <v>AKOUGNI</v>
       </c>
       <c r="D25" t="str">
-        <v>Diego</v>
+        <v>Germaine</v>
       </c>
       <c r="E25" t="str">
-        <v>d.pennelsanchez@e2c-grandlille.fr</v>
+        <v>g.akougni@e2c-grandlille.fr</v>
       </c>
       <c r="F25" t="str">
-        <v>0612562905</v>
+        <v>0648537574</v>
       </c>
       <c r="G25" t="str">
         <v>Grand Lille</v>
@@ -4186,41 +4159,44 @@
       <c r="H25" t="str">
         <v>Lille</v>
       </c>
+      <c r="I25" t="str">
+        <v>Assistant administratif / Assistante administrative, Assistant / Assistante Ressources Humaines (RH)</v>
+      </c>
       <c r="K25" t="str">
         <v>Je sais</v>
       </c>
       <c r="L25" t="str">
-        <v>référés Anne</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M25" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O25" t="str">
-        <v>CAPEAU Anne</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R25" s="1">
-        <v>39277</v>
+        <v>39183</v>
       </c>
       <c r="T25" t="str">
-        <v>LILLE</v>
+        <v>NOUMEA</v>
       </c>
       <c r="U25" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W25" t="str">
-        <v>5 Rue Louis Braille</v>
+        <v>1 Rue de la Brasserie</v>
       </c>
       <c r="X25" t="str">
-        <v>59000</v>
+        <v>59790</v>
       </c>
       <c r="Y25" t="str">
-        <v>Lille</v>
+        <v>Ronchin</v>
       </c>
       <c r="Z25" t="str">
         <v>Non</v>
@@ -4232,7 +4208,7 @@
         <v>NON</v>
       </c>
       <c r="AD25" t="str">
-        <v>4 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE25" t="str">
         <v>Non</v>
@@ -4253,40 +4229,46 @@
         <v>Non</v>
       </c>
       <c r="AK25" t="str">
-        <v>175h15m</v>
+        <v>222h30m</v>
       </c>
       <c r="AL25" t="str">
-        <v>85h</v>
+        <v>170h30m</v>
       </c>
       <c r="AM25" t="str">
-        <v>29h15m</v>
+        <v>42h15m</v>
       </c>
       <c r="AN25" s="1">
-        <v>46090.62510416667</v>
+        <v>46125.58611111111</v>
       </c>
       <c r="AO25" s="1">
-        <v>46168.59652777778</v>
+        <v>46168.495833333334</v>
       </c>
       <c r="AP25" s="1">
-        <v>46365.39166666667</v>
+        <v>46400.70625</v>
       </c>
       <c r="AU25" s="1">
-        <v>46063.67083333333</v>
+        <v>46077.404861111114</v>
       </c>
       <c r="AV25" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
+        <v>En direct</v>
       </c>
       <c r="AX25" s="1">
-        <v>46063.67222222222</v>
+        <v>46077.40625</v>
       </c>
       <c r="BA25" t="str">
         <v>NON</v>
       </c>
       <c r="BG25" t="str">
-        <v>11221</v>
+        <v>14717</v>
+      </c>
+      <c r="BH25" s="1">
+        <v>45889.083333333336</v>
+      </c>
+      <c r="BI25" t="str">
+        <v>5928480A</v>
       </c>
       <c r="BJ25" t="str">
-        <v>fa5cc185-0aaa-4c56-b1eb-36e11417a8e0</v>
+        <v>fe5352b3-71a5-498b-b965-d941e357a743</v>
       </c>
       <c r="BK25" t="str">
         <v>Accepted</v>
@@ -4295,30 +4277,30 @@
         <v/>
       </c>
       <c r="BM25" t="str">
-        <v>d.pennelsanchez@gmail.com</v>
+        <v>akougnigermaine@gmail.com</v>
       </c>
       <c r="BN25" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/d_pennelsanchez_e2c-grandlille_fr/IgDk-wMJpvETRojNqPgmxmqTAQKIMGTF8c_P_od_ASztqZE?e=j9xR63</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/g_akougni_e2c-grandlille_fr/IgCBBCBHbn0pR5R2Xl45gfLNAV5MmW4Q4kTp8enccFMP3wM?e=Ik47Ae</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>80998</v>
+        <v>82115</v>
       </c>
       <c r="B26" t="str">
         <v>Femme</v>
       </c>
       <c r="C26" t="str">
-        <v>LECLERCQ</v>
+        <v>LACQUEMENT</v>
       </c>
       <c r="D26" t="str">
-        <v>Erika</v>
+        <v>Laura</v>
       </c>
       <c r="E26" t="str">
-        <v>e.leclercq@e2c-grandlille.fr</v>
+        <v>l.lacquement@e2c-grandlille.fr</v>
       </c>
       <c r="F26" t="str">
-        <v>0766112078</v>
+        <v>0614401952</v>
       </c>
       <c r="G26" t="str">
         <v>Grand Lille</v>
@@ -4327,31 +4309,28 @@
         <v>Lille</v>
       </c>
       <c r="I26" t="str">
-        <v>Vendeur / Vendeuse en prêt-à-porter, Agent territorial spécialisé / Agente territoriale spécialisée des écoles maternelles (ATSEM)</v>
-      </c>
-      <c r="J26" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
+        <v>Esthéticien / Esthéticienne</v>
       </c>
       <c r="K26" t="str">
         <v>Je sais</v>
       </c>
       <c r="L26" t="str">
-        <v>référés German</v>
+        <v>référés Sura</v>
       </c>
       <c r="M26" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O26" t="str">
-        <v>LEON QUERO German</v>
+        <v>JAMIL HUSSAIN Sura</v>
       </c>
       <c r="P26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R26" s="1">
-        <v>39084</v>
+        <v>39759</v>
       </c>
       <c r="T26" t="str">
         <v>LILLE</v>
@@ -4359,6 +4338,9 @@
       <c r="U26" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="W26" t="str">
+        <v>332 Rue Jean-baptiste Lebas</v>
+      </c>
       <c r="X26" t="str">
         <v>59830</v>
       </c>
@@ -4375,7 +4357,7 @@
         <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD26" t="str">
-        <v>Infra 3</v>
+        <v>3 validé</v>
       </c>
       <c r="AE26" t="str">
         <v>Non</v>
@@ -4396,25 +4378,25 @@
         <v>Non</v>
       </c>
       <c r="AK26" t="str">
-        <v>207h30m</v>
+        <v>56h15m</v>
       </c>
       <c r="AL26" t="str">
-        <v>84h</v>
+        <v>69h</v>
       </c>
       <c r="AM26" t="str">
-        <v>3h15m</v>
+        <v>114h15m</v>
       </c>
       <c r="AN26" s="1">
-        <v>46090.62385416667</v>
+        <v>46125.59415509259</v>
       </c>
       <c r="AO26" s="1">
-        <v>46168.47222222222</v>
+        <v>46168.50347222222</v>
       </c>
       <c r="AP26" s="1">
-        <v>46365.402083333334</v>
+        <v>46400.7</v>
       </c>
       <c r="AU26" s="1">
-        <v>46063.65833333333</v>
+        <v>46070.584027777775</v>
       </c>
       <c r="AV26" t="str">
         <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
@@ -4423,10 +4405,10 @@
         <v>Anne BRACKE</v>
       </c>
       <c r="AX26" s="1">
-        <v>46057.65972222222</v>
+        <v>46056.58472222222</v>
       </c>
       <c r="AY26" t="str">
-        <v>a.bracke@impulsions-ms.fr</v>
+        <v>abracke@impulsions-ms.fr</v>
       </c>
       <c r="AZ26" t="str">
         <v>0754383009</v>
@@ -4434,11 +4416,29 @@
       <c r="BA26" t="str">
         <v>NON</v>
       </c>
+      <c r="BB26" t="str">
+        <v>LACQUEMENT</v>
+      </c>
+      <c r="BC26" t="str">
+        <v>Aurélie</v>
+      </c>
+      <c r="BD26" t="str">
+        <v>332 D RUE JEAN BAPTISTE LEBAS 59830 CYSOING</v>
+      </c>
+      <c r="BE26" t="str">
+        <v>0620618590</v>
+      </c>
+      <c r="BF26" t="str">
+        <v>fraulaju.l@gmail.com</v>
+      </c>
       <c r="BG26" t="str">
-        <v>11226</v>
+        <v>14734</v>
+      </c>
+      <c r="BH26" s="1">
+        <v>46104.041666666664</v>
       </c>
       <c r="BJ26" t="str">
-        <v>d9df52f8-6a24-4a90-9003-27aa8d86d290</v>
+        <v>73331821-8f69-4b98-8ad0-b728c88386e5</v>
       </c>
       <c r="BK26" t="str">
         <v>Accepted</v>
@@ -4447,30 +4447,30 @@
         <v/>
       </c>
       <c r="BM26" t="str">
-        <v>erikaleclercq1@icloud.com</v>
+        <v>l.lauralact@gmail.com</v>
       </c>
       <c r="BN26" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_leclercq_e2c-grandlille_fr/IgAfFOi3_77JT4H4CkCBchcYAX0WO8D1_y2wwL3Il2VkRQk?e=GdaSyd</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_lacquement_e2c-grandlille_fr/IgD8CennTiSSTbSQnvap_WT7AX8xSA4WlLWEvyp33fyU-l0?e=rdANQf</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>80995</v>
+        <v>82113</v>
       </c>
       <c r="B27" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C27" t="str">
-        <v>CADET</v>
+        <v>BELFARH</v>
       </c>
       <c r="D27" t="str">
-        <v>Maxence</v>
+        <v>Nihed</v>
       </c>
       <c r="E27" t="str">
-        <v>m.cadet@e2c-grandlille.fr</v>
+        <v>n.belfarh@e2c-grandlille.fr</v>
       </c>
       <c r="F27" t="str">
-        <v>0749398136</v>
+        <v>0638037438</v>
       </c>
       <c r="G27" t="str">
         <v>Grand Lille</v>
@@ -4478,41 +4478,44 @@
       <c r="H27" t="str">
         <v>Lille</v>
       </c>
+      <c r="I27" t="str">
+        <v>Vendeur / Vendeuse en boulangerie-pâtisserie</v>
+      </c>
       <c r="K27" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L27" t="str">
-        <v>référés Anne</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M27" t="str">
         <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O27" t="str">
-        <v>CAPEAU Anne</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P27">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q27">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R27" s="1">
-        <v>39023</v>
+        <v>37293</v>
       </c>
       <c r="T27" t="str">
-        <v>PERONNE</v>
+        <v>ORAN</v>
       </c>
       <c r="U27" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W27" t="str">
-        <v>2 Place de la République (Hellemmes)</v>
+        <v>17 Rue Jean Moulin</v>
       </c>
       <c r="X27" t="str">
-        <v>59260</v>
+        <v>59130</v>
       </c>
       <c r="Y27" t="str">
-        <v>Lille</v>
+        <v>Lambersart</v>
       </c>
       <c r="Z27" t="str">
         <v>Non</v>
@@ -4521,10 +4524,10 @@
         <v>Non</v>
       </c>
       <c r="AC27" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD27" t="str">
-        <v>3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE27" t="str">
         <v>Non</v>
@@ -4545,55 +4548,52 @@
         <v>Non</v>
       </c>
       <c r="AK27" t="str">
-        <v>87h15m</v>
+        <v>177h30m</v>
       </c>
       <c r="AL27" t="str">
-        <v>84h</v>
+        <v>185h</v>
       </c>
       <c r="AM27" t="str">
-        <v>44h15m</v>
+        <v>22h45m</v>
       </c>
       <c r="AN27" s="1">
-        <v>46125.59275462963</v>
+        <v>46125.59168981481</v>
       </c>
       <c r="AO27" s="1">
-        <v>46168.5</v>
+        <v>46168.49722222222</v>
       </c>
       <c r="AP27" s="1">
-        <v>46400.70277777778</v>
+        <v>46400.70416666667</v>
       </c>
       <c r="AU27" s="1">
-        <v>46063.64444444444</v>
+        <v>46070.57152777778</v>
       </c>
       <c r="AV27" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Hellemmes</v>
+        <v>MISSION LOCALE MNO - Antenne Lambersart</v>
       </c>
       <c r="AW27" t="str">
-        <v>Jeanine GORNIAK</v>
+        <v>Sébastien FOUQUET</v>
       </c>
       <c r="AX27" s="1">
-        <v>46057.64722222222</v>
+        <v>46069.572916666664</v>
       </c>
       <c r="AY27" t="str">
-        <v>j.gorniak@lilleavenirs.fr</v>
-      </c>
-      <c r="AZ27" t="str">
-        <v>0762748393</v>
+        <v>sebastien.fouquet@mlmno.fr</v>
       </c>
       <c r="BA27" t="str">
         <v>NON</v>
       </c>
       <c r="BG27" t="str">
-        <v>14727</v>
+        <v>14719</v>
       </c>
       <c r="BH27" s="1">
-        <v>46056.041666666664</v>
+        <v>45892.083333333336</v>
       </c>
       <c r="BI27" t="str">
-        <v>5890226V</v>
+        <v>5907923F</v>
       </c>
       <c r="BJ27" t="str">
-        <v>12270a9d-bcae-4b4d-a4d0-4c5c297db741</v>
+        <v>d3940fc7-f9af-4b51-80a1-e214905242ad</v>
       </c>
       <c r="BK27" t="str">
         <v>Accepted</v>
@@ -4602,30 +4602,30 @@
         <v/>
       </c>
       <c r="BM27" t="str">
-        <v>maxence.cadet2006@gmail.com</v>
+        <v>belfarhnihed@gmail.com</v>
       </c>
       <c r="BN27" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_cadet_e2c-grandlille_fr/IgDVd4iynutcQr0cxwqIbWnOAdKBvgGOm50gdJnaKzEWyS8?e=fU0GGr</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_belfarh_e2c-grandlille_fr/IgDREh-6hXS-T5ULHKMeY_sgARm1V_OEOzOaQSBKbaE03u8?e=J6rEMJ</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>80983</v>
+        <v>82109</v>
       </c>
       <c r="B28" t="str">
         <v>Femme</v>
       </c>
       <c r="C28" t="str">
-        <v>WATINE</v>
+        <v>DELOS</v>
       </c>
       <c r="D28" t="str">
-        <v>Léa</v>
+        <v>Célia</v>
       </c>
       <c r="E28" t="str">
-        <v>l.watine@e2c-grandlille.fr</v>
+        <v>c.delos@e2c-grandlille.fr</v>
       </c>
       <c r="F28" t="str">
-        <v>06 51 34 41 86</v>
+        <v>0629810326</v>
       </c>
       <c r="G28" t="str">
         <v>Grand Lille</v>
@@ -4634,28 +4634,28 @@
         <v>Lille</v>
       </c>
       <c r="I28" t="str">
-        <v>Menuisier / Menuisière, Chargé / Chargée de communication événementielle</v>
+        <v>Agent territorial spécialisé / Agente territoriale spécialisée des écoles maternelles (ATSEM)</v>
       </c>
       <c r="K28" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L28" t="str">
-        <v>référés Lucie</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M28" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O28" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P28">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q28">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R28" s="1">
-        <v>38689</v>
+        <v>37865</v>
       </c>
       <c r="T28" t="str">
         <v>LILLE</v>
@@ -4664,13 +4664,13 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W28" t="str">
-        <v>38 Rue Francisco Ferrer</v>
+        <v>67 Rue des Fossés</v>
       </c>
       <c r="X28" t="str">
-        <v>59800</v>
+        <v>59480</v>
       </c>
       <c r="Y28" t="str">
-        <v>Lille</v>
+        <v>La Bassée</v>
       </c>
       <c r="Z28" t="str">
         <v>Non</v>
@@ -4679,10 +4679,10 @@
         <v>Non</v>
       </c>
       <c r="AC28" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD28" t="str">
-        <v>4 non validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE28" t="str">
         <v>Non</v>
@@ -4703,46 +4703,46 @@
         <v>Non</v>
       </c>
       <c r="AK28" t="str">
-        <v>100h45m</v>
+        <v>177h</v>
       </c>
       <c r="AL28" t="str">
-        <v>214h</v>
+        <v>170h30m</v>
       </c>
       <c r="AM28" t="str">
-        <v>71h</v>
+        <v>87h45m</v>
       </c>
       <c r="AN28" s="1">
-        <v>46090.626967592594</v>
+        <v>46125.593090277776</v>
       </c>
       <c r="AO28" s="1">
-        <v>46133.49097222222</v>
+        <v>46168.501388888886</v>
       </c>
       <c r="AP28" s="1">
-        <v>46365.40416666667</v>
+        <v>46400.70694444444</v>
       </c>
       <c r="AU28" s="1">
-        <v>46056.620833333334</v>
+        <v>46070.51111111111</v>
       </c>
       <c r="AV28" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne de La Bassée</v>
+      </c>
+      <c r="AW28" t="str">
+        <v>Hervé DUMEZ</v>
       </c>
       <c r="AX28" s="1">
-        <v>46056.62222222222</v>
+        <v>46062.5125</v>
+      </c>
+      <c r="AY28" t="str">
+        <v>hdumez@impulsions-ms.fr</v>
       </c>
       <c r="BA28" t="str">
         <v>NON</v>
       </c>
       <c r="BG28" t="str">
-        <v>11298</v>
-      </c>
-      <c r="BH28" s="1">
-        <v>45922.083333333336</v>
-      </c>
-      <c r="BI28" t="str">
-        <v>5943905S</v>
+        <v>14730</v>
       </c>
       <c r="BJ28" t="str">
-        <v>1d324e81-21d7-4fb9-be91-8613b657f50a</v>
+        <v>79387dbe-4c23-4e0e-a3c0-b3b27d852e8b</v>
       </c>
       <c r="BK28" t="str">
         <v>Accepted</v>
@@ -4751,30 +4751,30 @@
         <v/>
       </c>
       <c r="BM28" t="str">
-        <v>leaawatine@gmail.com</v>
+        <v>deloscelia@icloud.com</v>
       </c>
       <c r="BN28" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_watine_e2c-grandlille_fr/IgB2Kfw6VwGZQp_RCIxnxusdAYz1btBeoPXOVNRriyKBUkU?e=wvjSnw</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_delos_e2c-grandlille_fr/IgB9mXK_OFJ7Qr4wLsP5PEolAe1iZp482MziT3M-YBtEMG4?e=HZB6on</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>79913</v>
+        <v>82108</v>
       </c>
       <c r="B29" t="str">
         <v>Femme</v>
       </c>
       <c r="C29" t="str">
-        <v>BOXOEN</v>
+        <v>GUETTAL</v>
       </c>
       <c r="D29" t="str">
-        <v>Léa</v>
+        <v>Laïla</v>
       </c>
       <c r="E29" t="str">
-        <v>l.boxoen@e2c-grandlille.fr</v>
+        <v>l.guettal@e2c-grandlille.fr</v>
       </c>
       <c r="F29" t="str">
-        <v>07 67 48 82 53</v>
+        <v>0670260140</v>
       </c>
       <c r="G29" t="str">
         <v>Grand Lille</v>
@@ -4783,49 +4783,49 @@
         <v>Lille</v>
       </c>
       <c r="I29" t="str">
-        <v>Pâtissier / Pâtissière</v>
-      </c>
-      <c r="J29" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
+        <v>Secrétaire médical / Secrétaire médicale</v>
       </c>
       <c r="K29" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L29" t="str">
-        <v>référés Lucie</v>
+        <v>référés Camille</v>
       </c>
       <c r="M29" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O29" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>PEAU Camille</v>
       </c>
       <c r="P29">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q29">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R29" s="1">
-        <v>38536</v>
+        <v>37410</v>
       </c>
       <c r="T29" t="str">
-        <v>ARMENTIERES</v>
+        <v>ISSOIRE</v>
       </c>
       <c r="U29" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W29" t="str">
-        <v>53 Rue du Mécanicien</v>
+        <v>3 Rue des Myosotis</v>
       </c>
       <c r="X29" t="str">
-        <v>59193</v>
+        <v>59000</v>
       </c>
       <c r="Y29" t="str">
-        <v>Erquinghem-Lys</v>
+        <v>Lille</v>
       </c>
       <c r="Z29" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>QN05972M</v>
       </c>
       <c r="AB29" t="str">
         <v>Non</v>
@@ -4834,7 +4834,7 @@
         <v>NON</v>
       </c>
       <c r="AD29" t="str">
-        <v>4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE29" t="str">
         <v>Non</v>
@@ -4843,7 +4843,7 @@
         <v>Non</v>
       </c>
       <c r="AG29" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH29" t="str">
         <v>Non</v>
@@ -4855,78 +4855,78 @@
         <v>Non</v>
       </c>
       <c r="AK29" t="str">
-        <v>269h30m</v>
+        <v>225h30m</v>
       </c>
       <c r="AL29" t="str">
-        <v>220h</v>
+        <v>209h30m</v>
       </c>
       <c r="AM29" t="str">
-        <v>19h30m</v>
+        <v>136h</v>
       </c>
       <c r="AN29" s="1">
-        <v>46063.60270833333</v>
+        <v>46090.62322916667</v>
       </c>
       <c r="AO29" s="1">
-        <v>46098.61111111111</v>
+        <v>46133.4875</v>
       </c>
       <c r="AP29" s="1">
-        <v>46336.50555555556</v>
+        <v>46365.41388888889</v>
       </c>
       <c r="AU29" s="1">
-        <v>46055.725694444445</v>
+        <v>46070.506944444445</v>
       </c>
       <c r="AV29" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
+        <v>En direct</v>
       </c>
       <c r="AX29" s="1">
-        <v>46052.72638888889</v>
+        <v>46063.50833333333</v>
       </c>
       <c r="BA29" t="str">
         <v>NON</v>
       </c>
       <c r="BG29" t="str">
-        <v>10272</v>
+        <v>11235</v>
       </c>
       <c r="BH29" s="1">
-        <v>45967.041666666664</v>
+        <v>45509.083333333336</v>
       </c>
       <c r="BI29" t="str">
-        <v>5959795N</v>
+        <v>5527753C</v>
       </c>
       <c r="BJ29" t="str">
-        <v>f1bb344e-9fe5-42fd-9271-728e06dfcd4d</v>
+        <v>cc63dba1-497a-4558-91ba-734dbed2f357</v>
       </c>
       <c r="BK29" t="str">
         <v>Accepted</v>
       </c>
       <c r="BL29" t="str">
-        <v/>
+        <v>Secrétaire médicale</v>
       </c>
       <c r="BM29" t="str">
-        <v>leaboxoen8@gmail.com</v>
+        <v>lailaguettal0306@gmail.com</v>
       </c>
       <c r="BN29" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/l_boxoen_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fl%5Fboxoen%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;ga=1</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_guettal_e2c-grandlille_fr/IgCgcsPw1GPkR77FWofbB0ygAcYSLy9bdsLR0Ccrz9OzpvI?e=BggVq8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>78466</v>
+        <v>81017</v>
       </c>
       <c r="B30" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C30" t="str">
-        <v>BENKERROU</v>
+        <v>DELACROIX</v>
       </c>
       <c r="D30" t="str">
-        <v>Jugurta</v>
+        <v>Maylis</v>
       </c>
       <c r="E30" t="str">
-        <v>j.benkerrou@e2c-grandlille.fr</v>
+        <v>m.delacroix@e2c-grandlille.fr</v>
       </c>
       <c r="F30" t="str">
-        <v>0695330267</v>
+        <v>0661243555</v>
       </c>
       <c r="G30" t="str">
         <v>Grand Lille</v>
@@ -4935,40 +4935,37 @@
         <v>Lille</v>
       </c>
       <c r="I30" t="str">
-        <v>Pâtissier / Pâtissière</v>
-      </c>
-      <c r="J30" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
+        <v>Agent / Agente d'accueil, Vendeur / Vendeuse en librairie, Vendeur / Vendeuse en animalerie</v>
       </c>
       <c r="K30" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L30" t="str">
-        <v>référés German</v>
+        <v>référés Fanny</v>
       </c>
       <c r="M30" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O30" t="str">
-        <v>LEON QUERO German</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P30">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q30">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R30" s="1">
-        <v>37501</v>
+        <v>39269</v>
       </c>
       <c r="T30" t="str">
-        <v>VALENCIENNES</v>
+        <v>LILLE</v>
       </c>
       <c r="U30" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W30" t="str">
-        <v>9 Rue de l'Ancienne Balaterie</v>
+        <v>12 Rue Rene Grauwin</v>
       </c>
       <c r="X30" t="str">
         <v>59160</v>
@@ -4986,7 +4983,7 @@
         <v>NON</v>
       </c>
       <c r="AD30" t="str">
-        <v>4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE30" t="str">
         <v>Non</v>
@@ -5007,49 +5004,55 @@
         <v>Non</v>
       </c>
       <c r="AK30" t="str">
-        <v>243h45m</v>
+        <v>358h15m</v>
       </c>
       <c r="AL30" t="str">
-        <v>224h</v>
+        <v>259h</v>
       </c>
       <c r="AM30" t="str">
-        <v>48h30m</v>
+        <v>3h15m</v>
       </c>
       <c r="AN30" s="1">
-        <v>46063.601493055554</v>
+        <v>46090.61549768518</v>
       </c>
       <c r="AO30" s="1">
-        <v>46098.61041666667</v>
+        <v>46133.48125</v>
       </c>
       <c r="AP30" s="1">
-        <v>46336.50555555556</v>
+        <v>46365.39027777778</v>
       </c>
       <c r="AU30" s="1">
-        <v>46049.459027777775</v>
+        <v>46063.68680555555</v>
       </c>
       <c r="AV30" t="str">
-        <v>MISSION LOCALE DE LILLE- LILLE AVENIRS -Siège-</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Lomme</v>
       </c>
       <c r="AW30" t="str">
-        <v>Catherine ROSIAUX</v>
+        <v>Elisa BOULIN</v>
       </c>
       <c r="AX30" s="1">
-        <v>46049.46041666667</v>
+        <v>46058.68819444445</v>
+      </c>
+      <c r="AY30" t="str">
+        <v>e.boulin@lilleavenirs.fr</v>
+      </c>
+      <c r="AZ30" t="str">
+        <v>0762762166</v>
       </c>
       <c r="BA30" t="str">
         <v>NON</v>
       </c>
       <c r="BG30" t="str">
-        <v>10396</v>
+        <v>11219</v>
       </c>
       <c r="BH30" s="1">
-        <v>45686.041666666664</v>
+        <v>46030.041666666664</v>
       </c>
       <c r="BI30" t="str">
-        <v>5683204W</v>
+        <v>5973107H</v>
       </c>
       <c r="BJ30" t="str">
-        <v>956790a3-e616-4984-8fba-d8509012b8a8</v>
+        <v>0f81fff5-bd89-4cb9-a274-04f87cd72186</v>
       </c>
       <c r="BK30" t="str">
         <v>Accepted</v>
@@ -5058,30 +5061,30 @@
         <v/>
       </c>
       <c r="BM30" t="str">
-        <v>benkerroujugurta@hotmail.com</v>
+        <v>maylisdelacroix@hotmail.com</v>
       </c>
       <c r="BN30" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/j_benkerrou_e2c-grandlille_fr/IgCEMBRnJY0AR76rPk_CYRNGASJP4dYz01JNTHw7Ze-so_4?e=95muJl</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_delacroix_e2c-grandlille_fr/IgDUM-raFMa3TKbjNvKo359jAVOtfh9rLr2Ux1fFu152fmw?e=360UBU</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>78083</v>
+        <v>81016</v>
       </c>
       <c r="B31" t="str">
         <v>Homme</v>
       </c>
       <c r="C31" t="str">
-        <v>NGAHAN KINDA</v>
+        <v>FLIN</v>
       </c>
       <c r="D31" t="str">
-        <v>Warren</v>
+        <v>Mathéo</v>
       </c>
       <c r="E31" t="str">
-        <v>w.ngahankinda@e2c-grandlille.fr</v>
+        <v>m.flin@e2c-grandlille.fr</v>
       </c>
       <c r="F31" t="str">
-        <v>06 44 73 56 78</v>
+        <v>06 33 47 04 08</v>
       </c>
       <c r="G31" t="str">
         <v>Grand Lille</v>
@@ -5090,7 +5093,7 @@
         <v>Lille</v>
       </c>
       <c r="I31" t="str">
-        <v>Pâtissier / Pâtissière</v>
+        <v>Administrateur / Administratrice sécurité informatique</v>
       </c>
       <c r="K31" t="str">
         <v>Je sais</v>
@@ -5099,7 +5102,7 @@
         <v>référés Lucie</v>
       </c>
       <c r="M31" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O31" t="str">
         <v>DERCOURT Lucie</v>
@@ -5111,37 +5114,34 @@
         <v>21</v>
       </c>
       <c r="R31" s="1">
-        <v>38295</v>
+        <v>38262</v>
       </c>
       <c r="T31" t="str">
-        <v>LILLE</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U31" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W31" t="str">
-        <v>23 Rue de l'Amiral Courbet</v>
+        <v>220 Rue Charles Pollet</v>
       </c>
       <c r="X31" t="str">
-        <v>59800</v>
+        <v>59830</v>
       </c>
       <c r="Y31" t="str">
-        <v>Lille</v>
+        <v>Wannehain</v>
       </c>
       <c r="Z31" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA31" t="str">
-        <v>QN05973M</v>
+        <v>Non</v>
       </c>
       <c r="AB31" t="str">
         <v>Non</v>
       </c>
       <c r="AC31" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD31" t="str">
-        <v>3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE31" t="str">
         <v>Non</v>
@@ -5162,49 +5162,55 @@
         <v>Non</v>
       </c>
       <c r="AK31" t="str">
-        <v>270h45m</v>
+        <v>315h45m</v>
       </c>
       <c r="AL31" t="str">
-        <v>214h</v>
+        <v>176h</v>
       </c>
       <c r="AM31" t="str">
-        <v>19h30m</v>
+        <v>48h45m</v>
       </c>
       <c r="AN31" s="1">
-        <v>46063.60650462963</v>
+        <v>46090.62105324074</v>
       </c>
       <c r="AO31" s="1">
-        <v>46098.61597222222</v>
+        <v>46133.48472222222</v>
       </c>
       <c r="AP31" s="1">
-        <v>46336.50763888889</v>
+        <v>46365.40694444445</v>
       </c>
       <c r="AU31" s="1">
-        <v>46049.654861111114</v>
+        <v>46063.68402777778</v>
       </c>
       <c r="AV31" t="str">
-        <v>MISSION LOCALE DE LILLE- LILLE AVENIRS -Siège-</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
       </c>
       <c r="AW31" t="str">
-        <v>Catherine TAQUIN ROSIAUX</v>
+        <v>Anne BRACKE</v>
       </c>
       <c r="AX31" s="1">
-        <v>46043.65625</v>
+        <v>46057.686111111114</v>
       </c>
       <c r="AY31" t="str">
-        <v>c.rosiaux@lilleavenirs.fr</v>
+        <v>abracke@impulsions-ms.fr</v>
       </c>
       <c r="AZ31" t="str">
-        <v>0669209968</v>
+        <v>0754383009</v>
       </c>
       <c r="BA31" t="str">
         <v>NON</v>
       </c>
       <c r="BG31" t="str">
-        <v>10415</v>
+        <v>11293</v>
+      </c>
+      <c r="BH31" s="1">
+        <v>46035.041666666664</v>
+      </c>
+      <c r="BI31" t="str">
+        <v>5974250A</v>
       </c>
       <c r="BJ31" t="str">
-        <v>22cd9873-1d71-4384-b63c-9d5a24683d34</v>
+        <v>c4ab81e2-9452-4251-95f6-6e3a309b04fa</v>
       </c>
       <c r="BK31" t="str">
         <v>Accepted</v>
@@ -5213,30 +5219,30 @@
         <v/>
       </c>
       <c r="BM31" t="str">
-        <v>warren.ngahankinda@gmail.com</v>
+        <v>matheoflin@gmail.com</v>
       </c>
       <c r="BN31" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/w_ngahankinda_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fw%5Fngahankinda%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;viewid=8456c5ff%2Da254%2D484b%2Db85d%2D351f906110b6</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_flin_e2c-grandlille_fr/IgB6V-bIRQaFR5chZex-OPnXAe4WCCcv9ICxT3vvMB1-2J8?e=uzHAj0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>78080</v>
+        <v>81011</v>
       </c>
       <c r="B32" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C32" t="str">
-        <v>E-SILVA</v>
+        <v>PENNEL--SANCHEZ</v>
       </c>
       <c r="D32" t="str">
-        <v>Morgane</v>
+        <v>Diego</v>
       </c>
       <c r="E32" t="str">
-        <v>m.esilva@e2c-grandlille.fr</v>
+        <v>d.pennelsanchez@e2c-grandlille.fr</v>
       </c>
       <c r="F32" t="str">
-        <v>0618802553</v>
+        <v>0612562905</v>
       </c>
       <c r="G32" t="str">
         <v>Grand Lille</v>
@@ -5244,41 +5250,35 @@
       <c r="H32" t="str">
         <v>Lille</v>
       </c>
-      <c r="I32" t="str">
-        <v>Assistant / Assistante dentaire, Aide-préparateur / Aide-préparatrice en pharmacie</v>
-      </c>
-      <c r="J32" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
-      </c>
       <c r="K32" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L32" t="str">
-        <v>référés German</v>
+        <v>référés Anne</v>
       </c>
       <c r="M32" t="str">
         <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O32" t="str">
-        <v>LEON QUERO German</v>
+        <v>CAPEAU Anne</v>
       </c>
       <c r="P32">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q32">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R32" s="1">
-        <v>37807</v>
+        <v>39277</v>
       </c>
       <c r="T32" t="str">
-        <v>ROUBAIX</v>
+        <v>LILLE</v>
       </c>
       <c r="U32" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W32" t="str">
-        <v>11 Rue Abélard</v>
+        <v>5 Rue Louis Braille</v>
       </c>
       <c r="X32" t="str">
         <v>59000</v>
@@ -5296,7 +5296,7 @@
         <v>NON</v>
       </c>
       <c r="AD32" t="str">
-        <v>3 non validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE32" t="str">
         <v>Non</v>
@@ -5317,55 +5317,40 @@
         <v>Non</v>
       </c>
       <c r="AK32" t="str">
-        <v>181h45m</v>
+        <v>220h</v>
       </c>
       <c r="AL32" t="str">
-        <v>107h</v>
+        <v>114h45m</v>
       </c>
       <c r="AM32" t="str">
-        <v>29h</v>
+        <v>121h30m</v>
       </c>
       <c r="AN32" s="1">
-        <v>46090.61877314815</v>
+        <v>46090.62510416667</v>
       </c>
       <c r="AO32" s="1">
-        <v>46133.48333333333</v>
+        <v>46168.59652777778</v>
       </c>
       <c r="AP32" s="1">
-        <v>46365.39444444444</v>
+        <v>46365.39166666667</v>
       </c>
       <c r="AU32" s="1">
-        <v>46049.652083333334</v>
+        <v>46063.67083333333</v>
       </c>
       <c r="AV32" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Wazemmes</v>
-      </c>
-      <c r="AW32" t="str">
-        <v>Laura TERRA</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
       </c>
       <c r="AX32" s="1">
-        <v>46042.65277777778</v>
-      </c>
-      <c r="AY32" t="str">
-        <v>l.terra@lilleavenirs.fr</v>
-      </c>
-      <c r="AZ32" t="str">
-        <v>0618802553</v>
+        <v>46063.67222222222</v>
       </c>
       <c r="BA32" t="str">
         <v>NON</v>
       </c>
       <c r="BG32" t="str">
-        <v>11225</v>
-      </c>
-      <c r="BH32" s="1">
-        <v>45742.041666666664</v>
-      </c>
-      <c r="BI32" t="str">
-        <v>5760794H</v>
+        <v>11221</v>
       </c>
       <c r="BJ32" t="str">
-        <v>a9316cd8-42e1-4241-a4ce-7d5c46d38002</v>
+        <v>fa5cc185-0aaa-4c56-b1eb-36e11417a8e0</v>
       </c>
       <c r="BK32" t="str">
         <v>Accepted</v>
@@ -5374,30 +5359,30 @@
         <v/>
       </c>
       <c r="BM32" t="str">
-        <v>esilvanur@gmail.com</v>
+        <v>d.pennelsanchez@gmail.com</v>
       </c>
       <c r="BN32" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_esilva_e2c-grandlille_fr/IgC9F9kli3qWS5zmL6jJlG-6Aff0MPqxZJk1cJvyrJxqPDE?e=TBTqbq</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/d_pennelsanchez_e2c-grandlille_fr/IgDk-wMJpvETRojNqPgmxmqTAQKIMGTF8c_P_od_ASztqZE?e=j9xR63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>78073</v>
+        <v>80998</v>
       </c>
       <c r="B33" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C33" t="str">
-        <v>BENZIZOUN</v>
+        <v>LECLERCQ</v>
       </c>
       <c r="D33" t="str">
-        <v>Rayane</v>
+        <v>Erika</v>
       </c>
       <c r="E33" t="str">
-        <v>r.benzizoun@e2c-grandlille.fr</v>
+        <v>e.leclercq@e2c-grandlille.fr</v>
       </c>
       <c r="F33" t="str">
-        <v>0618533946</v>
+        <v>0766112078</v>
       </c>
       <c r="G33" t="str">
         <v>Grand Lille</v>
@@ -5406,7 +5391,7 @@
         <v>Lille</v>
       </c>
       <c r="I33" t="str">
-        <v>Animateur socio-sportif / Animatrice socio-sportive, Organisateur / Organisatrice d'activités événementielles</v>
+        <v>Vendeur / Vendeuse en prêt-à-porter, Agent territorial spécialisé / Agente territoriale spécialisée des écoles maternelles (ATSEM)</v>
       </c>
       <c r="J33" t="str">
         <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
@@ -5418,19 +5403,19 @@
         <v>référés German</v>
       </c>
       <c r="M33" t="str">
-        <v>2602/février 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O33" t="str">
         <v>LEON QUERO German</v>
       </c>
       <c r="P33">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q33">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R33" s="1">
-        <v>38381</v>
+        <v>39084</v>
       </c>
       <c r="T33" t="str">
         <v>LILLE</v>
@@ -5438,14 +5423,11 @@
       <c r="U33" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="W33" t="str">
-        <v>5 Avenue du 18 Juin</v>
-      </c>
       <c r="X33" t="str">
-        <v>59790</v>
+        <v>59830</v>
       </c>
       <c r="Y33" t="str">
-        <v>Ronchin</v>
+        <v>Cysoing</v>
       </c>
       <c r="Z33" t="str">
         <v>Non</v>
@@ -5454,10 +5436,10 @@
         <v>Non</v>
       </c>
       <c r="AC33" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD33" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE33" t="str">
         <v>Non</v>
@@ -5478,40 +5460,49 @@
         <v>Non</v>
       </c>
       <c r="AK33" t="str">
-        <v>302h</v>
+        <v>273h45m</v>
       </c>
       <c r="AL33" t="str">
-        <v>203h</v>
+        <v>84h</v>
       </c>
       <c r="AM33" t="str">
-        <v>22h45m</v>
+        <v>93h45m</v>
       </c>
       <c r="AN33" s="1">
-        <v>46055.68449074074</v>
+        <v>46090.62385416667</v>
       </c>
       <c r="AO33" s="1">
-        <v>46133.459027777775</v>
+        <v>46168.47222222222</v>
       </c>
       <c r="AP33" s="1">
-        <v>46328.49513888889</v>
+        <v>46365.402083333334</v>
       </c>
       <c r="AU33" s="1">
-        <v>46049.64166666667</v>
+        <v>46063.65833333333</v>
       </c>
       <c r="AV33" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
+      </c>
+      <c r="AW33" t="str">
+        <v>Anne BRACKE</v>
       </c>
       <c r="AX33" s="1">
-        <v>46042.64236111111</v>
+        <v>46057.65972222222</v>
+      </c>
+      <c r="AY33" t="str">
+        <v>a.bracke@impulsions-ms.fr</v>
+      </c>
+      <c r="AZ33" t="str">
+        <v>0754383009</v>
       </c>
       <c r="BA33" t="str">
         <v>NON</v>
       </c>
       <c r="BG33" t="str">
-        <v>10040</v>
+        <v>11226</v>
       </c>
       <c r="BJ33" t="str">
-        <v>977534d8-4cdc-42ad-bbfd-9426a5c2db02</v>
+        <v>d9df52f8-6a24-4a90-9003-27aa8d86d290</v>
       </c>
       <c r="BK33" t="str">
         <v>Accepted</v>
@@ -5520,30 +5511,30 @@
         <v/>
       </c>
       <c r="BM33" t="str">
-        <v/>
+        <v>erikaleclercq1@icloud.com</v>
       </c>
       <c r="BN33" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_leclercq_e2c-grandlille_fr/IgAfFOi3_77JT4H4CkCBchcYAX0WO8D1_y2wwL3Il2VkRQk?e=GdaSyd</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>77911</v>
+        <v>80995</v>
       </c>
       <c r="B34" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C34" t="str">
-        <v>FAUCON</v>
+        <v>CADET</v>
       </c>
       <c r="D34" t="str">
-        <v>Lona</v>
+        <v>Maxence</v>
       </c>
       <c r="E34" t="str">
-        <v>l.faucon@e2c-grandlille.fr</v>
+        <v>m.cadet@e2c-grandlille.fr</v>
       </c>
       <c r="F34" t="str">
-        <v>0743604802</v>
+        <v>0749398136</v>
       </c>
       <c r="G34" t="str">
         <v>Grand Lille</v>
@@ -5551,44 +5542,41 @@
       <c r="H34" t="str">
         <v>Lille</v>
       </c>
-      <c r="I34" t="str">
-        <v>Pâtissier / Pâtissière</v>
-      </c>
       <c r="K34" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L34" t="str">
-        <v>référés Camille</v>
+        <v>référés Anne</v>
       </c>
       <c r="M34" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2604/avril 2026 LIL</v>
       </c>
       <c r="O34" t="str">
-        <v>PEAU Camille</v>
+        <v>CAPEAU Anne</v>
       </c>
       <c r="P34">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q34">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R34" s="1">
-        <v>38443</v>
+        <v>39023</v>
       </c>
       <c r="T34" t="str">
-        <v>AMIENS</v>
+        <v>PERONNE</v>
       </c>
       <c r="U34" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W34" t="str">
-        <v>11 Rue du Docteur Calmette</v>
+        <v>2 Place de la République (Hellemmes)</v>
       </c>
       <c r="X34" t="str">
-        <v>59120</v>
+        <v>59260</v>
       </c>
       <c r="Y34" t="str">
-        <v>Loos</v>
+        <v>Lille</v>
       </c>
       <c r="Z34" t="str">
         <v>Non</v>
@@ -5597,10 +5585,10 @@
         <v>Non</v>
       </c>
       <c r="AC34" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD34" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE34" t="str">
         <v>Non</v>
@@ -5621,55 +5609,55 @@
         <v>Non</v>
       </c>
       <c r="AK34" t="str">
-        <v>190h</v>
+        <v>98h30m</v>
       </c>
       <c r="AL34" t="str">
-        <v>222h</v>
+        <v>84h</v>
       </c>
       <c r="AM34" t="str">
-        <v>109h15m</v>
+        <v>170h15m</v>
       </c>
       <c r="AN34" s="1">
-        <v>46063.60461805556</v>
+        <v>46125.59275462963</v>
       </c>
       <c r="AO34" s="1">
-        <v>46098.6125</v>
+        <v>46168.5</v>
       </c>
       <c r="AP34" s="1">
-        <v>46336.506944444445</v>
+        <v>46400.70277777778</v>
       </c>
       <c r="AU34" s="1">
-        <v>46042.64027777778</v>
+        <v>46063.64444444444</v>
       </c>
       <c r="AV34" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne de Loos-</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Hellemmes</v>
       </c>
       <c r="AW34" t="str">
-        <v>Amandine HOCQ</v>
+        <v>Jeanine GORNIAK</v>
       </c>
       <c r="AX34" s="1">
-        <v>46034.64166666667</v>
+        <v>46057.64722222222</v>
       </c>
       <c r="AY34" t="str">
-        <v>ahocq@impulsions-ms.fr</v>
+        <v>j.gorniak@lilleavenirs.fr</v>
       </c>
       <c r="AZ34" t="str">
-        <v>0651230755</v>
+        <v>0762748393</v>
       </c>
       <c r="BA34" t="str">
         <v>NON</v>
       </c>
       <c r="BG34" t="str">
-        <v>10280</v>
+        <v>14727</v>
       </c>
       <c r="BH34" s="1">
-        <v>45125.083333333336</v>
+        <v>46056.041666666664</v>
       </c>
       <c r="BI34" t="str">
-        <v>4149594D</v>
+        <v>5890226V</v>
       </c>
       <c r="BJ34" t="str">
-        <v>ebe8947c-a7eb-442a-936d-3ce420cd3105</v>
+        <v>12270a9d-bcae-4b4d-a4d0-4c5c297db741</v>
       </c>
       <c r="BK34" t="str">
         <v>Accepted</v>
@@ -5678,30 +5666,30 @@
         <v/>
       </c>
       <c r="BM34" t="str">
-        <v>lonadelgove@gmail.com</v>
+        <v>maxence.cadet2006@gmail.com</v>
       </c>
       <c r="BN34" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_faucon_e2c-grandlille_fr/IgCBWHorMw9TSLxaRxwDCqeHAVUBBdUqM2T1bLmL6rqyHH0?e=P6Jgc5</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_cadet_e2c-grandlille_fr/IgDVd4iynutcQr0cxwqIbWnOAdKBvgGOm50gdJnaKzEWyS8?e=fU0GGr</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>77896</v>
+        <v>78083</v>
       </c>
       <c r="B35" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C35" t="str">
-        <v>GACHTOURI</v>
+        <v>NGAHAN KINDA</v>
       </c>
       <c r="D35" t="str">
-        <v>Myriam</v>
+        <v>Warren</v>
       </c>
       <c r="E35" t="str">
-        <v>m.gachtouri@e2c-grandlille.fr</v>
+        <v>w.ngahankinda@e2c-grandlille.fr</v>
       </c>
       <c r="F35" t="str">
-        <v>0775824140</v>
+        <v>06 44 73 56 78</v>
       </c>
       <c r="G35" t="str">
         <v>Grand Lille</v>
@@ -5716,40 +5704,43 @@
         <v>Je sais</v>
       </c>
       <c r="L35" t="str">
-        <v>référés Sura</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M35" t="str">
         <v>2602/Graines de pâtissier 2026 LIL</v>
       </c>
       <c r="O35" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P35">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q35">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R35" s="1">
-        <v>38731</v>
+        <v>38295</v>
       </c>
       <c r="T35" t="str">
-        <v>ROUBAIX</v>
+        <v>LILLE</v>
       </c>
       <c r="U35" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W35" t="str">
-        <v>97b Avenue Jean Jaurès</v>
+        <v>23 Rue de l'Amiral Courbet</v>
       </c>
       <c r="X35" t="str">
-        <v>59790</v>
+        <v>59800</v>
       </c>
       <c r="Y35" t="str">
-        <v>Ronchin</v>
+        <v>Lille</v>
       </c>
       <c r="Z35" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA35" t="str">
+        <v>QN05973M</v>
       </c>
       <c r="AB35" t="str">
         <v>Non</v>
@@ -5757,6 +5748,9 @@
       <c r="AC35" t="str">
         <v>NON</v>
       </c>
+      <c r="AD35" t="str">
+        <v>3 validé</v>
+      </c>
       <c r="AE35" t="str">
         <v>Non</v>
       </c>
@@ -5776,49 +5770,49 @@
         <v>Non</v>
       </c>
       <c r="AK35" t="str">
-        <v>135h</v>
+        <v>313h</v>
       </c>
       <c r="AL35" t="str">
-        <v>175h</v>
+        <v>214h</v>
       </c>
       <c r="AM35" t="str">
-        <v>140h30m</v>
+        <v>29h15m</v>
       </c>
       <c r="AN35" s="1">
-        <v>46063.60525462963</v>
+        <v>46063.60650462963</v>
       </c>
       <c r="AO35" s="1">
-        <v>46098.61319444444</v>
+        <v>46098.61597222222</v>
       </c>
       <c r="AP35" s="1">
-        <v>46336.506944444445</v>
+        <v>46336.50763888889</v>
       </c>
       <c r="AU35" s="1">
-        <v>46042.611805555556</v>
+        <v>46049.654861111114</v>
       </c>
       <c r="AV35" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Lomme</v>
+        <v>MISSION LOCALE DE LILLE- LILLE AVENIRS -Siège-</v>
       </c>
       <c r="AW35" t="str">
-        <v>Marie BOUREZ</v>
+        <v>Catherine TAQUIN ROSIAUX</v>
       </c>
       <c r="AX35" s="1">
-        <v>46028.6125</v>
+        <v>46043.65625</v>
       </c>
       <c r="AY35" t="str">
-        <v>m.bourez@lilleavenirs.fr</v>
+        <v>c.rosiaux@lilleavenirs.fr</v>
       </c>
       <c r="AZ35" t="str">
-        <v>0762771413</v>
+        <v>0669209968</v>
       </c>
       <c r="BA35" t="str">
         <v>NON</v>
       </c>
       <c r="BG35" t="str">
-        <v>10408</v>
+        <v>10415</v>
       </c>
       <c r="BJ35" t="str">
-        <v>f163d0ed-bfda-4dc0-8ac9-14e461b05a2b</v>
+        <v>22cd9873-1d71-4384-b63c-9d5a24683d34</v>
       </c>
       <c r="BK35" t="str">
         <v>Accepted</v>
@@ -5827,30 +5821,30 @@
         <v/>
       </c>
       <c r="BM35" t="str">
-        <v>myriam.gachtouri@icloud.com</v>
+        <v>warren.ngahankinda@gmail.com</v>
       </c>
       <c r="BN35" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_gachtouri_e2c-grandlille_fr/IgDuEI3tHvvaSq3DTOTU6HI3AeLFIpflebJTk-HAY0EhI1I?e=Ho5MfW</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/personal/w_ngahankinda_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fw%5Fngahankinda%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;viewid=8456c5ff%2Da254%2D484b%2Db85d%2D351f906110b6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>77891</v>
+        <v>78080</v>
       </c>
       <c r="B36" t="str">
         <v>Femme</v>
       </c>
       <c r="C36" t="str">
-        <v>HAMKACHE</v>
+        <v>E-SILVA</v>
       </c>
       <c r="D36" t="str">
-        <v>Soraya</v>
+        <v>Morgane</v>
       </c>
       <c r="E36" t="str">
-        <v>s.hamkache@e2c-grandlille.fr</v>
+        <v>m.esilva@e2c-grandlille.fr</v>
       </c>
       <c r="F36" t="str">
-        <v>07 44 78 79 32</v>
+        <v>0618802553</v>
       </c>
       <c r="G36" t="str">
         <v>Grand Lille</v>
@@ -5859,40 +5853,46 @@
         <v>Lille</v>
       </c>
       <c r="I36" t="str">
-        <v>Pâtissier / Pâtissière</v>
+        <v>Assistant / Assistante dentaire, Aide-préparateur / Aide-préparatrice en pharmacie, Auxiliaire de soins aux animaux</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
       </c>
       <c r="K36" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L36" t="str">
-        <v>référés Lucie</v>
+        <v>référés German</v>
       </c>
       <c r="M36" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O36" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P36">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q36">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R36" s="1">
-        <v>40124</v>
+        <v>37807</v>
       </c>
       <c r="T36" t="str">
-        <v>LILLE</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U36" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="W36" t="str">
+        <v>11 Rue Abélard</v>
+      </c>
       <c r="X36" t="str">
-        <v>59491</v>
+        <v>59000</v>
       </c>
       <c r="Y36" t="str">
-        <v>Villeneuve-d'Ascq</v>
+        <v>Lille</v>
       </c>
       <c r="Z36" t="str">
         <v>Non</v>
@@ -5904,7 +5904,7 @@
         <v>NON</v>
       </c>
       <c r="AD36" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE36" t="str">
         <v>Non</v>
@@ -5925,64 +5925,55 @@
         <v>Non</v>
       </c>
       <c r="AK36" t="str">
-        <v>216h15m</v>
+        <v>268h</v>
       </c>
       <c r="AL36" t="str">
-        <v>224h</v>
+        <v>212h</v>
       </c>
       <c r="AM36" t="str">
-        <v>72h45m</v>
+        <v>96h30m</v>
       </c>
       <c r="AN36" s="1">
-        <v>46063.60599537037</v>
+        <v>46090.61877314815</v>
       </c>
       <c r="AO36" s="1">
-        <v>46098.614583333336</v>
+        <v>46133.48333333333</v>
       </c>
       <c r="AP36" s="1">
-        <v>46336.50763888889</v>
+        <v>46365.39444444444</v>
       </c>
       <c r="AU36" s="1">
-        <v>46042.603472222225</v>
+        <v>46049.652083333334</v>
       </c>
       <c r="AV36" t="str">
-        <v>Centre social DE L'ALMA</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Wazemmes</v>
       </c>
       <c r="AW36" t="str">
-        <v>Ghalia OFAB</v>
+        <v>Laura TERRA</v>
       </c>
       <c r="AX36" s="1">
-        <v>46020.60555555556</v>
+        <v>46042.65277777778</v>
       </c>
       <c r="AY36" t="str">
-        <v>g.ogab@csalma.org</v>
+        <v>l.terra@lilleavenirs.fr</v>
       </c>
       <c r="AZ36" t="str">
-        <v>0770012518</v>
+        <v>0618802553</v>
       </c>
       <c r="BA36" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB36" t="str">
-        <v>HAMKACHE</v>
-      </c>
-      <c r="BC36" t="str">
-        <v>Malika</v>
-      </c>
-      <c r="BD36" t="str">
-        <v>2 RUE DE LA BRUYERE 59491 VILLENEUVE D'ASCQ</v>
-      </c>
-      <c r="BE36" t="str">
-        <v>0626348393</v>
-      </c>
-      <c r="BF36" t="str">
-        <v>m.ilka.59@hotmail.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG36" t="str">
-        <v>10270</v>
+        <v>11225</v>
+      </c>
+      <c r="BH36" s="1">
+        <v>45742.041666666664</v>
+      </c>
+      <c r="BI36" t="str">
+        <v>5760794H</v>
       </c>
       <c r="BJ36" t="str">
-        <v>72456382-6e18-44e1-b664-80a8f629f216</v>
+        <v>a9316cd8-42e1-4241-a4ce-7d5c46d38002</v>
       </c>
       <c r="BK36" t="str">
         <v>Accepted</v>
@@ -5991,30 +5982,30 @@
         <v/>
       </c>
       <c r="BM36" t="str">
-        <v>soraya.hamkache@outlook.com</v>
+        <v>esilvanur@gmail.com</v>
       </c>
       <c r="BN36" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/s_hamkache_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fs%5Fhamkache%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;ga=1&amp;startedResponseCatch=true</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_esilva_e2c-grandlille_fr/IgC9F9kli3qWS5zmL6jJlG-6Aff0MPqxZJk1cJvyrJxqPDE?e=TBTqbq</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>77616</v>
+        <v>78073</v>
       </c>
       <c r="B37" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C37" t="str">
-        <v>SCHARER</v>
+        <v>BENZIZOUN</v>
       </c>
       <c r="D37" t="str">
-        <v>Lola</v>
+        <v>Rayane</v>
       </c>
       <c r="E37" t="str">
-        <v>l.scharer@e2c-grandlille.fr</v>
+        <v>r.benzizoun@e2c-grandlille.fr</v>
       </c>
       <c r="F37" t="str">
-        <v>0663966961</v>
+        <v>0618533946</v>
       </c>
       <c r="G37" t="str">
         <v>Grand Lille</v>
@@ -6023,28 +6014,31 @@
         <v>Lille</v>
       </c>
       <c r="I37" t="str">
-        <v>Agent / Agente de voyages</v>
+        <v>Animateur socio-sportif / Animatrice socio-sportive, Organisateur / Organisatrice d'activités événementielles</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat d'apprentissage</v>
       </c>
       <c r="K37" t="str">
-        <v>J'explore</v>
+        <v>Je sais</v>
       </c>
       <c r="L37" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés German</v>
       </c>
       <c r="M37" t="str">
         <v>2602/février 2026 LIL</v>
       </c>
       <c r="O37" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R37" s="1">
-        <v>38632</v>
+        <v>38381</v>
       </c>
       <c r="T37" t="str">
         <v>LILLE</v>
@@ -6053,13 +6047,13 @@
         <v>FRANCAISE</v>
       </c>
       <c r="W37" t="str">
-        <v>22 Rue du Général Koenig</v>
+        <v>5 Avenue du 18 Juin</v>
       </c>
       <c r="X37" t="str">
-        <v>59136</v>
+        <v>59790</v>
       </c>
       <c r="Y37" t="str">
-        <v>Wavrin</v>
+        <v>Ronchin</v>
       </c>
       <c r="Z37" t="str">
         <v>Non</v>
@@ -6071,7 +6065,7 @@
         <v>NON</v>
       </c>
       <c r="AD37" t="str">
-        <v>3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE37" t="str">
         <v>Non</v>
@@ -6092,46 +6086,40 @@
         <v>Non</v>
       </c>
       <c r="AK37" t="str">
-        <v>296h30m</v>
+        <v>438h45m</v>
       </c>
       <c r="AL37" t="str">
-        <v>203h30m</v>
+        <v>298h</v>
       </c>
       <c r="AM37" t="str">
-        <v>29h</v>
+        <v>19h30m</v>
       </c>
       <c r="AN37" s="1">
-        <v>46055.69107638889</v>
+        <v>46055.68449074074</v>
       </c>
       <c r="AO37" s="1">
-        <v>46098.58819444444</v>
+        <v>46133.459027777775</v>
       </c>
       <c r="AP37" s="1">
-        <v>46328.501388888886</v>
+        <v>46328.49513888889</v>
       </c>
       <c r="AU37" s="1">
-        <v>46042.48819444444</v>
+        <v>46049.64166666667</v>
       </c>
       <c r="AV37" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne Wavrin-</v>
-      </c>
-      <c r="AW37" t="str">
-        <v>Hervé DUMEZ</v>
+        <v>En direct</v>
       </c>
       <c r="AX37" s="1">
-        <v>46042.49097222222</v>
-      </c>
-      <c r="AY37" t="str">
-        <v>hdumez@impulsions-ms.fr</v>
+        <v>46042.64236111111</v>
       </c>
       <c r="BA37" t="str">
         <v>NON</v>
       </c>
       <c r="BG37" t="str">
-        <v>10036</v>
+        <v>10040</v>
       </c>
       <c r="BJ37" t="str">
-        <v>8e683b97-0094-41a4-acdc-21200e637ad2</v>
+        <v>977534d8-4cdc-42ad-bbfd-9426a5c2db02</v>
       </c>
       <c r="BK37" t="str">
         <v>Accepted</v>
@@ -6148,22 +6136,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>77612</v>
+        <v>77616</v>
       </c>
       <c r="B38" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C38" t="str">
-        <v>DECARPENTRIES</v>
+        <v>SCHARER</v>
       </c>
       <c r="D38" t="str">
-        <v>Maxence</v>
+        <v>Lola</v>
       </c>
       <c r="E38" t="str">
-        <v>m.decarpentries@e2c-grandlille.fr</v>
+        <v>l.scharer@e2c-grandlille.fr</v>
       </c>
       <c r="F38" t="str">
-        <v>07 49 06 79 95</v>
+        <v>0663966961</v>
       </c>
       <c r="G38" t="str">
         <v>Grand Lille</v>
@@ -6172,49 +6160,46 @@
         <v>Lille</v>
       </c>
       <c r="I38" t="str">
-        <v>Mécanicien / Mécanicienne automobile, Employé / Employée de libre-service</v>
+        <v>Agent / Agente de voyages</v>
       </c>
       <c r="K38" t="str">
         <v>Je sais</v>
       </c>
       <c r="L38" t="str">
-        <v>référés Lucie</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M38" t="str">
         <v>2602/février 2026 LIL</v>
       </c>
       <c r="O38" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P38">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q38">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R38" s="1">
-        <v>37163</v>
+        <v>38632</v>
       </c>
       <c r="T38" t="str">
-        <v>LENS</v>
+        <v>LILLE</v>
       </c>
       <c r="U38" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W38" t="str">
-        <v>44 Rue Brézin</v>
+        <v>22 Rue du Général Koenig</v>
       </c>
       <c r="X38" t="str">
-        <v>59100</v>
+        <v>59136</v>
       </c>
       <c r="Y38" t="str">
-        <v>Roubaix</v>
+        <v>Wavrin</v>
       </c>
       <c r="Z38" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA38" t="str">
-        <v>QN05980M</v>
+        <v>Non</v>
       </c>
       <c r="AB38" t="str">
         <v>Non</v>
@@ -6223,7 +6208,7 @@
         <v>NON</v>
       </c>
       <c r="AD38" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE38" t="str">
         <v>Non</v>
@@ -6244,40 +6229,46 @@
         <v>Non</v>
       </c>
       <c r="AK38" t="str">
-        <v>167h15m</v>
+        <v>367h15m</v>
       </c>
       <c r="AL38" t="str">
-        <v>133h</v>
+        <v>231h30m</v>
       </c>
       <c r="AM38" t="str">
-        <v>116h30m</v>
+        <v>96h45m</v>
       </c>
       <c r="AN38" s="1">
-        <v>46055.68681712963</v>
+        <v>46055.69107638889</v>
       </c>
       <c r="AO38" s="1">
-        <v>46098.58263888889</v>
+        <v>46098.58819444444</v>
       </c>
       <c r="AP38" s="1">
-        <v>46328.49791666667</v>
+        <v>46328.501388888886</v>
       </c>
       <c r="AU38" s="1">
-        <v>46042.48263888889</v>
+        <v>46042.48819444444</v>
       </c>
       <c r="AV38" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne Wavrin-</v>
+      </c>
+      <c r="AW38" t="str">
+        <v>Hervé DUMEZ</v>
       </c>
       <c r="AX38" s="1">
-        <v>46038.48333333333</v>
+        <v>46042.49097222222</v>
+      </c>
+      <c r="AY38" t="str">
+        <v>hdumez@impulsions-ms.fr</v>
       </c>
       <c r="BA38" t="str">
         <v>NON</v>
       </c>
       <c r="BG38" t="str">
-        <v>10354</v>
+        <v>10036</v>
       </c>
       <c r="BJ38" t="str">
-        <v>b0aa233a-07eb-4aaf-ad90-1dac91bb0a1d</v>
+        <v>8e683b97-0094-41a4-acdc-21200e637ad2</v>
       </c>
       <c r="BK38" t="str">
         <v>Accepted</v>
@@ -6289,7 +6280,7 @@
         <v/>
       </c>
       <c r="BN38" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/m_decarpentries_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fm%5Fdecarpentries%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;ga=1&amp;startedResponseCatch=true</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6318,7 +6309,7 @@
         <v>Lille</v>
       </c>
       <c r="I39" t="str">
-        <v>Secrétaire de mairie</v>
+        <v>Agent administratif / Agente administrative de l'Etat</v>
       </c>
       <c r="K39" t="str">
         <v>J'ai des idées</v>
@@ -6333,7 +6324,7 @@
         <v>DERCOURT Lucie</v>
       </c>
       <c r="P39">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q39">
         <v>24</v>
@@ -6387,13 +6378,13 @@
         <v>Non</v>
       </c>
       <c r="AK39" t="str">
-        <v>171h15m</v>
+        <v>241h45m</v>
       </c>
       <c r="AL39" t="str">
-        <v>147h</v>
+        <v>247h</v>
       </c>
       <c r="AM39" t="str">
-        <v>38h15m</v>
+        <v>99h45m</v>
       </c>
       <c r="AN39" s="1">
         <v>46090.626388888886</v>
@@ -6542,13 +6533,13 @@
         <v>Non</v>
       </c>
       <c r="AK40" t="str">
-        <v>209h30m</v>
+        <v>329h</v>
       </c>
       <c r="AL40" t="str">
-        <v>146h20m</v>
+        <v>211h20m</v>
       </c>
       <c r="AM40" t="str">
-        <v>22h30m</v>
+        <v>38h30m</v>
       </c>
       <c r="AN40" s="1">
         <v>46090.625706018516</v>
@@ -6631,10 +6622,10 @@
         <v>Employé / Employée de libre-service</v>
       </c>
       <c r="K41" t="str">
-        <v>Je sais</v>
+        <v>J'y vais</v>
       </c>
       <c r="L41" t="str">
-        <v>référés Fanny</v>
+        <v>référés Laurence</v>
       </c>
       <c r="M41" t="str">
         <v>2603/mars 2026 LIL</v>
@@ -6697,13 +6688,13 @@
         <v>Non</v>
       </c>
       <c r="AK41" t="str">
-        <v>204h30m</v>
+        <v>311h15m</v>
       </c>
       <c r="AL41" t="str">
-        <v>145h</v>
+        <v>212h30m</v>
       </c>
       <c r="AM41" t="str">
-        <v>4h45m</v>
+        <v>36h15m</v>
       </c>
       <c r="AN41" s="1">
         <v>46090.622245370374</v>
@@ -6795,7 +6786,7 @@
         <v>Lille</v>
       </c>
       <c r="I42" t="str">
-        <v>Développeur / Développeuse - jeux vidéo, Employé / Employée de libre-service</v>
+        <v>Routier / Routière</v>
       </c>
       <c r="K42" t="str">
         <v>J'ai des idées</v>
@@ -6864,13 +6855,13 @@
         <v>Non</v>
       </c>
       <c r="AK42" t="str">
-        <v>284h15m</v>
+        <v>375h45m</v>
       </c>
       <c r="AL42" t="str">
-        <v>168h30m</v>
+        <v>196h30m</v>
       </c>
       <c r="AM42" t="str">
-        <v>40h15m</v>
+        <v>79h15m</v>
       </c>
       <c r="AN42" s="1">
         <v>46055.68803240741</v>
@@ -7013,13 +7004,13 @@
         <v>Non</v>
       </c>
       <c r="AK43" t="str">
-        <v>188h30m</v>
+        <v>205h15m</v>
       </c>
       <c r="AL43" t="str">
         <v>151h</v>
       </c>
       <c r="AM43" t="str">
-        <v>107h45m</v>
+        <v>146h45m</v>
       </c>
       <c r="AN43" s="1">
         <v>46063.60815972222</v>
@@ -7072,22 +7063,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>77247</v>
+        <v>57186</v>
       </c>
       <c r="B44" t="str">
         <v>Femme</v>
       </c>
       <c r="C44" t="str">
-        <v>DUGARDIN</v>
+        <v>MAZOUNI</v>
       </c>
       <c r="D44" t="str">
-        <v>Maëlla</v>
+        <v>Aya</v>
       </c>
       <c r="E44" t="str">
-        <v>m.dugardin@e2c-grandlille.fr</v>
+        <v>a.mazouni@e2c-grandlille.fr</v>
       </c>
       <c r="F44" t="str">
-        <v>0745720879</v>
+        <v>0663485572</v>
       </c>
       <c r="G44" t="str">
         <v>Grand Lille</v>
@@ -7096,43 +7087,49 @@
         <v>Lille</v>
       </c>
       <c r="I44" t="str">
-        <v>Pâtissier / Pâtissière</v>
+        <v>Technicien / Technicienne analyse-contrôle en industrie chimique, Assistant / Assistante de service social</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Je sais</v>
       </c>
       <c r="L44" t="str">
         <v>référés Gwenaelle</v>
       </c>
       <c r="M44" t="str">
-        <v>2602/Graines de pâtissier 2026 LIL</v>
+        <v>2602/février 2026 LIL</v>
       </c>
       <c r="O44" t="str">
         <v>GUYO Gwenaelle</v>
       </c>
       <c r="P44">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q44">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R44" s="1">
-        <v>39725</v>
+        <v>37174</v>
       </c>
       <c r="T44" t="str">
-        <v>SECLIN</v>
+        <v>BENI MESSOUS, ALGÉRIE</v>
       </c>
       <c r="U44" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W44" t="str">
-        <v>37 Rue Delemazure</v>
+        <v>5 5 Résidence Marcel Bertrand</v>
       </c>
       <c r="X44" t="str">
-        <v>59800</v>
+        <v>59790</v>
       </c>
       <c r="Y44" t="str">
-        <v>Lille</v>
+        <v>RONCHIN</v>
       </c>
       <c r="Z44" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA44" t="str">
+        <v>QN05979M</v>
       </c>
       <c r="AB44" t="str">
         <v>Non</v>
@@ -7141,7 +7138,7 @@
         <v>NON</v>
       </c>
       <c r="AD44" t="str">
-        <v>3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE44" t="str">
         <v>Non</v>
@@ -7156,70 +7153,46 @@
         <v>Non</v>
       </c>
       <c r="AI44" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AJ44" t="str">
         <v>Non</v>
       </c>
       <c r="AK44" t="str">
-        <v>167h45m</v>
+        <v>338h15m</v>
       </c>
       <c r="AL44" t="str">
-        <v>70h</v>
+        <v>184h</v>
       </c>
       <c r="AM44" t="str">
-        <v>84h</v>
+        <v>126h</v>
       </c>
       <c r="AN44" s="1">
-        <v>46063.60412037037</v>
+        <v>46055.688680555555</v>
       </c>
       <c r="AO44" s="1">
-        <v>46133.46388888889</v>
+        <v>46098.58541666667</v>
       </c>
       <c r="AP44" s="1">
-        <v>46336.50625</v>
+        <v>46328.5</v>
       </c>
       <c r="AU44" s="1">
-        <v>46028.433333333334</v>
+        <v>45965</v>
       </c>
       <c r="AV44" t="str">
-        <v>ITINERAIRES</v>
-      </c>
-      <c r="AW44" t="str">
-        <v>Charlotte FRANCOIS</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne Faches Thumesnil</v>
       </c>
       <c r="AX44" s="1">
-        <v>45996.44027777778</v>
-      </c>
-      <c r="AY44" t="str">
-        <v>charlotte.francois@itineraires.asso.fr</v>
-      </c>
-      <c r="AZ44" t="str">
-        <v>0659191206</v>
+        <v>45964</v>
       </c>
       <c r="BA44" t="str">
         <v>NON</v>
       </c>
-      <c r="BB44" t="str">
-        <v>FARRANDO éducatrice spécialisée</v>
-      </c>
-      <c r="BC44" t="str">
-        <v xml:space="preserve">Zoé </v>
-      </c>
-      <c r="BD44" t="str">
-        <v>27 Rue Delemazure 59260 HELLEMMES</v>
-      </c>
-      <c r="BE44" t="str">
-        <v>0623259857</v>
-      </c>
-      <c r="BF44" t="str">
-        <v>mecsspriethemera@asso-solfa.fr</v>
-      </c>
       <c r="BG44" t="str">
-        <v>10402</v>
+        <v>10071</v>
       </c>
       <c r="BJ44" t="str">
-        <v>61f663b2-681f-4738-985d-bf80a6524b7e</v>
+        <v>fa16f985-3d45-472b-a9eb-19920a3783cc</v>
       </c>
       <c r="BK44" t="str">
         <v>Accepted</v>
@@ -7228,30 +7201,30 @@
         <v/>
       </c>
       <c r="BM44" t="str">
-        <v>maella-dugardin04@icloud.com</v>
+        <v/>
       </c>
       <c r="BN44" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_dugardin_e2c-grandlille_fr/IgDU5k214WOoToipDlvj0ZdcAfihCP6zX3BQP7D4azg3088?e=nfBIIi</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>77176</v>
+        <v>56970</v>
       </c>
       <c r="B45" t="str">
         <v>Femme</v>
       </c>
       <c r="C45" t="str">
-        <v>AYAD</v>
+        <v>LEFRANCOIS</v>
       </c>
       <c r="D45" t="str">
-        <v>Lilia</v>
+        <v>Kloe</v>
       </c>
       <c r="E45" t="str">
-        <v>l.ayad@e2c-grandlille.fr</v>
+        <v>k.lefrancois@e2c-grandlille.fr</v>
       </c>
       <c r="F45" t="str">
-        <v>0626413638</v>
+        <v>07 67 79 32 58</v>
       </c>
       <c r="G45" t="str">
         <v>Grand Lille</v>
@@ -7260,43 +7233,43 @@
         <v>Lille</v>
       </c>
       <c r="I45" t="str">
-        <v>Vendeur / Vendeuse en accessoires de la personne</v>
+        <v>Auxiliaire de puériculture</v>
       </c>
       <c r="K45" t="str">
         <v>Je sais</v>
       </c>
       <c r="L45" t="str">
-        <v>référés Fanny</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M45" t="str">
         <v>2602/février 2026 LIL</v>
       </c>
       <c r="O45" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P45">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q45">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R45" s="1">
-        <v>37874</v>
+        <v>39595</v>
       </c>
       <c r="T45" t="str">
-        <v>AZAZEGA</v>
+        <v>LILLE, FRANCE</v>
       </c>
       <c r="U45" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W45" t="str">
-        <v>14 Ruelle Saint-Sauveur</v>
+        <v>140 140 Rue Henri Ghesquière</v>
       </c>
       <c r="X45" t="str">
-        <v>59800</v>
+        <v>59261</v>
       </c>
       <c r="Y45" t="str">
-        <v>Lille</v>
+        <v>WAHAGNIES</v>
       </c>
       <c r="Z45" t="str">
         <v>Non</v>
@@ -7308,10 +7281,10 @@
         <v>NON</v>
       </c>
       <c r="AD45" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE45" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF45" t="str">
         <v>Non</v>
@@ -7329,40 +7302,58 @@
         <v>Non</v>
       </c>
       <c r="AK45" t="str">
-        <v>186h45m</v>
+        <v>336h30m</v>
       </c>
       <c r="AL45" t="str">
-        <v>196h</v>
+        <v>117h30m</v>
       </c>
       <c r="AM45" t="str">
-        <v>129h30m</v>
+        <v>142h</v>
       </c>
       <c r="AN45" s="1">
-        <v>46055.68376157407</v>
+        <v>46055.687418981484</v>
       </c>
       <c r="AO45" s="1">
-        <v>46098.58263888889</v>
+        <v>46133.46111111111</v>
       </c>
       <c r="AP45" s="1">
-        <v>46328.49444444444</v>
+        <v>46328.498611111114</v>
       </c>
       <c r="AU45" s="1">
-        <v>46028.686111111114</v>
+        <v>45944</v>
       </c>
       <c r="AV45" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne d'Ostricourt</v>
+      </c>
+      <c r="AW45" t="str">
+        <v>M. Pascal GAMBIER - 06.81.64.53.27</v>
       </c>
       <c r="AX45" s="1">
-        <v>46028.68819444445</v>
+        <v>45943</v>
       </c>
       <c r="BA45" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB45" t="str">
+        <v>FIEVET</v>
+      </c>
+      <c r="BC45" t="str">
+        <v>Sylvia</v>
+      </c>
+      <c r="BD45" t="str">
+        <v>140 RUE HENRI GHESQUIERES 59261 WAHAGNIES</v>
+      </c>
+      <c r="BE45" t="str">
+        <v>0633919464</v>
+      </c>
+      <c r="BF45" t="str">
+        <v>vincsyl@live.fr</v>
       </c>
       <c r="BG45" t="str">
-        <v>10073</v>
+        <v>10068</v>
       </c>
       <c r="BJ45" t="str">
-        <v>298b4b80-7a1b-4528-8dba-cf288a0c30b3</v>
+        <v>bea7ca7b-c90a-4417-a113-1038a82451e3</v>
       </c>
       <c r="BK45" t="str">
         <v>Accepted</v>
@@ -7374,27 +7365,27 @@
         <v/>
       </c>
       <c r="BN45" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/personal/k_lefrancois_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fk%5Flefrancois%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;ga=1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>57186</v>
+        <v>55505</v>
       </c>
       <c r="B46" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C46" t="str">
-        <v>MAZOUNI</v>
+        <v>BERGOT</v>
       </c>
       <c r="D46" t="str">
-        <v>Aya</v>
+        <v>Etan</v>
       </c>
       <c r="E46" t="str">
-        <v>a.mazouni@e2c-grandlille.fr</v>
+        <v>e.bergot@e2c-grandlille.fr</v>
       </c>
       <c r="F46" t="str">
-        <v>0663485572</v>
+        <v>0685068151</v>
       </c>
       <c r="G46" t="str">
         <v>Grand Lille</v>
@@ -7403,49 +7394,46 @@
         <v>Lille</v>
       </c>
       <c r="I46" t="str">
-        <v>Technicien / Technicienne analyse-contrôle en industrie chimique, Assistant / Assistante de service social</v>
+        <v>Styliste, Coiffeur barbier / Coiffeuse barbière, Photographe</v>
       </c>
       <c r="K46" t="str">
         <v>Je sais</v>
       </c>
       <c r="L46" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés Camille</v>
       </c>
       <c r="M46" t="str">
-        <v>2602/février 2026 LIL</v>
+        <v>2603/mars 2026 LIL</v>
       </c>
       <c r="O46" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>PEAU Camille</v>
       </c>
       <c r="P46">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q46">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R46" s="1">
-        <v>37174</v>
+        <v>39659</v>
       </c>
       <c r="T46" t="str">
-        <v>BENI MESSOUS, ALGÉRIE</v>
+        <v>ROUBAIX, FRANCE</v>
       </c>
       <c r="U46" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W46" t="str">
-        <v>5 5 Résidence Marcel Bertrand</v>
+        <v>257 257 Rue Gustave Delory</v>
       </c>
       <c r="X46" t="str">
-        <v>59790</v>
+        <v>59830</v>
       </c>
       <c r="Y46" t="str">
-        <v>RONCHIN</v>
+        <v>CYSOING</v>
       </c>
       <c r="Z46" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA46" t="str">
-        <v>QN05979M</v>
+        <v>Non</v>
       </c>
       <c r="AB46" t="str">
         <v>Non</v>
@@ -7454,7 +7442,7 @@
         <v>NON</v>
       </c>
       <c r="AD46" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE46" t="str">
         <v>Non</v>
@@ -7475,40 +7463,61 @@
         <v>Non</v>
       </c>
       <c r="AK46" t="str">
-        <v>243h45m</v>
+        <v>232h15m</v>
       </c>
       <c r="AL46" t="str">
-        <v>119h</v>
+        <v>248h15m</v>
       </c>
       <c r="AM46" t="str">
-        <v>81h</v>
+        <v>120h30m</v>
       </c>
       <c r="AN46" s="1">
-        <v>46055.688680555555</v>
+        <v>46090.612604166665</v>
       </c>
       <c r="AO46" s="1">
-        <v>46098.58541666667</v>
+        <v>46133.47986111111</v>
       </c>
       <c r="AP46" s="1">
-        <v>46328.5</v>
+        <v>46365.39444444444</v>
       </c>
       <c r="AU46" s="1">
-        <v>45965</v>
+        <v>45944</v>
       </c>
       <c r="AV46" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne Faches Thumesnil</v>
+        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
+      </c>
+      <c r="AW46" t="str">
+        <v>Anne BRACKE</v>
       </c>
       <c r="AX46" s="1">
-        <v>45964</v>
+        <v>45940.507314814815</v>
+      </c>
+      <c r="AY46" t="str">
+        <v>abracke@impulsions-ms.fr</v>
       </c>
       <c r="BA46" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB46" t="str">
+        <v>MOUMA</v>
+      </c>
+      <c r="BC46" t="str">
+        <v>Nadia</v>
+      </c>
+      <c r="BD46" t="str">
+        <v>257 RUE GUSTAVE DELORY 59830 CYSOING</v>
+      </c>
+      <c r="BE46" t="str">
+        <v>0662616204</v>
+      </c>
+      <c r="BF46" t="str">
+        <v>nadia.mouma@gmail.com</v>
       </c>
       <c r="BG46" t="str">
-        <v>10071</v>
+        <v>11210</v>
       </c>
       <c r="BJ46" t="str">
-        <v>fa16f985-3d45-472b-a9eb-19920a3783cc</v>
+        <v>29b8879a-f898-4691-8488-913ee2c248b4</v>
       </c>
       <c r="BK46" t="str">
         <v>Accepted</v>
@@ -7517,30 +7526,30 @@
         <v/>
       </c>
       <c r="BM46" t="str">
-        <v/>
+        <v>etanbergot@gmail.com</v>
       </c>
       <c r="BN46" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_bergot_e2c-grandlille_fr/IgCve20h4StqTrrKv3PpmP6zAeOVafj36P10Fn8x6C5dnv8?e=tMYKs1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>56970</v>
+        <v>40005</v>
       </c>
       <c r="B47" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C47" t="str">
-        <v>LEFRANCOIS</v>
+        <v>DUBREUCQ</v>
       </c>
       <c r="D47" t="str">
-        <v>Kloe</v>
+        <v>Kilian</v>
       </c>
       <c r="E47" t="str">
-        <v>k.lefrancois@e2c-grandlille.fr</v>
+        <v>kiliandubreucq6@gmail.com</v>
       </c>
       <c r="F47" t="str">
-        <v>07 67 79 32 58</v>
+        <v>0743610987</v>
       </c>
       <c r="G47" t="str">
         <v>Grand Lille</v>
@@ -7549,43 +7558,43 @@
         <v>Lille</v>
       </c>
       <c r="I47" t="str">
-        <v>Auxiliaire de puériculture</v>
+        <v>Employé / Employée de libre-service</v>
       </c>
       <c r="K47" t="str">
         <v>Je sais</v>
       </c>
       <c r="L47" t="str">
-        <v>référés Lucie</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M47" t="str">
-        <v>2602/février 2026 LIL</v>
+        <v>2512/décembre 2025 LIL</v>
       </c>
       <c r="O47" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P47">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q47">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R47" s="1">
-        <v>39595</v>
+        <v>37934</v>
       </c>
       <c r="T47" t="str">
-        <v>LILLE, FRANCE</v>
+        <v>DENAIN</v>
       </c>
       <c r="U47" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W47" t="str">
-        <v>140 140 Rue Henri Ghesquière</v>
+        <v>34 34 Rue de l'Industrie</v>
       </c>
       <c r="X47" t="str">
-        <v>59261</v>
+        <v>59790</v>
       </c>
       <c r="Y47" t="str">
-        <v>WAHAGNIES</v>
+        <v>RONCHIN</v>
       </c>
       <c r="Z47" t="str">
         <v>Non</v>
@@ -7594,10 +7603,10 @@
         <v>Non</v>
       </c>
       <c r="AC47" t="str">
-        <v>NON</v>
+        <v>CEJ_FRANCE_TRAVAIL</v>
       </c>
       <c r="AD47" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE47" t="str">
         <v>Non</v>
@@ -7618,58 +7627,34 @@
         <v>Non</v>
       </c>
       <c r="AK47" t="str">
-        <v>259h15m</v>
+        <v>427h15m</v>
       </c>
       <c r="AL47" t="str">
-        <v>75h</v>
+        <v>173h</v>
       </c>
       <c r="AM47" t="str">
-        <v>85h</v>
+        <v>165h</v>
       </c>
       <c r="AN47" s="1">
-        <v>46055.687418981484</v>
+        <v>46006</v>
       </c>
       <c r="AO47" s="1">
-        <v>46133.46111111111</v>
+        <v>46063.71805555555</v>
       </c>
       <c r="AP47" s="1">
-        <v>46328.498611111114</v>
-      </c>
-      <c r="AU47" s="1">
-        <v>45944</v>
+        <v>46280.083333333336</v>
       </c>
       <c r="AV47" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne d'Ostricourt</v>
-      </c>
-      <c r="AW47" t="str">
-        <v>M. Pascal GAMBIER - 06.81.64.53.27</v>
-      </c>
-      <c r="AX47" s="1">
-        <v>45943</v>
+        <v>FRANCE TRAVAIL - Lille Grand Sud</v>
       </c>
       <c r="BA47" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB47" t="str">
-        <v>FIEVET</v>
-      </c>
-      <c r="BC47" t="str">
-        <v>Sylvia</v>
-      </c>
-      <c r="BD47" t="str">
-        <v>140 RUE HENRI GHESQUIERES 59261 WAHAGNIES</v>
-      </c>
-      <c r="BE47" t="str">
-        <v>0633919464</v>
-      </c>
-      <c r="BF47" t="str">
-        <v>vincsyl@live.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG47" t="str">
-        <v>10068</v>
+        <v>598150</v>
       </c>
       <c r="BJ47" t="str">
-        <v>bea7ca7b-c90a-4417-a113-1038a82451e3</v>
+        <v>9634e305-063f-4ce7-ae11-ff4d5f312dd2</v>
       </c>
       <c r="BK47" t="str">
         <v>Accepted</v>
@@ -7681,27 +7666,27 @@
         <v/>
       </c>
       <c r="BN47" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/k_lefrancois_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fk%5Flefrancois%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2FActivit%C3%A9s%20E2C&amp;ga=1</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>55505</v>
+        <v>40002</v>
       </c>
       <c r="B48" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C48" t="str">
-        <v>BERGOT</v>
+        <v>LEMAIRE</v>
       </c>
       <c r="D48" t="str">
-        <v>Etan</v>
+        <v>Eva</v>
       </c>
       <c r="E48" t="str">
-        <v>e.bergot@e2c-grandlille.fr</v>
+        <v>evalemaire2707@gmail.com</v>
       </c>
       <c r="F48" t="str">
-        <v>0685068151</v>
+        <v>0615321559</v>
       </c>
       <c r="G48" t="str">
         <v>Grand Lille</v>
@@ -7710,43 +7695,43 @@
         <v>Lille</v>
       </c>
       <c r="I48" t="str">
-        <v>Styliste, Coiffeur barbier / Coiffeuse barbière, Photographe</v>
+        <v>Designer graphique</v>
       </c>
       <c r="K48" t="str">
         <v>Je sais</v>
       </c>
       <c r="L48" t="str">
-        <v>référés Camille</v>
+        <v>référés Sura</v>
       </c>
       <c r="M48" t="str">
-        <v>2603/mars 2026 LIL</v>
+        <v>2512/décembre 2025 LIL</v>
       </c>
       <c r="O48" t="str">
-        <v>PEAU Camille</v>
+        <v>JAMIL HUSSAIN Sura</v>
       </c>
       <c r="P48">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q48">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R48" s="1">
-        <v>39659</v>
+        <v>38925</v>
       </c>
       <c r="T48" t="str">
-        <v>ROUBAIX, FRANCE</v>
+        <v>LILLE</v>
       </c>
       <c r="U48" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W48" t="str">
-        <v>257 257 Rue Gustave Delory</v>
+        <v>19 19 Rue Molière</v>
       </c>
       <c r="X48" t="str">
-        <v>59830</v>
+        <v>59790</v>
       </c>
       <c r="Y48" t="str">
-        <v>CYSOING</v>
+        <v>RONCHIN</v>
       </c>
       <c r="Z48" t="str">
         <v>Non</v>
@@ -7758,7 +7743,7 @@
         <v>NON</v>
       </c>
       <c r="AD48" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE48" t="str">
         <v>Non</v>
@@ -7779,61 +7764,34 @@
         <v>Non</v>
       </c>
       <c r="AK48" t="str">
-        <v>190h15m</v>
+        <v>387h45m</v>
       </c>
       <c r="AL48" t="str">
-        <v>126h</v>
+        <v>286h15m</v>
       </c>
       <c r="AM48" t="str">
-        <v>43h45m</v>
+        <v>199h30m</v>
       </c>
       <c r="AN48" s="1">
-        <v>46090.612604166665</v>
+        <v>46006</v>
       </c>
       <c r="AO48" s="1">
-        <v>46133.47986111111</v>
+        <v>46063.720138888886</v>
       </c>
       <c r="AP48" s="1">
-        <v>46365.39444444444</v>
-      </c>
-      <c r="AU48" s="1">
-        <v>45944</v>
+        <v>46280.083333333336</v>
       </c>
       <c r="AV48" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne Templeuve</v>
-      </c>
-      <c r="AW48" t="str">
-        <v>Anne BRACKE</v>
-      </c>
-      <c r="AX48" s="1">
-        <v>45940.507314814815</v>
-      </c>
-      <c r="AY48" t="str">
-        <v>abracke@impulsions-ms.fr</v>
+        <v>FRANCE TRAVAIL - Lille Grand Sud</v>
       </c>
       <c r="BA48" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB48" t="str">
-        <v>MOUMA</v>
-      </c>
-      <c r="BC48" t="str">
-        <v>Nadia</v>
-      </c>
-      <c r="BD48" t="str">
-        <v>257 RUE GUSTAVE DELORY 59830 CYSOING</v>
-      </c>
-      <c r="BE48" t="str">
-        <v>0662616204</v>
-      </c>
-      <c r="BF48" t="str">
-        <v>nadia.mouma@gmail.com</v>
+        <v>NON</v>
       </c>
       <c r="BG48" t="str">
-        <v>11210</v>
+        <v>598138</v>
       </c>
       <c r="BJ48" t="str">
-        <v>29b8879a-f898-4691-8488-913ee2c248b4</v>
+        <v>4da37b0e-71d1-4028-86ff-30684fe01507</v>
       </c>
       <c r="BK48" t="str">
         <v>Accepted</v>
@@ -7842,30 +7800,30 @@
         <v/>
       </c>
       <c r="BM48" t="str">
-        <v>etanbergot@gmail.com</v>
+        <v/>
       </c>
       <c r="BN48" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_bergot_e2c-grandlille_fr/IgCve20h4StqTrrKv3PpmP6zAeOVafj36P10Fn8x6C5dnv8?e=tMYKs1</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>40005</v>
+        <v>39985</v>
       </c>
       <c r="B49" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C49" t="str">
-        <v>DUBREUCQ</v>
+        <v>BENCHARQUI</v>
       </c>
       <c r="D49" t="str">
-        <v>Kilian</v>
+        <v>Hibat</v>
       </c>
       <c r="E49" t="str">
-        <v>kiliandubreucq6@gmail.com</v>
+        <v>hibabencharqui02@gmail.com</v>
       </c>
       <c r="F49" t="str">
-        <v>0743610987</v>
+        <v>0782062177</v>
       </c>
       <c r="G49" t="str">
         <v>Grand Lille</v>
@@ -7874,43 +7832,43 @@
         <v>Lille</v>
       </c>
       <c r="I49" t="str">
-        <v>Employé / Employée de libre-service</v>
+        <v>Coordonnateur / Coordonnatrice de projet socioéducatif</v>
       </c>
       <c r="K49" t="str">
-        <v>Je sais</v>
+        <v>J'y vais</v>
       </c>
       <c r="L49" t="str">
-        <v>référés Gwenaelle</v>
+        <v>référés Laurence</v>
       </c>
       <c r="M49" t="str">
         <v>2512/décembre 2025 LIL</v>
       </c>
       <c r="O49" t="str">
-        <v>GUYO Gwenaelle</v>
+        <v>DUFOUR Fanny</v>
       </c>
       <c r="P49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R49" s="1">
-        <v>37934</v>
+        <v>37603</v>
       </c>
       <c r="T49" t="str">
-        <v>DENAIN</v>
+        <v>CASABLANCA, MAROC</v>
       </c>
       <c r="U49" t="str">
-        <v>FRANCAISE</v>
+        <v>EUROPEENNE</v>
       </c>
       <c r="W49" t="str">
-        <v>34 34 Rue de l'Industrie</v>
+        <v>1 1 Place du Général de Gaulle</v>
       </c>
       <c r="X49" t="str">
-        <v>59790</v>
+        <v>59840</v>
       </c>
       <c r="Y49" t="str">
-        <v>RONCHIN</v>
+        <v>PERENCHIES</v>
       </c>
       <c r="Z49" t="str">
         <v>Non</v>
@@ -7919,10 +7877,10 @@
         <v>Non</v>
       </c>
       <c r="AC49" t="str">
-        <v>CEJ_FRANCE_TRAVAIL</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD49" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE49" t="str">
         <v>Non</v>
@@ -7943,34 +7901,40 @@
         <v>Non</v>
       </c>
       <c r="AK49" t="str">
-        <v>337h15m</v>
+        <v>387h15m</v>
       </c>
       <c r="AL49" t="str">
-        <v>110h</v>
+        <v>399h</v>
       </c>
       <c r="AM49" t="str">
-        <v>111h30m</v>
+        <v>77h45m</v>
       </c>
       <c r="AN49" s="1">
         <v>46006</v>
       </c>
       <c r="AO49" s="1">
-        <v>46063.71805555555</v>
+        <v>46063.71527777778</v>
       </c>
       <c r="AP49" s="1">
         <v>46280.083333333336</v>
       </c>
       <c r="AV49" t="str">
-        <v>FRANCE TRAVAIL - Lille Grand Sud</v>
+        <v>MISSION LOCALE MNO - Antenne Saint André</v>
+      </c>
+      <c r="AW49" t="str">
+        <v>Prescripteur : tassadit.bakkali@mlmno.fr - 06 46 26 40 60</v>
+      </c>
+      <c r="AY49" t="str">
+        <v>Nvelle conseillère : Anaîs COLIER</v>
       </c>
       <c r="BA49" t="str">
         <v>NON</v>
       </c>
       <c r="BG49" t="str">
-        <v>598150</v>
+        <v>598140</v>
       </c>
       <c r="BJ49" t="str">
-        <v>9634e305-063f-4ce7-ae11-ff4d5f312dd2</v>
+        <v>f657973a-70fa-4faf-aa7e-eea0f16d81cf</v>
       </c>
       <c r="BK49" t="str">
         <v>Accepted</v>
@@ -7987,22 +7951,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>40002</v>
+        <v>37177</v>
       </c>
       <c r="B50" t="str">
         <v>Femme</v>
       </c>
       <c r="C50" t="str">
-        <v>LEMAIRE</v>
+        <v>GARDIN</v>
       </c>
       <c r="D50" t="str">
-        <v>Eva</v>
+        <v>Galéane</v>
       </c>
       <c r="E50" t="str">
-        <v>evalemaire2707@gmail.com</v>
+        <v>galeane.gardin@gmail.com</v>
       </c>
       <c r="F50" t="str">
-        <v>0615321559</v>
+        <v>06 13 19 88 04</v>
       </c>
       <c r="G50" t="str">
         <v>Grand Lille</v>
@@ -8011,28 +7975,28 @@
         <v>Lille</v>
       </c>
       <c r="I50" t="str">
-        <v>Monteur / Monteuse audiovisuel, Chargé / Chargée de communication</v>
+        <v>Agent / Agente d'accueil, Assistant / Assistante Ressources Humaines (RH)</v>
       </c>
       <c r="K50" t="str">
         <v>Je sais</v>
       </c>
       <c r="L50" t="str">
-        <v>référés Sura</v>
+        <v>référés Lucie</v>
       </c>
       <c r="M50" t="str">
-        <v>2512/décembre 2025 LIL</v>
+        <v>2511/novembre 2025 LIL</v>
       </c>
       <c r="O50" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
+        <v>DERCOURT Lucie</v>
       </c>
       <c r="P50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q50">
         <v>19</v>
       </c>
       <c r="R50" s="1">
-        <v>38925</v>
+        <v>38721</v>
       </c>
       <c r="T50" t="str">
         <v>LILLE</v>
@@ -8040,14 +8004,17 @@
       <c r="U50" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V50" t="str">
+        <v>NON</v>
+      </c>
       <c r="W50" t="str">
-        <v>19 19 Rue Molière</v>
+        <v>34 34 Rue Frémaux</v>
       </c>
       <c r="X50" t="str">
-        <v>59790</v>
+        <v>59160</v>
       </c>
       <c r="Y50" t="str">
-        <v>RONCHIN</v>
+        <v>LOMME</v>
       </c>
       <c r="Z50" t="str">
         <v>Non</v>
@@ -8059,7 +8026,7 @@
         <v>NON</v>
       </c>
       <c r="AD50" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE50" t="str">
         <v>Non</v>
@@ -8080,34 +8047,34 @@
         <v>Non</v>
       </c>
       <c r="AK50" t="str">
-        <v>322h15m</v>
+        <v>377h15m</v>
       </c>
       <c r="AL50" t="str">
-        <v>238h15m</v>
+        <v>121h</v>
       </c>
       <c r="AM50" t="str">
-        <v>134h30m</v>
+        <v>252h45m</v>
       </c>
       <c r="AN50" s="1">
-        <v>46006</v>
+        <v>45971</v>
       </c>
       <c r="AO50" s="1">
-        <v>46063.720138888886</v>
+        <v>46028.47152777778</v>
       </c>
       <c r="AP50" s="1">
-        <v>46280.083333333336</v>
+        <v>46244.083333333336</v>
       </c>
       <c r="AV50" t="str">
-        <v>FRANCE TRAVAIL - Lille Grand Sud</v>
+        <v>En direct</v>
       </c>
       <c r="BA50" t="str">
         <v>NON</v>
       </c>
       <c r="BG50" t="str">
-        <v>598138</v>
+        <v>597057</v>
       </c>
       <c r="BJ50" t="str">
-        <v>4da37b0e-71d1-4028-86ff-30684fe01507</v>
+        <v>0e581210-b449-4978-9aa7-e2a3efe486c3</v>
       </c>
       <c r="BK50" t="str">
         <v>Accepted</v>
@@ -8119,27 +8086,27 @@
         <v/>
       </c>
       <c r="BN50" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/lille_e2c-grandlille_fr/IgA3i511HOHdSJqNmesRw6svAdb8HarujdquWAxSP6qJw8g?e=UQJFL9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>39985</v>
+        <v>37176</v>
       </c>
       <c r="B51" t="str">
         <v>Femme</v>
       </c>
       <c r="C51" t="str">
-        <v>BENCHARQUI</v>
+        <v>PEUTEVYNCK</v>
       </c>
       <c r="D51" t="str">
-        <v>Hibat</v>
+        <v>Lucie</v>
       </c>
       <c r="E51" t="str">
-        <v>hibabencharqui02@gmail.com</v>
+        <v>lucie.peut@icloud.com</v>
       </c>
       <c r="F51" t="str">
-        <v>0782062177</v>
+        <v>0646560142</v>
       </c>
       <c r="G51" t="str">
         <v>Grand Lille</v>
@@ -8148,43 +8115,46 @@
         <v>Lille</v>
       </c>
       <c r="I51" t="str">
-        <v>Coordonnateur / Coordonnatrice de projet socioéducatif</v>
+        <v>Auxiliaire de puériculture, Aide à domicile</v>
       </c>
       <c r="K51" t="str">
-        <v>J'y vais</v>
+        <v>Je sais</v>
       </c>
       <c r="L51" t="str">
-        <v>référés Laurence</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M51" t="str">
-        <v>2512/décembre 2025 LIL</v>
+        <v>2511/novembre 2025 LIL</v>
       </c>
       <c r="O51" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P51">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q51">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R51" s="1">
-        <v>37603</v>
+        <v>38980</v>
       </c>
       <c r="T51" t="str">
-        <v>CASABLANCA, MAROC</v>
+        <v>LILLE</v>
       </c>
       <c r="U51" t="str">
-        <v>EUROPEENNE</v>
+        <v>FRANCAISE</v>
+      </c>
+      <c r="V51" t="str">
+        <v>NON</v>
       </c>
       <c r="W51" t="str">
-        <v>1 1 Place du Général de Gaulle</v>
+        <v>3 3 Rue Vincent Auriol Pavillon Duez</v>
       </c>
       <c r="X51" t="str">
-        <v>59840</v>
+        <v>59120</v>
       </c>
       <c r="Y51" t="str">
-        <v>PERENCHIES</v>
+        <v>LOOS</v>
       </c>
       <c r="Z51" t="str">
         <v>Non</v>
@@ -8193,10 +8163,10 @@
         <v>Non</v>
       </c>
       <c r="AC51" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>NON</v>
       </c>
       <c r="AD51" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE51" t="str">
         <v>Non</v>
@@ -8214,37 +8184,34 @@
         <v>Non</v>
       </c>
       <c r="AJ51" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AK51" t="str">
-        <v>295h30m</v>
+        <v>189h40m</v>
       </c>
       <c r="AL51" t="str">
-        <v>314h</v>
+        <v>284h20m</v>
       </c>
       <c r="AM51" t="str">
-        <v>42h</v>
+        <v>426h30m</v>
       </c>
       <c r="AN51" s="1">
-        <v>46006</v>
+        <v>45971</v>
       </c>
       <c r="AO51" s="1">
-        <v>46063.71527777778</v>
+        <v>46028.472916666666</v>
       </c>
       <c r="AP51" s="1">
-        <v>46280.083333333336</v>
+        <v>46244.083333333336</v>
       </c>
       <c r="AV51" t="str">
-        <v>MISSION LOCALE MNO - Antenne Saint André</v>
+        <v>DEPARTEMENT DU NORD</v>
       </c>
       <c r="BA51" t="str">
         <v>NON</v>
       </c>
-      <c r="BG51" t="str">
-        <v>598140</v>
-      </c>
       <c r="BJ51" t="str">
-        <v>f657973a-70fa-4faf-aa7e-eea0f16d81cf</v>
+        <v>db0c0a41-0d32-4dad-8566-fdef12e6d4e0</v>
       </c>
       <c r="BK51" t="str">
         <v>Accepted</v>
@@ -8261,22 +8228,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>39984</v>
+        <v>37170</v>
       </c>
       <c r="B52" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C52" t="str">
-        <v>FIUMENE</v>
+        <v>BERNARD</v>
       </c>
       <c r="D52" t="str">
-        <v>Lola-Rosa</v>
+        <v>Théo</v>
       </c>
       <c r="E52" t="str">
-        <v>fiumenelolarosa779@gmail.com</v>
+        <v>theobernard105@gmail.com</v>
       </c>
       <c r="F52" t="str">
-        <v>0783387457</v>
+        <v>0649994723</v>
       </c>
       <c r="G52" t="str">
         <v>Grand Lille</v>
@@ -8284,44 +8251,47 @@
       <c r="H52" t="str">
         <v>Lille</v>
       </c>
-      <c r="I52" t="str">
-        <v>Animateur coordinateur socioculturel / Animatrice coordinatrice socioculturelle</v>
+      <c r="J52" t="str">
+        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat travail temporaire insertion, Contrat durée déterminée insertion, CDI Intérimaire, Contrat d'apprentissage</v>
       </c>
       <c r="K52" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L52" t="str">
-        <v>référés Sura</v>
+        <v>référés German</v>
       </c>
       <c r="M52" t="str">
-        <v>2512/décembre 2025 LIL</v>
+        <v>2511/novembre 2025 LIL</v>
       </c>
       <c r="O52" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
+        <v>LEON QUERO German</v>
       </c>
       <c r="P52">
+        <v>19</v>
+      </c>
+      <c r="Q52">
         <v>18</v>
       </c>
-      <c r="Q52">
-        <v>17</v>
-      </c>
       <c r="R52" s="1">
-        <v>39570</v>
+        <v>39147</v>
       </c>
       <c r="T52" t="str">
-        <v>VALENCIENNES</v>
+        <v>LESQUIN</v>
       </c>
       <c r="U52" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V52" t="str">
+        <v>NON</v>
+      </c>
       <c r="W52" t="str">
-        <v>81 81 Rue Georges Clémenceau Appartement 82</v>
+        <v>21 21 Rue Danton Appartement 3</v>
       </c>
       <c r="X52" t="str">
-        <v>59000</v>
+        <v>59160</v>
       </c>
       <c r="Y52" t="str">
-        <v>LILLE</v>
+        <v>LOMME</v>
       </c>
       <c r="Z52" t="str">
         <v>Non</v>
@@ -8330,10 +8300,10 @@
         <v>Non</v>
       </c>
       <c r="AC52" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD52" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE52" t="str">
         <v>Non</v>
@@ -8354,37 +8324,37 @@
         <v>Non</v>
       </c>
       <c r="AK52" t="str">
-        <v>332h15m</v>
+        <v>439h15m</v>
       </c>
       <c r="AL52" t="str">
-        <v>150h</v>
+        <v>98h</v>
       </c>
       <c r="AM52" t="str">
-        <v>74h45m</v>
+        <v>230h</v>
       </c>
       <c r="AN52" s="1">
-        <v>46006</v>
+        <v>45971</v>
       </c>
       <c r="AO52" s="1">
-        <v>46063.71875</v>
+        <v>46028.67013888889</v>
       </c>
       <c r="AP52" s="1">
-        <v>46280.083333333336</v>
+        <v>46244.083333333336</v>
       </c>
       <c r="AV52" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Moulins</v>
+        <v>MISSION LOCALE DE LILLE - Antenne Lomme</v>
+      </c>
+      <c r="AW52" t="str">
+        <v>Elisa BOULIN</v>
       </c>
       <c r="BA52" t="str">
         <v>NON</v>
       </c>
-      <c r="BB52" t="str">
-        <v>Monsieur Sergio FIUMENE - Père - 06 11 84 33 46 - fiume.sergio@laposte.net mesanges2@outlook.fr - Mère</v>
-      </c>
       <c r="BG52" t="str">
-        <v>598105</v>
+        <v>597051</v>
       </c>
       <c r="BJ52" t="str">
-        <v>7f7d0378-52dd-46e5-947c-21bbb88c34dc</v>
+        <v>3fe7d615-4f3e-443e-977a-926adadc107b</v>
       </c>
       <c r="BK52" t="str">
         <v>Accepted</v>
@@ -8401,22 +8371,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>39948</v>
+        <v>37169</v>
       </c>
       <c r="B53" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C53" t="str">
-        <v>DELANNOY</v>
+        <v>GOBERT</v>
       </c>
       <c r="D53" t="str">
-        <v>Hélèna</v>
+        <v>Eitan</v>
       </c>
       <c r="E53" t="str">
-        <v>helena.delannoy59@gmail.com</v>
+        <v>eitan.gobert@gmail.com</v>
       </c>
       <c r="F53" t="str">
-        <v>0635267232</v>
+        <v>0768166777</v>
       </c>
       <c r="G53" t="str">
         <v>Grand Lille</v>
@@ -8425,49 +8395,49 @@
         <v>Lille</v>
       </c>
       <c r="I53" t="str">
-        <v>Hôte / Hôtesse de caisse</v>
+        <v>Formateur / Formatrice d'anglais, Professeur / Professeure d'anglais, Surveillant / Surveillante en milieu scolaire</v>
       </c>
       <c r="K53" t="str">
-        <v>J'y vais</v>
+        <v>Je sais</v>
       </c>
       <c r="L53" t="str">
-        <v>référés Laurence</v>
+        <v>référés Gwenaelle</v>
       </c>
       <c r="M53" t="str">
-        <v>2512/décembre 2025 LIL</v>
+        <v>2511/novembre 2025 LIL</v>
       </c>
       <c r="O53" t="str">
-        <v>DUFOUR Fanny</v>
+        <v>GUYO Gwenaelle</v>
       </c>
       <c r="P53">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q53">
         <v>21</v>
       </c>
       <c r="R53" s="1">
-        <v>38329</v>
+        <v>38021</v>
       </c>
       <c r="T53" t="str">
-        <v>ROUBAIX</v>
+        <v>VILLENEUVE D'ASCQ</v>
       </c>
       <c r="U53" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V53" t="str">
+        <v>NON</v>
+      </c>
       <c r="W53" t="str">
-        <v>4 4 Rue d'Artois</v>
+        <v>350 350 Rue Jules Ferry</v>
       </c>
       <c r="X53" t="str">
-        <v>59370</v>
+        <v>59261</v>
       </c>
       <c r="Y53" t="str">
-        <v>MONS EN BAROEUL</v>
+        <v>WAHAGNIES</v>
       </c>
       <c r="Z53" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA53" t="str">
-        <v>QN05978M</v>
+        <v>Non</v>
       </c>
       <c r="AB53" t="str">
         <v>Non</v>
@@ -8476,7 +8446,7 @@
         <v>NON</v>
       </c>
       <c r="AD53" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE53" t="str">
         <v>Non</v>
@@ -8497,40 +8467,34 @@
         <v>Non</v>
       </c>
       <c r="AK53" t="str">
-        <v>386h15m</v>
+        <v>423h15m</v>
       </c>
       <c r="AL53" t="str">
-        <v>390h15m</v>
+        <v>82h</v>
       </c>
       <c r="AM53" t="str">
-        <v>347h45m</v>
+        <v>252h45m</v>
       </c>
       <c r="AN53" s="1">
-        <v>46006</v>
+        <v>45971</v>
       </c>
       <c r="AO53" s="1">
-        <v>46063.717361111114</v>
+        <v>46028.47152777778</v>
       </c>
       <c r="AP53" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AU53" s="1">
-        <v>45937.583333333336</v>
+        <v>46244.083333333336</v>
       </c>
       <c r="AV53" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="AX53" s="1">
-        <v>45936.583333333336</v>
+        <v>SITE WEB</v>
       </c>
       <c r="BA53" t="str">
         <v>NON</v>
       </c>
       <c r="BG53" t="str">
-        <v>523173</v>
+        <v>597053</v>
       </c>
       <c r="BJ53" t="str">
-        <v>c6b5d1d9-ae2e-4bc5-8783-4e8d0ab60285</v>
+        <v>73479dad-dc16-4eb9-87e1-3e3cc1a53a0e</v>
       </c>
       <c r="BK53" t="str">
         <v>Accepted</v>
@@ -8547,22 +8511,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>37177</v>
+        <v>37168</v>
       </c>
       <c r="B54" t="str">
         <v>Femme</v>
       </c>
       <c r="C54" t="str">
-        <v>GARDIN</v>
+        <v>DELANNOY</v>
       </c>
       <c r="D54" t="str">
-        <v>Galéane</v>
+        <v>Alycia</v>
       </c>
       <c r="E54" t="str">
-        <v>galeane.gardin@gmail.com</v>
+        <v>alyciadelannoy59@gmail.com</v>
       </c>
       <c r="F54" t="str">
-        <v>06 13 19 88 04</v>
+        <v>0621998147</v>
       </c>
       <c r="G54" t="str">
         <v>Grand Lille</v>
@@ -8571,19 +8535,19 @@
         <v>Lille</v>
       </c>
       <c r="I54" t="str">
-        <v>Assistant / Assistante d'éducation, Conseiller / Conseillère clientèle à distance</v>
+        <v>Assistant / Assistante accueil petite enfance, Vendeur / Vendeuse en prêt-à-porter</v>
       </c>
       <c r="K54" t="str">
-        <v>Je sais</v>
+        <v>J'y vais</v>
       </c>
       <c r="L54" t="str">
-        <v>référés Lucie</v>
+        <v>référés Laurence</v>
       </c>
       <c r="M54" t="str">
         <v>2511/novembre 2025 LIL</v>
       </c>
       <c r="O54" t="str">
-        <v>DERCOURT Lucie</v>
+        <v>PEAU Camille</v>
       </c>
       <c r="P54">
         <v>20</v>
@@ -8592,10 +8556,10 @@
         <v>19</v>
       </c>
       <c r="R54" s="1">
-        <v>38721</v>
+        <v>38744</v>
       </c>
       <c r="T54" t="str">
-        <v>LILLE</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U54" t="str">
         <v>FRANCAISE</v>
@@ -8604,16 +8568,19 @@
         <v>NON</v>
       </c>
       <c r="W54" t="str">
-        <v>34 34 Rue Frémaux</v>
+        <v>4 4 Rue d'Artois</v>
       </c>
       <c r="X54" t="str">
-        <v>59160</v>
+        <v>59370</v>
       </c>
       <c r="Y54" t="str">
-        <v>LOMME</v>
+        <v>MONS EN BAROEUL</v>
       </c>
       <c r="Z54" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA54" t="str">
+        <v>QN05978M</v>
       </c>
       <c r="AB54" t="str">
         <v>Non</v>
@@ -8622,7 +8589,7 @@
         <v>NON</v>
       </c>
       <c r="AD54" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE54" t="str">
         <v>Non</v>
@@ -8634,7 +8601,7 @@
         <v>SANS</v>
       </c>
       <c r="AH54" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AI54" t="str">
         <v>Non</v>
@@ -8643,19 +8610,19 @@
         <v>Non</v>
       </c>
       <c r="AK54" t="str">
-        <v>322h30m</v>
+        <v>449h15m</v>
       </c>
       <c r="AL54" t="str">
-        <v>121h</v>
+        <v>423h40m</v>
       </c>
       <c r="AM54" t="str">
-        <v>169h</v>
+        <v>164h25m</v>
       </c>
       <c r="AN54" s="1">
         <v>45971</v>
       </c>
       <c r="AO54" s="1">
-        <v>46028.47152777778</v>
+        <v>46063.63958333333</v>
       </c>
       <c r="AP54" s="1">
         <v>46244.083333333336</v>
@@ -8667,10 +8634,10 @@
         <v>NON</v>
       </c>
       <c r="BG54" t="str">
-        <v>597057</v>
+        <v>564472</v>
       </c>
       <c r="BJ54" t="str">
-        <v>0e581210-b449-4978-9aa7-e2a3efe486c3</v>
+        <v>4a0640a4-c752-4fcc-844b-46caaed84e39</v>
       </c>
       <c r="BK54" t="str">
         <v>Accepted</v>
@@ -8682,1275 +8649,12 @@
         <v/>
       </c>
       <c r="BN54" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/lille_e2c-grandlille_fr/IgA3i511HOHdSJqNmesRw6svAdb8HarujdquWAxSP6qJw8g?e=UQJFL9</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>37176</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C55" t="str">
-        <v>PEUTEVYNCK</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Lucie</v>
-      </c>
-      <c r="E55" t="str">
-        <v>lucie.peut@icloud.com</v>
-      </c>
-      <c r="F55" t="str">
-        <v>0646560142</v>
-      </c>
-      <c r="G55" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H55" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I55" t="str">
-        <v>Auxiliaire de puériculture, Aide à domicile</v>
-      </c>
-      <c r="K55" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L55" t="str">
-        <v>référés Gwenaelle</v>
-      </c>
-      <c r="M55" t="str">
-        <v>2511/novembre 2025 LIL</v>
-      </c>
-      <c r="O55" t="str">
-        <v>GUYO Gwenaelle</v>
-      </c>
-      <c r="P55">
-        <v>19</v>
-      </c>
-      <c r="Q55">
-        <v>19</v>
-      </c>
-      <c r="R55" s="1">
-        <v>38980</v>
-      </c>
-      <c r="T55" t="str">
-        <v>LILLE</v>
-      </c>
-      <c r="U55" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W55" t="str">
-        <v>3 3 Rue Vincent Auriol Pavillon Duez</v>
-      </c>
-      <c r="X55" t="str">
-        <v>59120</v>
-      </c>
-      <c r="Y55" t="str">
-        <v>LOOS</v>
-      </c>
-      <c r="Z55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD55" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
-      </c>
-      <c r="AE55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG55" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI55" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ55" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AK55" t="str">
-        <v>170h40m</v>
-      </c>
-      <c r="AL55" t="str">
-        <v>193h20m</v>
-      </c>
-      <c r="AM55" t="str">
-        <v>310h</v>
-      </c>
-      <c r="AN55" s="1">
-        <v>45971</v>
-      </c>
-      <c r="AO55" s="1">
-        <v>46028.472916666666</v>
-      </c>
-      <c r="AP55" s="1">
-        <v>46244.083333333336</v>
-      </c>
-      <c r="AV55" t="str">
-        <v>DEPARTEMENT DU NORD</v>
-      </c>
-      <c r="BA55" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BJ55" t="str">
-        <v>db0c0a41-0d32-4dad-8566-fdef12e6d4e0</v>
-      </c>
-      <c r="BK55" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL55" t="str">
-        <v/>
-      </c>
-      <c r="BM55" t="str">
-        <v/>
-      </c>
-      <c r="BN55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>37170</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C56" t="str">
-        <v>BERNARD</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Théo</v>
-      </c>
-      <c r="E56" t="str">
-        <v>theobernard105@gmail.com</v>
-      </c>
-      <c r="F56" t="str">
-        <v>0649994723</v>
-      </c>
-      <c r="G56" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H56" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="J56" t="str">
-        <v>Contrat à durée indéterminée, Contrat à durée déterminée, Contrat travail temporaire insertion, Contrat durée déterminée insertion, CDI Intérimaire, Contrat d'apprentissage</v>
-      </c>
-      <c r="K56" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L56" t="str">
-        <v>référés German</v>
-      </c>
-      <c r="M56" t="str">
-        <v>2511/novembre 2025 LIL</v>
-      </c>
-      <c r="O56" t="str">
-        <v>LEON QUERO German</v>
-      </c>
-      <c r="P56">
-        <v>19</v>
-      </c>
-      <c r="Q56">
-        <v>18</v>
-      </c>
-      <c r="R56" s="1">
-        <v>39147</v>
-      </c>
-      <c r="T56" t="str">
-        <v>LESQUIN</v>
-      </c>
-      <c r="U56" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V56" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W56" t="str">
-        <v>21 21 Rue Danton Appartement 3</v>
-      </c>
-      <c r="X56" t="str">
-        <v>59160</v>
-      </c>
-      <c r="Y56" t="str">
-        <v>LOMME</v>
-      </c>
-      <c r="Z56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC56" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
-      </c>
-      <c r="AD56" t="str">
-        <v>3 non validé</v>
-      </c>
-      <c r="AE56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG56" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ56" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK56" t="str">
-        <v>424h45m</v>
-      </c>
-      <c r="AL56" t="str">
-        <v>98h</v>
-      </c>
-      <c r="AM56" t="str">
-        <v>117h</v>
-      </c>
-      <c r="AN56" s="1">
-        <v>45971</v>
-      </c>
-      <c r="AO56" s="1">
-        <v>46028.67013888889</v>
-      </c>
-      <c r="AP56" s="1">
-        <v>46244.083333333336</v>
-      </c>
-      <c r="AV56" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Lomme</v>
-      </c>
-      <c r="AW56" t="str">
-        <v>Elisa BOULIN</v>
-      </c>
-      <c r="BA56" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG56" t="str">
-        <v>597051</v>
-      </c>
-      <c r="BJ56" t="str">
-        <v>3fe7d615-4f3e-443e-977a-926adadc107b</v>
-      </c>
-      <c r="BK56" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL56" t="str">
-        <v/>
-      </c>
-      <c r="BM56" t="str">
-        <v/>
-      </c>
-      <c r="BN56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>37169</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C57" t="str">
-        <v>GOBERT</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Eitan</v>
-      </c>
-      <c r="E57" t="str">
-        <v>eitan.gobert@gmail.com</v>
-      </c>
-      <c r="F57" t="str">
-        <v>0768166777</v>
-      </c>
-      <c r="G57" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H57" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I57" t="str">
-        <v>Formateur / Formatrice d'anglais, Professeur / Professeure d'anglais, Surveillant / Surveillante en milieu scolaire</v>
-      </c>
-      <c r="K57" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L57" t="str">
-        <v>référés Gwenaelle</v>
-      </c>
-      <c r="M57" t="str">
-        <v>2511/novembre 2025 LIL</v>
-      </c>
-      <c r="O57" t="str">
-        <v>GUYO Gwenaelle</v>
-      </c>
-      <c r="P57">
-        <v>22</v>
-      </c>
-      <c r="Q57">
-        <v>21</v>
-      </c>
-      <c r="R57" s="1">
-        <v>38021</v>
-      </c>
-      <c r="T57" t="str">
-        <v>VILLENEUVE D'ASCQ</v>
-      </c>
-      <c r="U57" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V57" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W57" t="str">
-        <v>350 350 Rue Jules Ferry</v>
-      </c>
-      <c r="X57" t="str">
-        <v>59261</v>
-      </c>
-      <c r="Y57" t="str">
-        <v>WAHAGNIES</v>
-      </c>
-      <c r="Z57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC57" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD57" t="str">
-        <v>[OLD]Niveau 4 validé</v>
-      </c>
-      <c r="AE57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG57" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ57" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK57" t="str">
-        <v>416h30m</v>
-      </c>
-      <c r="AL57" t="str">
-        <v>82h</v>
-      </c>
-      <c r="AM57" t="str">
-        <v>131h30m</v>
-      </c>
-      <c r="AN57" s="1">
-        <v>45971</v>
-      </c>
-      <c r="AO57" s="1">
-        <v>46028.47152777778</v>
-      </c>
-      <c r="AP57" s="1">
-        <v>46244.083333333336</v>
-      </c>
-      <c r="AV57" t="str">
-        <v>SITE WEB</v>
-      </c>
-      <c r="BA57" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG57" t="str">
-        <v>597053</v>
-      </c>
-      <c r="BJ57" t="str">
-        <v>73479dad-dc16-4eb9-87e1-3e3cc1a53a0e</v>
-      </c>
-      <c r="BK57" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL57" t="str">
-        <v/>
-      </c>
-      <c r="BM57" t="str">
-        <v/>
-      </c>
-      <c r="BN57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>37168</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C58" t="str">
-        <v>DELANNOY</v>
-      </c>
-      <c r="D58" t="str">
-        <v>Alycia</v>
-      </c>
-      <c r="E58" t="str">
-        <v>alyciadelannoy59@gmail.com</v>
-      </c>
-      <c r="F58" t="str">
-        <v>0621998147</v>
-      </c>
-      <c r="G58" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H58" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I58" t="str">
-        <v>Assistant / Assistante accueil petite enfance, Vendeur / Vendeuse en prêt-à-porter</v>
-      </c>
-      <c r="K58" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L58" t="str">
-        <v>référés Laurence</v>
-      </c>
-      <c r="M58" t="str">
-        <v>2511/novembre 2025 LIL</v>
-      </c>
-      <c r="O58" t="str">
-        <v>PEAU Camille</v>
-      </c>
-      <c r="P58">
-        <v>20</v>
-      </c>
-      <c r="Q58">
-        <v>19</v>
-      </c>
-      <c r="R58" s="1">
-        <v>38744</v>
-      </c>
-      <c r="T58" t="str">
-        <v>ROUBAIX</v>
-      </c>
-      <c r="U58" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V58" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W58" t="str">
-        <v>4 4 Rue d'Artois</v>
-      </c>
-      <c r="X58" t="str">
-        <v>59370</v>
-      </c>
-      <c r="Y58" t="str">
-        <v>MONS EN BAROEUL</v>
-      </c>
-      <c r="Z58" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA58" t="str">
-        <v>QN05978M</v>
-      </c>
-      <c r="AB58" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC58" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD58" t="str">
-        <v>[OLD]Niveau 3 validé</v>
-      </c>
-      <c r="AE58" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF58" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG58" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH58" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AI58" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ58" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK58" t="str">
-        <v>346h15m</v>
-      </c>
-      <c r="AL58" t="str">
-        <v>337h40m</v>
-      </c>
-      <c r="AM58" t="str">
-        <v>139h15m</v>
-      </c>
-      <c r="AN58" s="1">
-        <v>45971</v>
-      </c>
-      <c r="AO58" s="1">
-        <v>46063.63958333333</v>
-      </c>
-      <c r="AP58" s="1">
-        <v>46244.083333333336</v>
-      </c>
-      <c r="AV58" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA58" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG58" t="str">
-        <v>564472</v>
-      </c>
-      <c r="BJ58" t="str">
-        <v>4a0640a4-c752-4fcc-844b-46caaed84e39</v>
-      </c>
-      <c r="BK58" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL58" t="str">
-        <v/>
-      </c>
-      <c r="BM58" t="str">
-        <v/>
-      </c>
-      <c r="BN58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>34899</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C59" t="str">
-        <v>SU</v>
-      </c>
-      <c r="D59" t="str">
-        <v>Elodie</v>
-      </c>
-      <c r="E59" t="str">
-        <v>elodiesu2702@gmail.com</v>
-      </c>
-      <c r="F59" t="str">
-        <v>0767852988</v>
-      </c>
-      <c r="G59" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H59" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I59" t="str">
-        <v>Réceptionniste</v>
-      </c>
-      <c r="K59" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L59" t="str">
-        <v>référés Sura</v>
-      </c>
-      <c r="M59" t="str">
-        <v>2510/octobre 2025 LIL</v>
-      </c>
-      <c r="O59" t="str">
-        <v>JAMIL HUSSAIN Sura</v>
-      </c>
-      <c r="P59">
-        <v>21</v>
-      </c>
-      <c r="Q59">
-        <v>20</v>
-      </c>
-      <c r="R59" s="1">
-        <v>38410</v>
-      </c>
-      <c r="T59" t="str">
-        <v>LILLE</v>
-      </c>
-      <c r="U59" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V59" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W59" t="str">
-        <v>15 15 Rue Montesquieu</v>
-      </c>
-      <c r="X59" t="str">
-        <v>59160</v>
-      </c>
-      <c r="Y59" t="str">
-        <v>LOMME</v>
-      </c>
-      <c r="Z59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC59" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD59" t="str">
-        <v>[OLD]Niveau 4 non validé</v>
-      </c>
-      <c r="AE59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG59" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ59" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK59" t="str">
-        <v>486h30m</v>
-      </c>
-      <c r="AL59" t="str">
-        <v>179h30m</v>
-      </c>
-      <c r="AM59" t="str">
-        <v>108h</v>
-      </c>
-      <c r="AN59" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO59" s="1">
-        <v>45978.041666666664</v>
-      </c>
-      <c r="AP59" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV59" t="str">
-        <v>SITE WEB</v>
-      </c>
-      <c r="BA59" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG59" t="str">
-        <v>595511</v>
-      </c>
-      <c r="BJ59" t="str">
-        <v>16fc4498-3eaa-4166-be8a-4772d1b606f9</v>
-      </c>
-      <c r="BK59" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL59" t="str">
-        <v/>
-      </c>
-      <c r="BM59" t="str">
-        <v/>
-      </c>
-      <c r="BN59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>34893</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C60" t="str">
-        <v>CHLAHBI</v>
-      </c>
-      <c r="D60" t="str">
-        <v>Yassine</v>
-      </c>
-      <c r="E60" t="str">
-        <v>yassinechlahbi81@gmail.com</v>
-      </c>
-      <c r="F60" t="str">
-        <v>0783566292</v>
-      </c>
-      <c r="G60" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H60" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I60" t="str">
-        <v>Électricien / Électricienne du bâtiment, Plombier / Plombière</v>
-      </c>
-      <c r="L60" t="str">
-        <v>référés Laurence</v>
-      </c>
-      <c r="M60" t="str">
-        <v>2510/octobre 2025 LIL</v>
-      </c>
-      <c r="O60" t="str">
-        <v>DUFOUR Fanny</v>
-      </c>
-      <c r="P60">
-        <v>17</v>
-      </c>
-      <c r="Q60">
-        <v>16</v>
-      </c>
-      <c r="R60" s="1">
-        <v>39832</v>
-      </c>
-      <c r="T60" t="str">
-        <v>LILLE</v>
-      </c>
-      <c r="U60" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V60" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W60" t="str">
-        <v>65 65 Rue de Belle vue Porte 11</v>
-      </c>
-      <c r="X60" t="str">
-        <v>59000</v>
-      </c>
-      <c r="Y60" t="str">
-        <v>LILLE</v>
-      </c>
-      <c r="Z60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC60" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD60" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG60" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ60" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK60" t="str">
-        <v>279h30m</v>
-      </c>
-      <c r="AL60" t="str">
-        <v>280h</v>
-      </c>
-      <c r="AM60" t="str">
-        <v>250h30m</v>
-      </c>
-      <c r="AN60" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO60" s="1">
-        <v>45978.041666666664</v>
-      </c>
-      <c r="AP60" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV60" t="str">
-        <v>MISSION LOCALE DE LILLE - Antenne Fives</v>
-      </c>
-      <c r="AW60" t="str">
-        <v>Jeanine GORNIAK</v>
-      </c>
-      <c r="BA60" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BB60" t="str">
-        <v>Monsieur et Madame CHLAHBI - 06 62 90 59 77 - 07 68 46 15 42</v>
-      </c>
-      <c r="BG60" t="str">
-        <v>595501</v>
-      </c>
-      <c r="BJ60" t="str">
-        <v>ba8d13f0-37cd-4e9d-8e49-4be77065f2c8</v>
-      </c>
-      <c r="BK60" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL60" t="str">
-        <v/>
-      </c>
-      <c r="BM60" t="str">
-        <v/>
-      </c>
-      <c r="BN60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>32937</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C61" t="str">
-        <v>JACQUOT</v>
-      </c>
-      <c r="D61" t="str">
-        <v>Killian</v>
-      </c>
-      <c r="E61" t="str">
-        <v>killianjacquot5@gmail.com</v>
-      </c>
-      <c r="F61" t="str">
-        <v>0621273189</v>
-      </c>
-      <c r="G61" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H61" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I61" t="str">
-        <v>Agent administratif / Agente administrative, Agent / Agente d'accueil</v>
-      </c>
-      <c r="K61" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L61" t="str">
-        <v>référés Fanny</v>
-      </c>
-      <c r="M61" t="str">
-        <v>2510/octobre 2025 LIL</v>
-      </c>
-      <c r="O61" t="str">
-        <v>DUFOUR Fanny</v>
-      </c>
-      <c r="P61">
-        <v>21</v>
-      </c>
-      <c r="Q61">
-        <v>21</v>
-      </c>
-      <c r="R61" s="1">
-        <v>38203</v>
-      </c>
-      <c r="T61" t="str">
-        <v>BEUVRY</v>
-      </c>
-      <c r="U61" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V61" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W61" t="str">
-        <v>5 5 Résidence Sainte Anne</v>
-      </c>
-      <c r="X61" t="str">
-        <v>62400</v>
-      </c>
-      <c r="Y61" t="str">
-        <v>LOCON</v>
-      </c>
-      <c r="Z61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC61" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD61" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
-      </c>
-      <c r="AE61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG61" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ61" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK61" t="str">
-        <v>285h45m</v>
-      </c>
-      <c r="AL61" t="str">
-        <v>397h</v>
-      </c>
-      <c r="AM61" t="str">
-        <v>148h30m</v>
-      </c>
-      <c r="AN61" s="1">
-        <v>45929</v>
-      </c>
-      <c r="AO61" s="1">
-        <v>46028.40833333333</v>
-      </c>
-      <c r="AP61" s="1">
-        <v>46202.083333333336</v>
-      </c>
-      <c r="AV61" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA61" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG61" t="str">
-        <v>559944</v>
-      </c>
-      <c r="BJ61" t="str">
-        <v>3e5f4043-bfad-4f34-9b48-6edfc621052c</v>
-      </c>
-      <c r="BK61" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL61" t="str">
-        <v/>
-      </c>
-      <c r="BM61" t="str">
-        <v/>
-      </c>
-      <c r="BN61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>32936</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C62" t="str">
-        <v>DJOUDI</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Lilia</v>
-      </c>
-      <c r="E62" t="str">
-        <v>liliadjoudi05@gmail.com</v>
-      </c>
-      <c r="F62" t="str">
-        <v>0613041869</v>
-      </c>
-      <c r="G62" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H62" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="I62" t="str">
-        <v>Agent administratif / Agente administrative</v>
-      </c>
-      <c r="L62" t="str">
-        <v>référés Anne</v>
-      </c>
-      <c r="M62" t="str">
-        <v>2509/septembre 2025 LIL</v>
-      </c>
-      <c r="O62" t="str">
-        <v>CAPEAU Anne</v>
-      </c>
-      <c r="P62">
-        <v>19</v>
-      </c>
-      <c r="Q62">
-        <v>19</v>
-      </c>
-      <c r="R62" s="1">
-        <v>38903</v>
-      </c>
-      <c r="T62" t="str">
-        <v>DECHY</v>
-      </c>
-      <c r="U62" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V62" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W62" t="str">
-        <v>51 A 51 A Rue Jean Jaurès</v>
-      </c>
-      <c r="X62" t="str">
-        <v>59287</v>
-      </c>
-      <c r="Y62" t="str">
-        <v>LEWARDE</v>
-      </c>
-      <c r="Z62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC62" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD62" t="str">
-        <v>[OLD]Niveau 3 validé</v>
-      </c>
-      <c r="AE62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG62" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ62" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK62" t="str">
-        <v>479h15m</v>
-      </c>
-      <c r="AL62" t="str">
-        <v>238h</v>
-      </c>
-      <c r="AM62" t="str">
-        <v>172h15m</v>
-      </c>
-      <c r="AN62" s="1">
-        <v>45901</v>
-      </c>
-      <c r="AO62" s="1">
-        <v>45936.083333333336</v>
-      </c>
-      <c r="AP62" s="1">
-        <v>46174.083333333336</v>
-      </c>
-      <c r="AV62" t="str">
-        <v>SITE WEB</v>
-      </c>
-      <c r="BA62" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG62" t="str">
-        <v>594211</v>
-      </c>
-      <c r="BJ62" t="str">
-        <v>e868ce1c-ff70-4e70-92cc-e0712fc613c5</v>
-      </c>
-      <c r="BK62" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL62" t="str">
-        <v/>
-      </c>
-      <c r="BM62" t="str">
-        <v/>
-      </c>
-      <c r="BN62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>32933</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C63" t="str">
-        <v>BOSSEMAN</v>
-      </c>
-      <c r="D63" t="str">
-        <v>Loïk</v>
-      </c>
-      <c r="E63" t="str">
-        <v>contact.loikbosseman@gmail.com</v>
-      </c>
-      <c r="F63" t="str">
-        <v>0638017617</v>
-      </c>
-      <c r="G63" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H63" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="K63" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L63" t="str">
-        <v>référés Camille</v>
-      </c>
-      <c r="M63" t="str">
-        <v>2509/septembre 2025 LIL</v>
-      </c>
-      <c r="O63" t="str">
-        <v>PEAU Camille</v>
-      </c>
-      <c r="P63">
-        <v>20</v>
-      </c>
-      <c r="Q63">
-        <v>19</v>
-      </c>
-      <c r="R63" s="1">
-        <v>38813</v>
-      </c>
-      <c r="T63" t="str">
-        <v>LILLE</v>
-      </c>
-      <c r="U63" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V63" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W63" t="str">
-        <v>1620 1620 Rue Faidherbe</v>
-      </c>
-      <c r="X63" t="str">
-        <v>59134</v>
-      </c>
-      <c r="Y63" t="str">
-        <v>FOURNES EN WEPPES</v>
-      </c>
-      <c r="Z63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC63" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
-      </c>
-      <c r="AD63" t="str">
-        <v>4 validé</v>
-      </c>
-      <c r="AE63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG63" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ63" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK63" t="str">
-        <v>583h15m</v>
-      </c>
-      <c r="AL63" t="str">
-        <v>308h</v>
-      </c>
-      <c r="AM63" t="str">
-        <v>67h45m</v>
-      </c>
-      <c r="AN63" s="1">
-        <v>45901</v>
-      </c>
-      <c r="AO63" s="1">
-        <v>45936.083333333336</v>
-      </c>
-      <c r="AP63" s="1">
-        <v>46174.083333333336</v>
-      </c>
-      <c r="AV63" t="str">
-        <v>MISSION LOCALE METROPOLE SUD - Antenne de La Bassée</v>
-      </c>
-      <c r="AW63" t="str">
-        <v>Valérie DUMORTIER</v>
-      </c>
-      <c r="BA63" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG63" t="str">
-        <v>594203</v>
-      </c>
-      <c r="BJ63" t="str">
-        <v>f58f6a32-c154-4179-93b1-c66690a1f0a6</v>
-      </c>
-      <c r="BK63" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL63" t="str">
-        <v/>
-      </c>
-      <c r="BM63" t="str">
-        <v/>
-      </c>
-      <c r="BN63" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BN63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BN54"/>
   </ignoredErrors>
 </worksheet>
 </file>